--- a/BRISAS/EXPENSAS/2026/SEPTIEMBRE/BRISAS-SEPTIEMBRE.xlsx
+++ b/BRISAS/EXPENSAS/2026/SEPTIEMBRE/BRISAS-SEPTIEMBRE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\SEPTIEMBRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B047A46-97CC-4B1C-B731-CD77A6E6E454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D90C6A-5451-4323-81F2-09171381406E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$B$1:$T$167</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$215</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$219</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="495">
   <si>
     <t>Dpto.</t>
   </si>
@@ -1515,6 +1515,21 @@
   </si>
   <si>
     <t>Deposito 14/09</t>
+  </si>
+  <si>
+    <t>Ferreteria Rex  - CUIT: 27164125136 - 24/09 - Lijas</t>
+  </si>
+  <si>
+    <t>Compra de cintas  - 09/09</t>
+  </si>
+  <si>
+    <t>Transf 29/08</t>
+  </si>
+  <si>
+    <t>Krayacich Matias - CUIT: 20228429725 - Fc. 000001447 - Se realizó el análisis de la topología de nodos de fibra óptica y la resolución del conflicto de IP duplicada en un nodo, junto con el borrado y re-agregado de 43 cámaras distribuidas en 4 monitores de dos puestos de vigilancia. Además, se actualizó el firmware de 2 dispositivos NVR, se configuró la actualización automática de fecha y hora en todos los DVR/NVR, se reemplazó una cámara analógica por una IP en el Puesto 2 y se reordenaron los puntos de conectividad en el armario bajo escritorio del Puesto 1 (utilizando materiales provistos por el cliente).</t>
+  </si>
+  <si>
+    <t>Tarazona Galvis Jose - CUIT: 2095917657 - Fc. 00000120 - Relevamiento y puesta en valor del sistema de videovigilancia de Brisas de Adrogué. Total: 24 cámaras reparadas, incluyendo reemplazo de 6 cámaras quemadas, reemplazo de 7 cámaras con lente quemado por dentro, cambio de 4 fuentes de alimentación y reparación de 7 cámaras por distintas fallas, incluyendo cambio de cajas estancas deterioradas/inundadas, cambio de video balun, plug de tensión y fichas de alimentación de 220V para las fuentes de las cámaras. El material de reparación fue provisto por Brisas de Adrogué.</t>
   </si>
 </sst>
 </file>
@@ -2399,7 +2414,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="456">
+  <cellXfs count="457">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -2906,10 +2921,7 @@
     <xf numFmtId="44" fontId="28" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="28" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="28" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2920,41 +2932,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3016,33 +2993,60 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3101,10 +3105,30 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="13" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3131,12 +3155,6 @@
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="19" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3561,7 +3579,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O215"/>
+  <dimension ref="A1:O219"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -3577,34 +3595,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="393"/>
-      <c r="B1" s="388" t="s">
+      <c r="A1" s="379"/>
+      <c r="B1" s="374" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="389"/>
-      <c r="D1" s="389"/>
-      <c r="E1" s="390"/>
+      <c r="C1" s="375"/>
+      <c r="D1" s="375"/>
+      <c r="E1" s="376"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="394"/>
-      <c r="B2" s="388" t="s">
+      <c r="A2" s="380"/>
+      <c r="B2" s="374" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="389"/>
-      <c r="D2" s="389"/>
-      <c r="E2" s="390"/>
+      <c r="C2" s="375"/>
+      <c r="D2" s="375"/>
+      <c r="E2" s="376"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="394"/>
-      <c r="B3" s="405" t="s">
+      <c r="A3" s="380"/>
+      <c r="B3" s="391" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="406"/>
-      <c r="D3" s="406"/>
-      <c r="E3" s="407"/>
+      <c r="C3" s="392"/>
+      <c r="D3" s="392"/>
+      <c r="E3" s="393"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="394"/>
+      <c r="A4" s="380"/>
       <c r="B4" s="43" t="s">
         <v>154</v>
       </c>
@@ -3613,7 +3631,7 @@
       <c r="E4" s="42"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="394"/>
+      <c r="A5" s="380"/>
       <c r="B5" s="46" t="s">
         <v>387</v>
       </c>
@@ -3622,7 +3640,7 @@
       <c r="E5" s="45"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="394"/>
+      <c r="A6" s="380"/>
       <c r="B6" s="47" t="s">
         <v>280</v>
       </c>
@@ -3631,7 +3649,7 @@
       <c r="E6" s="45"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="394"/>
+      <c r="A7" s="380"/>
       <c r="B7" s="47" t="s">
         <v>279</v>
       </c>
@@ -3640,13 +3658,13 @@
       <c r="E7" s="45"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="395"/>
-      <c r="B8" s="391" t="s">
+      <c r="A8" s="381"/>
+      <c r="B8" s="377" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="391"/>
-      <c r="D8" s="391"/>
-      <c r="E8" s="392"/>
+      <c r="C8" s="377"/>
+      <c r="D8" s="377"/>
+      <c r="E8" s="378"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="30"/>
@@ -3656,27 +3674,27 @@
       <c r="E9" s="30"/>
     </row>
     <row r="10" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="396" t="s">
+      <c r="A10" s="382" t="s">
         <v>386</v>
       </c>
-      <c r="B10" s="397"/>
-      <c r="C10" s="397"/>
-      <c r="D10" s="397"/>
-      <c r="E10" s="398"/>
+      <c r="B10" s="383"/>
+      <c r="C10" s="383"/>
+      <c r="D10" s="383"/>
+      <c r="E10" s="384"/>
     </row>
     <row r="11" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="399"/>
-      <c r="B11" s="400"/>
-      <c r="C11" s="400"/>
-      <c r="D11" s="400"/>
-      <c r="E11" s="401"/>
+      <c r="A11" s="385"/>
+      <c r="B11" s="386"/>
+      <c r="C11" s="386"/>
+      <c r="D11" s="386"/>
+      <c r="E11" s="387"/>
     </row>
     <row r="12" spans="1:5" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="402"/>
-      <c r="B12" s="403"/>
-      <c r="C12" s="403"/>
-      <c r="D12" s="403"/>
-      <c r="E12" s="404"/>
+      <c r="A12" s="388"/>
+      <c r="B12" s="389"/>
+      <c r="C12" s="389"/>
+      <c r="D12" s="389"/>
+      <c r="E12" s="390"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="30"/>
@@ -3693,34 +3711,34 @@
       <c r="E14" s="30"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="383" t="s">
+      <c r="A15" s="394" t="s">
         <v>238</v>
       </c>
-      <c r="B15" s="383"/>
-      <c r="C15" s="383"/>
-      <c r="D15" s="383"/>
-      <c r="E15" s="383"/>
+      <c r="B15" s="394"/>
+      <c r="C15" s="394"/>
+      <c r="D15" s="394"/>
+      <c r="E15" s="394"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="383"/>
-      <c r="B16" s="383"/>
-      <c r="C16" s="383"/>
-      <c r="D16" s="383"/>
-      <c r="E16" s="383"/>
+      <c r="A16" s="394"/>
+      <c r="B16" s="394"/>
+      <c r="C16" s="394"/>
+      <c r="D16" s="394"/>
+      <c r="E16" s="394"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="383"/>
-      <c r="B17" s="383"/>
-      <c r="C17" s="383"/>
-      <c r="D17" s="383"/>
-      <c r="E17" s="383"/>
+      <c r="A17" s="394"/>
+      <c r="B17" s="394"/>
+      <c r="C17" s="394"/>
+      <c r="D17" s="394"/>
+      <c r="E17" s="394"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="383"/>
-      <c r="B18" s="383"/>
-      <c r="C18" s="383"/>
-      <c r="D18" s="383"/>
-      <c r="E18" s="383"/>
+      <c r="A18" s="394"/>
+      <c r="B18" s="394"/>
+      <c r="C18" s="394"/>
+      <c r="D18" s="394"/>
+      <c r="E18" s="394"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="30"/>
@@ -3772,30 +3790,30 @@
       <c r="B24" s="257"/>
       <c r="C24" s="22"/>
       <c r="D24" s="259">
-        <v>2323546.3199999998</v>
+        <v>2306396.09</v>
       </c>
       <c r="E24" s="258"/>
       <c r="F24" s="30"/>
       <c r="G24" s="246"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="384" t="s">
+      <c r="A25" s="395" t="s">
         <v>389</v>
       </c>
-      <c r="B25" s="385"/>
+      <c r="B25" s="396"/>
       <c r="C25" s="22"/>
       <c r="D25" s="259">
-        <v>-505371.32</v>
+        <v>-501641.09</v>
       </c>
       <c r="E25" s="22"/>
       <c r="F25" s="30"/>
       <c r="G25" s="247"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="386" t="s">
+      <c r="A26" s="397" t="s">
         <v>390</v>
       </c>
-      <c r="B26" s="387"/>
+      <c r="B26" s="398"/>
       <c r="C26" s="22"/>
       <c r="D26" s="259">
         <v>0</v>
@@ -3812,7 +3830,7 @@
       <c r="C27" s="94"/>
       <c r="D27" s="189">
         <f>SUM(D24:D26)</f>
-        <v>1818174.9999999998</v>
+        <v>1804754.9999999998</v>
       </c>
       <c r="E27" s="79"/>
       <c r="F27" s="247"/>
@@ -3820,10 +3838,10 @@
       <c r="H27" s="71"/>
     </row>
     <row r="28" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="372" t="s">
+      <c r="A28" s="371" t="s">
         <v>419</v>
       </c>
-      <c r="B28" s="373"/>
+      <c r="B28" s="372"/>
       <c r="C28" s="22"/>
       <c r="D28" s="361">
         <v>2450000</v>
@@ -3833,7 +3851,7 @@
       </c>
       <c r="F28" s="30"/>
       <c r="G28" s="247">
-        <f>D28+D144</f>
+        <f>D28+D146</f>
         <v>2947450</v>
       </c>
     </row>
@@ -3860,7 +3878,7 @@
       <c r="D30" s="190"/>
       <c r="E30" s="81">
         <f>D27+D29</f>
-        <v>4268175</v>
+        <v>4254755</v>
       </c>
       <c r="F30" s="247"/>
       <c r="G30" s="30"/>
@@ -3973,10 +3991,10 @@
       <c r="G37" s="30"/>
     </row>
     <row r="38" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="372" t="s">
+      <c r="A38" s="371" t="s">
         <v>266</v>
       </c>
-      <c r="B38" s="373"/>
+      <c r="B38" s="372"/>
       <c r="C38" s="22"/>
       <c r="D38" s="360">
         <v>198615</v>
@@ -3988,10 +4006,10 @@
       <c r="G38" s="30"/>
     </row>
     <row r="39" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="372" t="s">
+      <c r="A39" s="371" t="s">
         <v>267</v>
       </c>
-      <c r="B39" s="373"/>
+      <c r="B39" s="372"/>
       <c r="C39" s="22"/>
       <c r="D39" s="194">
         <v>7805</v>
@@ -4003,10 +4021,10 @@
       <c r="G39" s="30"/>
     </row>
     <row r="40" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="372" t="s">
+      <c r="A40" s="371" t="s">
         <v>304</v>
       </c>
-      <c r="B40" s="373"/>
+      <c r="B40" s="372"/>
       <c r="C40" s="271"/>
       <c r="D40" s="360">
         <v>26214.080000000002</v>
@@ -4018,10 +4036,10 @@
       <c r="G40" s="30"/>
     </row>
     <row r="41" spans="1:9" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="372" t="s">
+      <c r="A41" s="371" t="s">
         <v>304</v>
       </c>
-      <c r="B41" s="373"/>
+      <c r="B41" s="372"/>
       <c r="C41" s="22"/>
       <c r="D41" s="360">
         <v>23573.47</v>
@@ -4058,10 +4076,10 @@
       <c r="G43" s="30"/>
     </row>
     <row r="44" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="372" t="s">
+      <c r="A44" s="371" t="s">
         <v>444</v>
       </c>
-      <c r="B44" s="374"/>
+      <c r="B44" s="373"/>
       <c r="C44" s="100"/>
       <c r="D44" s="360">
         <v>52575768.960000001</v>
@@ -4077,10 +4095,10 @@
       <c r="I44" s="37"/>
     </row>
     <row r="45" spans="1:9" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="372" t="s">
+      <c r="A45" s="371" t="s">
         <v>413</v>
       </c>
-      <c r="B45" s="374"/>
+      <c r="B45" s="373"/>
       <c r="C45" s="100"/>
       <c r="D45" s="360">
         <v>6304871.7599999998</v>
@@ -4119,10 +4137,10 @@
       <c r="G47" s="30"/>
     </row>
     <row r="48" spans="1:9" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="372" t="s">
+      <c r="A48" s="371" t="s">
         <v>449</v>
       </c>
-      <c r="B48" s="374"/>
+      <c r="B48" s="373"/>
       <c r="C48" s="100"/>
       <c r="D48" s="360">
         <v>1472058.6</v>
@@ -4134,10 +4152,10 @@
       <c r="G48" s="30"/>
     </row>
     <row r="49" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="372" t="s">
+      <c r="A49" s="371" t="s">
         <v>411</v>
       </c>
-      <c r="B49" s="374"/>
+      <c r="B49" s="373"/>
       <c r="C49" s="100"/>
       <c r="D49" s="360">
         <v>890281.7</v>
@@ -4149,10 +4167,10 @@
       <c r="G49" s="30"/>
     </row>
     <row r="50" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="372" t="s">
+      <c r="A50" s="371" t="s">
         <v>448</v>
       </c>
-      <c r="B50" s="374"/>
+      <c r="B50" s="373"/>
       <c r="C50" s="100"/>
       <c r="D50" s="360">
         <v>145751.48000000001</v>
@@ -4164,10 +4182,10 @@
       <c r="G50" s="30"/>
     </row>
     <row r="51" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="372" t="s">
+      <c r="A51" s="371" t="s">
         <v>473</v>
       </c>
-      <c r="B51" s="374"/>
+      <c r="B51" s="373"/>
       <c r="C51" s="100"/>
       <c r="D51" s="360">
         <v>913550</v>
@@ -4179,10 +4197,10 @@
       <c r="G51" s="30"/>
     </row>
     <row r="52" spans="1:7" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="372" t="s">
+      <c r="A52" s="371" t="s">
         <v>474</v>
       </c>
-      <c r="B52" s="374"/>
+      <c r="B52" s="373"/>
       <c r="C52" s="100"/>
       <c r="D52" s="360">
         <v>756250</v>
@@ -4194,10 +4212,10 @@
       <c r="G52" s="30"/>
     </row>
     <row r="53" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="372" t="s">
+      <c r="A53" s="371" t="s">
         <v>423</v>
       </c>
-      <c r="B53" s="373"/>
+      <c r="B53" s="372"/>
       <c r="C53" s="101"/>
       <c r="D53" s="360">
         <v>7500000</v>
@@ -4209,10 +4227,10 @@
       <c r="G53" s="30"/>
     </row>
     <row r="54" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="372" t="s">
+      <c r="A54" s="371" t="s">
         <v>464</v>
       </c>
-      <c r="B54" s="373"/>
+      <c r="B54" s="372"/>
       <c r="C54" s="101"/>
       <c r="D54" s="360">
         <v>700000</v>
@@ -4224,10 +4242,10 @@
       <c r="G54" s="30"/>
     </row>
     <row r="55" spans="1:7" ht="39" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="372" t="s">
+      <c r="A55" s="371" t="s">
         <v>393</v>
       </c>
-      <c r="B55" s="373"/>
+      <c r="B55" s="372"/>
       <c r="C55" s="101"/>
       <c r="D55" s="360">
         <v>228690</v>
@@ -4239,10 +4257,10 @@
       <c r="G55" s="30"/>
     </row>
     <row r="56" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="372" t="s">
+      <c r="A56" s="371" t="s">
         <v>453</v>
       </c>
-      <c r="B56" s="373"/>
+      <c r="B56" s="372"/>
       <c r="C56" s="101"/>
       <c r="D56" s="360">
         <v>325664.55</v>
@@ -4254,10 +4272,10 @@
       <c r="G56" s="30"/>
     </row>
     <row r="57" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="372" t="s">
+      <c r="A57" s="371" t="s">
         <v>454</v>
       </c>
-      <c r="B57" s="373"/>
+      <c r="B57" s="372"/>
       <c r="C57" s="101"/>
       <c r="D57" s="360">
         <v>943800</v>
@@ -4269,10 +4287,10 @@
       <c r="G57" s="30"/>
     </row>
     <row r="58" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="372" t="s">
+      <c r="A58" s="371" t="s">
         <v>336</v>
       </c>
-      <c r="B58" s="373"/>
+      <c r="B58" s="372"/>
       <c r="C58" s="101"/>
       <c r="D58" s="194">
         <v>820380</v>
@@ -4284,10 +4302,10 @@
       <c r="G58" s="30"/>
     </row>
     <row r="59" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="372" t="s">
+      <c r="A59" s="371" t="s">
         <v>414</v>
       </c>
-      <c r="B59" s="373"/>
+      <c r="B59" s="372"/>
       <c r="C59" s="101"/>
       <c r="D59" s="360">
         <v>120000</v>
@@ -4299,10 +4317,10 @@
       <c r="G59" s="30"/>
     </row>
     <row r="60" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="372" t="s">
+      <c r="A60" s="371" t="s">
         <v>422</v>
       </c>
-      <c r="B60" s="373"/>
+      <c r="B60" s="372"/>
       <c r="C60" s="101"/>
       <c r="D60" s="360">
         <v>360000</v>
@@ -4314,10 +4332,10 @@
       <c r="G60" s="30"/>
     </row>
     <row r="61" spans="1:7" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="372" t="s">
+      <c r="A61" s="371" t="s">
         <v>463</v>
       </c>
-      <c r="B61" s="373"/>
+      <c r="B61" s="372"/>
       <c r="C61" s="101"/>
       <c r="D61" s="360">
         <v>480000</v>
@@ -4329,10 +4347,10 @@
       <c r="G61" s="30"/>
     </row>
     <row r="62" spans="1:7" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="372" t="s">
+      <c r="A62" s="371" t="s">
         <v>476</v>
       </c>
-      <c r="B62" s="373"/>
+      <c r="B62" s="372"/>
       <c r="C62" s="101"/>
       <c r="D62" s="360">
         <v>480000</v>
@@ -4344,10 +4362,10 @@
       <c r="G62" s="30"/>
     </row>
     <row r="63" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="372" t="s">
+      <c r="A63" s="371" t="s">
         <v>431</v>
       </c>
-      <c r="B63" s="373"/>
+      <c r="B63" s="372"/>
       <c r="C63" s="101"/>
       <c r="D63" s="360">
         <v>150000</v>
@@ -4359,10 +4377,10 @@
       <c r="G63" s="30"/>
     </row>
     <row r="64" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="372" t="s">
+      <c r="A64" s="371" t="s">
         <v>394</v>
       </c>
-      <c r="B64" s="373"/>
+      <c r="B64" s="372"/>
       <c r="C64" s="101"/>
       <c r="D64" s="360">
         <v>1600000</v>
@@ -4374,10 +4392,10 @@
       <c r="G64" s="30"/>
     </row>
     <row r="65" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="372" t="s">
+      <c r="A65" s="371" t="s">
         <v>430</v>
       </c>
-      <c r="B65" s="373"/>
+      <c r="B65" s="372"/>
       <c r="C65" s="22"/>
       <c r="D65" s="360">
         <v>2877995</v>
@@ -4415,11 +4433,11 @@
       <c r="G67" s="30"/>
     </row>
     <row r="68" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="372" t="s">
+      <c r="A68" s="371" t="s">
         <v>417</v>
       </c>
-      <c r="B68" s="374"/>
-      <c r="C68" s="373"/>
+      <c r="B68" s="373"/>
+      <c r="C68" s="372"/>
       <c r="D68" s="362">
         <v>1798000</v>
       </c>
@@ -4429,134 +4447,134 @@
       <c r="F68" s="30"/>
       <c r="G68" s="30"/>
     </row>
-    <row r="69" spans="1:8" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="372" t="s">
-        <v>421</v>
-      </c>
-      <c r="B69" s="374"/>
-      <c r="C69" s="373"/>
+    <row r="69" spans="1:8" ht="166.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="371" t="s">
+        <v>493</v>
+      </c>
+      <c r="B69" s="373"/>
+      <c r="C69" s="370"/>
       <c r="D69" s="362">
-        <v>1922000</v>
+        <v>1900000</v>
       </c>
       <c r="E69" s="256" t="s">
-        <v>418</v>
+        <v>492</v>
       </c>
       <c r="F69" s="30"/>
       <c r="G69" s="30"/>
     </row>
-    <row r="70" spans="1:8" ht="91.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="372" t="s">
-        <v>438</v>
-      </c>
-      <c r="B70" s="374"/>
-      <c r="C70" s="373"/>
+    <row r="70" spans="1:8" ht="149.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="371" t="s">
+        <v>494</v>
+      </c>
+      <c r="B70" s="373"/>
+      <c r="C70" s="370"/>
       <c r="D70" s="362">
-        <v>1000000</v>
+        <v>2000000</v>
       </c>
       <c r="E70" s="256" t="s">
-        <v>418</v>
+        <v>492</v>
       </c>
       <c r="F70" s="30"/>
       <c r="G70" s="30"/>
     </row>
-    <row r="71" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="372" t="s">
-        <v>484</v>
-      </c>
-      <c r="B71" s="374"/>
-      <c r="C71" s="373"/>
+    <row r="71" spans="1:8" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="371" t="s">
+        <v>421</v>
+      </c>
+      <c r="B71" s="373"/>
+      <c r="C71" s="372"/>
       <c r="D71" s="362">
-        <v>2690000</v>
+        <v>1922000</v>
       </c>
       <c r="E71" s="256" t="s">
-        <v>483</v>
+        <v>418</v>
       </c>
       <c r="F71" s="30"/>
       <c r="G71" s="30"/>
     </row>
-    <row r="72" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="372" t="s">
-        <v>465</v>
+    <row r="72" spans="1:8" ht="91.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="371" t="s">
+        <v>438</v>
       </c>
       <c r="B72" s="373"/>
-      <c r="C72" s="22"/>
+      <c r="C72" s="372"/>
       <c r="D72" s="362">
-        <v>820000</v>
-      </c>
-      <c r="E72" s="78" t="s">
-        <v>466</v>
+        <v>1000000</v>
+      </c>
+      <c r="E72" s="256" t="s">
+        <v>418</v>
       </c>
       <c r="F72" s="30"/>
       <c r="G72" s="30"/>
     </row>
-    <row r="73" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="372" t="s">
-        <v>462</v>
+    <row r="73" spans="1:8" ht="154.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="371" t="s">
+        <v>484</v>
       </c>
       <c r="B73" s="373"/>
-      <c r="C73" s="97"/>
+      <c r="C73" s="372"/>
       <c r="D73" s="362">
-        <v>130000</v>
-      </c>
-      <c r="E73" s="140" t="s">
-        <v>412</v>
-      </c>
-      <c r="F73" s="251"/>
+        <v>2690000</v>
+      </c>
+      <c r="E73" s="256" t="s">
+        <v>483</v>
+      </c>
+      <c r="F73" s="30"/>
       <c r="G73" s="30"/>
     </row>
-    <row r="74" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="372" t="s">
-        <v>410</v>
-      </c>
-      <c r="B74" s="373"/>
-      <c r="C74" s="97"/>
+    <row r="74" spans="1:8" ht="111.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="371" t="s">
+        <v>465</v>
+      </c>
+      <c r="B74" s="372"/>
+      <c r="C74" s="22"/>
       <c r="D74" s="362">
-        <v>350000</v>
-      </c>
-      <c r="E74" s="140" t="s">
-        <v>403</v>
+        <v>820000</v>
+      </c>
+      <c r="E74" s="78" t="s">
+        <v>466</v>
       </c>
       <c r="F74" s="30"/>
       <c r="G74" s="30"/>
     </row>
-    <row r="75" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="372" t="s">
-        <v>439</v>
-      </c>
-      <c r="B75" s="373"/>
+    <row r="75" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="371" t="s">
+        <v>462</v>
+      </c>
+      <c r="B75" s="372"/>
       <c r="C75" s="97"/>
       <c r="D75" s="362">
-        <v>36500</v>
+        <v>130000</v>
       </c>
       <c r="E75" s="140" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="F75" s="251"/>
       <c r="G75" s="30"/>
     </row>
-    <row r="76" spans="1:8" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="372" t="s">
-        <v>440</v>
-      </c>
-      <c r="B76" s="373"/>
+    <row r="76" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="371" t="s">
+        <v>410</v>
+      </c>
+      <c r="B76" s="372"/>
       <c r="C76" s="97"/>
       <c r="D76" s="362">
-        <v>363675.38</v>
+        <v>350000</v>
       </c>
       <c r="E76" s="140" t="s">
-        <v>418</v>
-      </c>
-      <c r="F76" s="251"/>
+        <v>403</v>
+      </c>
+      <c r="F76" s="30"/>
       <c r="G76" s="30"/>
     </row>
-    <row r="77" spans="1:8" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="372" t="s">
-        <v>424</v>
-      </c>
-      <c r="B77" s="373"/>
+    <row r="77" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="371" t="s">
+        <v>439</v>
+      </c>
+      <c r="B77" s="372"/>
       <c r="C77" s="97"/>
       <c r="D77" s="362">
-        <v>365000</v>
+        <v>36500</v>
       </c>
       <c r="E77" s="140" t="s">
         <v>418</v>
@@ -4564,74 +4582,74 @@
       <c r="F77" s="251"/>
       <c r="G77" s="30"/>
     </row>
-    <row r="78" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="372" t="s">
-        <v>457</v>
-      </c>
-      <c r="B78" s="373"/>
+    <row r="78" spans="1:8" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="371" t="s">
+        <v>440</v>
+      </c>
+      <c r="B78" s="372"/>
       <c r="C78" s="97"/>
       <c r="D78" s="362">
-        <v>34010</v>
-      </c>
-      <c r="E78" s="84" t="s">
-        <v>415</v>
-      </c>
-      <c r="F78" s="30"/>
+        <v>363675.38</v>
+      </c>
+      <c r="E78" s="140" t="s">
+        <v>418</v>
+      </c>
+      <c r="F78" s="251"/>
       <c r="G78" s="30"/>
     </row>
-    <row r="79" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="372" t="s">
-        <v>433</v>
-      </c>
-      <c r="B79" s="373"/>
+    <row r="79" spans="1:8" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="371" t="s">
+        <v>424</v>
+      </c>
+      <c r="B79" s="372"/>
       <c r="C79" s="97"/>
       <c r="D79" s="362">
-        <v>363000</v>
+        <v>365000</v>
       </c>
       <c r="E79" s="140" t="s">
-        <v>434</v>
-      </c>
-      <c r="F79" s="30"/>
+        <v>418</v>
+      </c>
+      <c r="F79" s="251"/>
       <c r="G79" s="30"/>
     </row>
-    <row r="80" spans="1:8" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="372" t="s">
-        <v>467</v>
-      </c>
-      <c r="B80" s="373"/>
+    <row r="80" spans="1:8" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="371" t="s">
+        <v>457</v>
+      </c>
+      <c r="B80" s="372"/>
       <c r="C80" s="97"/>
       <c r="D80" s="362">
-        <v>132000</v>
-      </c>
-      <c r="E80" s="140" t="s">
-        <v>466</v>
+        <v>34010</v>
+      </c>
+      <c r="E80" s="84" t="s">
+        <v>415</v>
       </c>
       <c r="F80" s="30"/>
       <c r="G80" s="30"/>
     </row>
     <row r="81" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="375" t="s">
-        <v>467</v>
-      </c>
-      <c r="B81" s="376"/>
+      <c r="A81" s="371" t="s">
+        <v>433</v>
+      </c>
+      <c r="B81" s="372"/>
       <c r="C81" s="97"/>
       <c r="D81" s="362">
-        <v>268760</v>
+        <v>363000</v>
       </c>
       <c r="E81" s="140" t="s">
-        <v>478</v>
+        <v>434</v>
       </c>
       <c r="F81" s="30"/>
       <c r="G81" s="30"/>
     </row>
     <row r="82" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="372" t="s">
-        <v>468</v>
-      </c>
-      <c r="B82" s="373"/>
+      <c r="A82" s="371" t="s">
+        <v>467</v>
+      </c>
+      <c r="B82" s="372"/>
       <c r="C82" s="97"/>
       <c r="D82" s="362">
-        <v>242600</v>
+        <v>132000</v>
       </c>
       <c r="E82" s="140" t="s">
         <v>466</v>
@@ -4640,160 +4658,160 @@
       <c r="G82" s="30"/>
     </row>
     <row r="83" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="372" t="s">
-        <v>475</v>
-      </c>
-      <c r="B83" s="373"/>
+      <c r="A83" s="399" t="s">
+        <v>467</v>
+      </c>
+      <c r="B83" s="400"/>
       <c r="C83" s="97"/>
       <c r="D83" s="362">
-        <v>386381.46</v>
+        <v>268760</v>
       </c>
       <c r="E83" s="140" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="F83" s="30"/>
       <c r="G83" s="30"/>
     </row>
-    <row r="84" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="372" t="s">
-        <v>408</v>
-      </c>
-      <c r="B84" s="373"/>
+    <row r="84" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="371" t="s">
+        <v>468</v>
+      </c>
+      <c r="B84" s="372"/>
       <c r="C84" s="97"/>
       <c r="D84" s="362">
-        <v>1200000</v>
+        <v>242600</v>
       </c>
       <c r="E84" s="140" t="s">
-        <v>405</v>
+        <v>466</v>
       </c>
       <c r="F84" s="30"/>
       <c r="G84" s="30"/>
     </row>
-    <row r="85" spans="1:7" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="372" t="s">
-        <v>429</v>
-      </c>
-      <c r="B85" s="373"/>
+    <row r="85" spans="1:7" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="371" t="s">
+        <v>475</v>
+      </c>
+      <c r="B85" s="372"/>
       <c r="C85" s="97"/>
       <c r="D85" s="362">
-        <v>607420</v>
+        <v>386381.46</v>
       </c>
       <c r="E85" s="140" t="s">
-        <v>412</v>
+        <v>471</v>
       </c>
       <c r="F85" s="30"/>
       <c r="G85" s="30"/>
     </row>
-    <row r="86" spans="1:7" ht="271.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="372" t="s">
-        <v>460</v>
-      </c>
-      <c r="B86" s="373"/>
+    <row r="86" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="371" t="s">
+        <v>408</v>
+      </c>
+      <c r="B86" s="372"/>
       <c r="C86" s="97"/>
       <c r="D86" s="362">
-        <v>8120483.25</v>
+        <v>1200000</v>
       </c>
       <c r="E86" s="140" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="F86" s="30"/>
       <c r="G86" s="30"/>
     </row>
-    <row r="87" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="372" t="s">
-        <v>461</v>
-      </c>
-      <c r="B87" s="373"/>
+    <row r="87" spans="1:7" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="371" t="s">
+        <v>429</v>
+      </c>
+      <c r="B87" s="372"/>
       <c r="C87" s="97"/>
       <c r="D87" s="362">
-        <v>1000000</v>
+        <v>607420</v>
       </c>
       <c r="E87" s="140" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="F87" s="30"/>
       <c r="G87" s="30"/>
     </row>
-    <row r="88" spans="1:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="372" t="s">
-        <v>472</v>
-      </c>
-      <c r="B88" s="373"/>
+    <row r="88" spans="1:7" ht="271.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="371" t="s">
+        <v>460</v>
+      </c>
+      <c r="B88" s="372"/>
       <c r="C88" s="97"/>
       <c r="D88" s="362">
-        <v>303000</v>
-      </c>
-      <c r="E88" s="84" t="s">
-        <v>471</v>
+        <v>8120483.25</v>
+      </c>
+      <c r="E88" s="140" t="s">
+        <v>399</v>
       </c>
       <c r="F88" s="30"/>
       <c r="G88" s="30"/>
     </row>
-    <row r="89" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="372" t="s">
-        <v>432</v>
-      </c>
-      <c r="B89" s="373"/>
+    <row r="89" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="371" t="s">
+        <v>461</v>
+      </c>
+      <c r="B89" s="372"/>
       <c r="C89" s="97"/>
       <c r="D89" s="362">
-        <v>253700</v>
-      </c>
-      <c r="E89" s="84" t="s">
-        <v>412</v>
+        <v>1000000</v>
+      </c>
+      <c r="E89" s="140" t="s">
+        <v>399</v>
       </c>
       <c r="F89" s="30"/>
       <c r="G89" s="30"/>
     </row>
-    <row r="90" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="372" t="s">
-        <v>485</v>
-      </c>
-      <c r="B90" s="373"/>
+    <row r="90" spans="1:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="371" t="s">
+        <v>472</v>
+      </c>
+      <c r="B90" s="372"/>
       <c r="C90" s="97"/>
       <c r="D90" s="362">
-        <v>112400</v>
+        <v>303000</v>
       </c>
       <c r="E90" s="84" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="F90" s="30"/>
       <c r="G90" s="30"/>
     </row>
     <row r="91" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="372" t="s">
-        <v>456</v>
-      </c>
-      <c r="B91" s="373"/>
+      <c r="A91" s="371" t="s">
+        <v>432</v>
+      </c>
+      <c r="B91" s="372"/>
       <c r="C91" s="97"/>
       <c r="D91" s="362">
-        <v>1500000</v>
-      </c>
-      <c r="E91" s="140" t="s">
-        <v>407</v>
+        <v>253700</v>
+      </c>
+      <c r="E91" s="84" t="s">
+        <v>412</v>
       </c>
       <c r="F91" s="30"/>
       <c r="G91" s="30"/>
     </row>
     <row r="92" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="372" t="s">
-        <v>409</v>
-      </c>
-      <c r="B92" s="373"/>
+      <c r="A92" s="371" t="s">
+        <v>485</v>
+      </c>
+      <c r="B92" s="372"/>
       <c r="C92" s="97"/>
       <c r="D92" s="362">
-        <v>2100000</v>
-      </c>
-      <c r="E92" s="140" t="s">
-        <v>403</v>
+        <v>112400</v>
+      </c>
+      <c r="E92" s="84" t="s">
+        <v>486</v>
       </c>
       <c r="F92" s="30"/>
       <c r="G92" s="30"/>
     </row>
     <row r="93" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="372" t="s">
-        <v>406</v>
-      </c>
-      <c r="B93" s="373"/>
+      <c r="A93" s="371" t="s">
+        <v>456</v>
+      </c>
+      <c r="B93" s="372"/>
       <c r="C93" s="97"/>
       <c r="D93" s="362">
         <v>1500000</v>
@@ -4805,672 +4823,684 @@
       <c r="G93" s="30"/>
     </row>
     <row r="94" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="372" t="s">
-        <v>442</v>
-      </c>
-      <c r="B94" s="373"/>
+      <c r="A94" s="371" t="s">
+        <v>409</v>
+      </c>
+      <c r="B94" s="372"/>
       <c r="C94" s="97"/>
       <c r="D94" s="362">
-        <v>1500000</v>
+        <v>2100000</v>
       </c>
       <c r="E94" s="140" t="s">
-        <v>443</v>
+        <v>403</v>
       </c>
       <c r="F94" s="30"/>
       <c r="G94" s="30"/>
     </row>
     <row r="95" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="372" t="s">
-        <v>477</v>
-      </c>
-      <c r="B95" s="373"/>
+      <c r="A95" s="371" t="s">
+        <v>406</v>
+      </c>
+      <c r="B95" s="372"/>
       <c r="C95" s="97"/>
       <c r="D95" s="362">
-        <v>2550000</v>
+        <v>1500000</v>
       </c>
       <c r="E95" s="140" t="s">
-        <v>471</v>
+        <v>407</v>
       </c>
       <c r="F95" s="30"/>
       <c r="G95" s="30"/>
     </row>
     <row r="96" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="372" t="s">
-        <v>402</v>
-      </c>
-      <c r="B96" s="373"/>
+      <c r="A96" s="371" t="s">
+        <v>442</v>
+      </c>
+      <c r="B96" s="372"/>
       <c r="C96" s="97"/>
       <c r="D96" s="362">
-        <v>134310</v>
+        <v>1500000</v>
       </c>
       <c r="E96" s="140" t="s">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="F96" s="30"/>
       <c r="G96" s="30"/>
     </row>
-    <row r="97" spans="1:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="372" t="s">
-        <v>400</v>
-      </c>
-      <c r="B97" s="373"/>
+    <row r="97" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="371" t="s">
+        <v>477</v>
+      </c>
+      <c r="B97" s="372"/>
       <c r="C97" s="97"/>
       <c r="D97" s="362">
-        <v>132173.57999999999</v>
-      </c>
-      <c r="E97" s="84" t="s">
-        <v>458</v>
+        <v>2550000</v>
+      </c>
+      <c r="E97" s="140" t="s">
+        <v>471</v>
       </c>
       <c r="F97" s="30"/>
       <c r="G97" s="30"/>
     </row>
-    <row r="98" spans="1:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="372" t="s">
-        <v>436</v>
-      </c>
-      <c r="B98" s="373"/>
+    <row r="98" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="371" t="s">
+        <v>402</v>
+      </c>
+      <c r="B98" s="372"/>
       <c r="C98" s="97"/>
       <c r="D98" s="362">
-        <v>80361.81</v>
-      </c>
-      <c r="E98" s="84" t="s">
-        <v>435</v>
+        <v>134310</v>
+      </c>
+      <c r="E98" s="140" t="s">
+        <v>401</v>
       </c>
       <c r="F98" s="30"/>
       <c r="G98" s="30"/>
     </row>
-    <row r="99" spans="1:7" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="372" t="s">
-        <v>451</v>
-      </c>
-      <c r="B99" s="373"/>
+    <row r="99" spans="1:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="371" t="s">
+        <v>400</v>
+      </c>
+      <c r="B99" s="372"/>
       <c r="C99" s="97"/>
       <c r="D99" s="362">
-        <v>43590.79</v>
+        <v>132173.57999999999</v>
       </c>
       <c r="E99" s="84" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="F99" s="30"/>
       <c r="G99" s="30"/>
     </row>
-    <row r="100" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="372" t="s">
-        <v>425</v>
-      </c>
-      <c r="B100" s="373"/>
+    <row r="100" spans="1:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="371" t="s">
+        <v>436</v>
+      </c>
+      <c r="B100" s="372"/>
       <c r="C100" s="97"/>
       <c r="D100" s="362">
-        <v>322000</v>
-      </c>
-      <c r="E100" s="140" t="s">
-        <v>418</v>
+        <v>80361.81</v>
+      </c>
+      <c r="E100" s="84" t="s">
+        <v>435</v>
       </c>
       <c r="F100" s="30"/>
       <c r="G100" s="30"/>
     </row>
-    <row r="101" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="103" t="s">
-        <v>179</v>
-      </c>
-      <c r="B101" s="103"/>
-      <c r="C101" s="103"/>
-      <c r="D101" s="198"/>
-      <c r="E101" s="80">
-        <f>SUM(D68:D100)</f>
-        <v>32361366.27</v>
+    <row r="101" spans="1:7" ht="55.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="371" t="s">
+        <v>451</v>
+      </c>
+      <c r="B101" s="372"/>
+      <c r="C101" s="97"/>
+      <c r="D101" s="362">
+        <v>43590.79</v>
+      </c>
+      <c r="E101" s="84" t="s">
+        <v>434</v>
       </c>
       <c r="F101" s="30"/>
       <c r="G101" s="30"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A102" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B102" s="8"/>
-      <c r="C102" s="8"/>
-      <c r="D102" s="199"/>
-      <c r="E102" s="24"/>
+    <row r="102" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="371" t="s">
+        <v>425</v>
+      </c>
+      <c r="B102" s="372"/>
+      <c r="C102" s="97"/>
+      <c r="D102" s="362">
+        <v>322000</v>
+      </c>
+      <c r="E102" s="140" t="s">
+        <v>418</v>
+      </c>
       <c r="F102" s="30"/>
       <c r="G102" s="30"/>
     </row>
-    <row r="103" spans="1:7" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="372" t="s">
-        <v>395</v>
-      </c>
-      <c r="B103" s="373"/>
-      <c r="C103" s="22"/>
-      <c r="D103" s="359">
-        <v>3218160</v>
-      </c>
-      <c r="E103" s="84" t="s">
-        <v>338</v>
+    <row r="103" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="103" t="s">
+        <v>179</v>
+      </c>
+      <c r="B103" s="103"/>
+      <c r="C103" s="103"/>
+      <c r="D103" s="198"/>
+      <c r="E103" s="80">
+        <f>SUM(D68:D102)</f>
+        <v>36261366.270000003</v>
       </c>
       <c r="F103" s="30"/>
       <c r="G103" s="30"/>
     </row>
-    <row r="104" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="95" t="s">
-        <v>149</v>
-      </c>
-      <c r="B104" s="95"/>
-      <c r="C104" s="95"/>
-      <c r="D104" s="192"/>
-      <c r="E104" s="81">
-        <f>SUM(D103:D103)</f>
-        <v>3218160</v>
-      </c>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B104" s="8"/>
+      <c r="C104" s="8"/>
+      <c r="D104" s="199"/>
+      <c r="E104" s="24"/>
       <c r="F104" s="30"/>
       <c r="G104" s="30"/>
     </row>
-    <row r="105" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B105" s="102"/>
-      <c r="C105" s="9"/>
-      <c r="D105" s="197"/>
-      <c r="E105" s="27"/>
+    <row r="105" spans="1:7" ht="23.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="371" t="s">
+        <v>395</v>
+      </c>
+      <c r="B105" s="372"/>
+      <c r="C105" s="22"/>
+      <c r="D105" s="359">
+        <v>3218160</v>
+      </c>
+      <c r="E105" s="84" t="s">
+        <v>338</v>
+      </c>
       <c r="F105" s="30"/>
       <c r="G105" s="30"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A106" s="22" t="s">
+    <row r="106" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="95" t="s">
+        <v>149</v>
+      </c>
+      <c r="B106" s="95"/>
+      <c r="C106" s="95"/>
+      <c r="D106" s="192"/>
+      <c r="E106" s="81">
+        <f>SUM(D105:D105)</f>
+        <v>3218160</v>
+      </c>
+      <c r="F106" s="30"/>
+      <c r="G106" s="30"/>
+    </row>
+    <row r="107" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B107" s="102"/>
+      <c r="C107" s="9"/>
+      <c r="D107" s="197"/>
+      <c r="E107" s="27"/>
+      <c r="F107" s="30"/>
+      <c r="G107" s="30"/>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B106" s="22"/>
-      <c r="C106" s="22"/>
-      <c r="D106" s="194">
+      <c r="B108" s="22"/>
+      <c r="C108" s="22"/>
+      <c r="D108" s="194">
         <f>1958349.8-25093-1</f>
         <v>1933255.8</v>
       </c>
-      <c r="E106" s="29"/>
-      <c r="F106" s="30"/>
-      <c r="G106" s="30"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A107" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B107" s="22"/>
-      <c r="C107" s="22"/>
-      <c r="D107" s="194">
-        <v>69000</v>
-      </c>
-      <c r="E107" s="28"/>
-      <c r="F107" s="30"/>
-      <c r="G107" s="30"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A108" s="104" t="s">
-        <v>150</v>
-      </c>
-      <c r="B108" s="104"/>
-      <c r="C108" s="104"/>
-      <c r="D108" s="200"/>
-      <c r="E108" s="83">
-        <f>SUM(D106:D107)</f>
-        <v>2002255.8</v>
-      </c>
+      <c r="E108" s="29"/>
       <c r="F108" s="30"/>
       <c r="G108" s="30"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A109" s="22"/>
+      <c r="A109" s="22" t="s">
+        <v>23</v>
+      </c>
       <c r="B109" s="22"/>
       <c r="C109" s="22"/>
-      <c r="D109" s="22"/>
-      <c r="E109" s="52"/>
+      <c r="D109" s="194">
+        <v>69000</v>
+      </c>
+      <c r="E109" s="28"/>
       <c r="F109" s="30"/>
       <c r="G109" s="30"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A110" s="22"/>
-      <c r="B110" s="22"/>
-      <c r="C110" s="22"/>
-      <c r="D110" s="22"/>
-      <c r="E110" s="52"/>
-      <c r="F110" s="250"/>
-      <c r="G110" s="252"/>
-    </row>
-    <row r="111" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="105" t="s">
+      <c r="A110" s="104" t="s">
+        <v>150</v>
+      </c>
+      <c r="B110" s="104"/>
+      <c r="C110" s="104"/>
+      <c r="D110" s="200"/>
+      <c r="E110" s="83">
+        <f>SUM(D108:D109)</f>
+        <v>2002255.8</v>
+      </c>
+      <c r="F110" s="30"/>
+      <c r="G110" s="30"/>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111" s="22"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="52"/>
+      <c r="F111" s="30"/>
+      <c r="G111" s="30"/>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="22"/>
+      <c r="B112" s="22"/>
+      <c r="C112" s="22"/>
+      <c r="D112" s="22"/>
+      <c r="E112" s="52"/>
+      <c r="F112" s="250"/>
+      <c r="G112" s="252"/>
+    </row>
+    <row r="113" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="B111" s="106"/>
-      <c r="C111" s="51"/>
-      <c r="D111" s="51"/>
-      <c r="E111" s="138">
-        <f>(SUM(E30:E109))</f>
-        <v>123129661.33999999</v>
-      </c>
-      <c r="F111" s="253"/>
-      <c r="G111" s="30"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A112" s="30"/>
-      <c r="B112" s="30"/>
-      <c r="C112" s="30"/>
-      <c r="D112" s="30"/>
-      <c r="E112" s="30"/>
-      <c r="F112" s="30"/>
-      <c r="G112" s="30"/>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A113" s="30"/>
-      <c r="B113" s="30"/>
-      <c r="C113" s="30"/>
-      <c r="D113" s="30"/>
-      <c r="E113" s="30"/>
-      <c r="F113" s="30"/>
+      <c r="B113" s="106"/>
+      <c r="C113" s="51"/>
+      <c r="D113" s="51"/>
+      <c r="E113" s="138">
+        <f>(SUM(E30:E111))</f>
+        <v>127016241.33999999</v>
+      </c>
+      <c r="F113" s="253"/>
       <c r="G113" s="30"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A114" s="107" t="s">
-        <v>9</v>
-      </c>
-      <c r="B114" s="40"/>
-      <c r="C114" s="40"/>
-      <c r="D114" s="40"/>
-      <c r="E114" s="40"/>
+      <c r="A114" s="30"/>
+      <c r="B114" s="30"/>
+      <c r="C114" s="30"/>
+      <c r="D114" s="30"/>
+      <c r="E114" s="30"/>
       <c r="F114" s="30"/>
       <c r="G114" s="30"/>
     </row>
-    <row r="115" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="372" t="s">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="30"/>
+      <c r="D115" s="30"/>
+      <c r="E115" s="30"/>
+      <c r="F115" s="30"/>
+      <c r="G115" s="30"/>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" s="107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B116" s="40"/>
+      <c r="C116" s="40"/>
+      <c r="D116" s="40"/>
+      <c r="E116" s="40"/>
+      <c r="F116" s="30"/>
+      <c r="G116" s="30"/>
+    </row>
+    <row r="117" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="371" t="s">
         <v>404</v>
       </c>
-      <c r="B115" s="373"/>
-      <c r="C115" s="22"/>
-      <c r="D115" s="360">
+      <c r="B117" s="372"/>
+      <c r="C117" s="22"/>
+      <c r="D117" s="360">
         <v>2574957.5</v>
       </c>
-      <c r="E115" s="52" t="s">
+      <c r="E117" s="52" t="s">
         <v>405</v>
       </c>
-      <c r="F115" s="30">
+      <c r="F117" s="30">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="G115" s="30"/>
-    </row>
-    <row r="116" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="372" t="s">
+      <c r="G117" s="30"/>
+    </row>
+    <row r="118" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="371" t="s">
         <v>341</v>
       </c>
-      <c r="B116" s="373"/>
-      <c r="C116" s="22"/>
-      <c r="D116" s="360">
-        <v>83694.649999999994</v>
-      </c>
-      <c r="E116" s="242" t="s">
-        <v>469</v>
-      </c>
-      <c r="F116" s="30">
-        <f>F115+1</f>
-        <v>2</v>
-      </c>
-      <c r="G116" s="30"/>
-    </row>
-    <row r="117" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="372" t="s">
-        <v>342</v>
-      </c>
-      <c r="B117" s="373"/>
-      <c r="C117" s="22"/>
-      <c r="D117" s="360">
-        <v>83694.649999999994</v>
-      </c>
-      <c r="E117" s="242" t="str">
-        <f>E116</f>
-        <v>Debito 22/09</v>
-      </c>
-      <c r="F117" s="30">
-        <f t="shared" ref="F117:F126" si="0">F116+1</f>
-        <v>3</v>
-      </c>
-      <c r="G117" s="30"/>
-    </row>
-    <row r="118" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="372" t="s">
-        <v>343</v>
-      </c>
-      <c r="B118" s="373"/>
+      <c r="B118" s="372"/>
       <c r="C118" s="22"/>
       <c r="D118" s="360">
+        <v>83694.649999999994</v>
+      </c>
+      <c r="E118" s="242" t="s">
+        <v>469</v>
+      </c>
+      <c r="F118" s="30">
+        <f>F117+1</f>
+        <v>2</v>
+      </c>
+      <c r="G118" s="30"/>
+    </row>
+    <row r="119" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="371" t="s">
+        <v>342</v>
+      </c>
+      <c r="B119" s="372"/>
+      <c r="C119" s="22"/>
+      <c r="D119" s="360">
+        <v>83694.649999999994</v>
+      </c>
+      <c r="E119" s="242" t="str">
+        <f>E118</f>
+        <v>Debito 22/09</v>
+      </c>
+      <c r="F119" s="30">
+        <f t="shared" ref="F119:F128" si="0">F118+1</f>
+        <v>3</v>
+      </c>
+      <c r="G119" s="30"/>
+    </row>
+    <row r="120" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A120" s="371" t="s">
+        <v>343</v>
+      </c>
+      <c r="B120" s="372"/>
+      <c r="C120" s="22"/>
+      <c r="D120" s="360">
         <v>76773.23</v>
       </c>
-      <c r="E118" s="242" t="str">
-        <f>E117</f>
+      <c r="E120" s="242" t="str">
+        <f>E119</f>
         <v>Debito 22/09</v>
       </c>
-      <c r="F118" s="30">
+      <c r="F120" s="30">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="G118" s="30"/>
-    </row>
-    <row r="119" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="372" t="s">
+      <c r="G120" s="30"/>
+    </row>
+    <row r="121" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="371" t="s">
         <v>355</v>
       </c>
-      <c r="B119" s="373"/>
-      <c r="C119" s="22"/>
-      <c r="D119" s="360">
+      <c r="B121" s="372"/>
+      <c r="C121" s="22"/>
+      <c r="D121" s="360">
         <v>82044.789999999994</v>
       </c>
-      <c r="E119" s="242" t="s">
+      <c r="E121" s="242" t="s">
         <v>403</v>
       </c>
-      <c r="F119" s="30">
+      <c r="F121" s="30">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G119" s="30"/>
-    </row>
-    <row r="120" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="372" t="s">
+      <c r="G121" s="30"/>
+    </row>
+    <row r="122" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="371" t="s">
         <v>344</v>
       </c>
-      <c r="B120" s="373"/>
-      <c r="C120" s="22"/>
-      <c r="D120" s="360">
+      <c r="B122" s="372"/>
+      <c r="C122" s="22"/>
+      <c r="D122" s="360">
         <v>512864.3</v>
       </c>
-      <c r="E120" s="242" t="s">
+      <c r="E122" s="242" t="s">
         <v>403</v>
       </c>
-      <c r="F120" s="30">
+      <c r="F122" s="30">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="G120" s="30"/>
-    </row>
-    <row r="121" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="372" t="s">
+      <c r="G122" s="30"/>
+    </row>
+    <row r="123" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="371" t="s">
         <v>345</v>
       </c>
-      <c r="B121" s="373"/>
-      <c r="C121" s="22"/>
-      <c r="D121" s="360">
+      <c r="B123" s="372"/>
+      <c r="C123" s="22"/>
+      <c r="D123" s="360">
         <v>1267805.3700000001</v>
       </c>
-      <c r="E121" s="242" t="s">
+      <c r="E123" s="242" t="s">
         <v>459</v>
       </c>
-      <c r="F121" s="30">
+      <c r="F123" s="30">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="G121" s="30"/>
-    </row>
-    <row r="122" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="372" t="s">
+      <c r="G123" s="30"/>
+    </row>
+    <row r="124" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A124" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="B122" s="373"/>
-      <c r="C122" s="22"/>
-      <c r="D122" s="360">
+      <c r="B124" s="372"/>
+      <c r="C124" s="22"/>
+      <c r="D124" s="360">
         <v>184910.38</v>
       </c>
-      <c r="E122" s="242" t="s">
+      <c r="E124" s="242" t="s">
         <v>416</v>
       </c>
-      <c r="F122" s="30">
+      <c r="F124" s="30">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G122" s="30"/>
-    </row>
-    <row r="123" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="372" t="s">
+      <c r="G124" s="30"/>
+    </row>
+    <row r="125" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A125" s="371" t="s">
         <v>348</v>
       </c>
-      <c r="B123" s="373"/>
-      <c r="C123" s="22"/>
-      <c r="D123" s="360">
-        <v>227417.49</v>
-      </c>
-      <c r="E123" s="242" t="s">
-        <v>469</v>
-      </c>
-      <c r="F123" s="30"/>
-      <c r="G123" s="30"/>
-    </row>
-    <row r="124" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="372" t="s">
-        <v>349</v>
-      </c>
-      <c r="B124" s="373"/>
-      <c r="C124" s="22"/>
-      <c r="D124" s="360">
-        <v>180329.89</v>
-      </c>
-      <c r="E124" s="242" t="s">
-        <v>479</v>
-      </c>
-      <c r="F124" s="30">
-        <f>F122+1</f>
-        <v>9</v>
-      </c>
-      <c r="G124" s="30"/>
-    </row>
-    <row r="125" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="372" t="s">
-        <v>350</v>
-      </c>
-      <c r="B125" s="373"/>
+      <c r="B125" s="372"/>
       <c r="C125" s="22"/>
       <c r="D125" s="360">
-        <v>285600.08</v>
+        <v>227417.49</v>
       </c>
       <c r="E125" s="242" t="s">
         <v>469</v>
       </c>
-      <c r="F125" s="30">
+      <c r="F125" s="30"/>
+      <c r="G125" s="30"/>
+    </row>
+    <row r="126" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="371" t="s">
+        <v>349</v>
+      </c>
+      <c r="B126" s="372"/>
+      <c r="C126" s="22"/>
+      <c r="D126" s="360">
+        <v>180329.89</v>
+      </c>
+      <c r="E126" s="242" t="s">
+        <v>479</v>
+      </c>
+      <c r="F126" s="30">
+        <f>F124+1</f>
+        <v>9</v>
+      </c>
+      <c r="G126" s="30"/>
+    </row>
+    <row r="127" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="371" t="s">
+        <v>350</v>
+      </c>
+      <c r="B127" s="372"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="360">
+        <v>285600.08</v>
+      </c>
+      <c r="E127" s="242" t="s">
+        <v>469</v>
+      </c>
+      <c r="F127" s="30">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="G125" s="30"/>
-    </row>
-    <row r="126" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="372" t="s">
+      <c r="G127" s="30"/>
+    </row>
+    <row r="128" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="371" t="s">
         <v>351</v>
       </c>
-      <c r="B126" s="373"/>
-      <c r="C126" s="22"/>
-      <c r="D126" s="360">
+      <c r="B128" s="372"/>
+      <c r="C128" s="22"/>
+      <c r="D128" s="360">
         <v>285600.08</v>
       </c>
-      <c r="E126" s="242" t="s">
+      <c r="E128" s="242" t="s">
         <v>469</v>
       </c>
-      <c r="F126" s="30">
+      <c r="F128" s="30">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="G126" s="30"/>
-    </row>
-    <row r="127" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="370" t="s">
+      <c r="G128" s="30"/>
+    </row>
+    <row r="129" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="407" t="s">
         <v>426</v>
       </c>
-      <c r="B127" s="371"/>
-      <c r="C127" s="22"/>
-      <c r="D127" s="360">
-        <v>1314489</v>
-      </c>
-      <c r="E127" s="78" t="s">
-        <v>335</v>
-      </c>
-      <c r="F127" s="30"/>
-      <c r="G127" s="30"/>
-    </row>
-    <row r="128" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="370" t="s">
-        <v>428</v>
-      </c>
-      <c r="B128" s="371"/>
-      <c r="C128" s="22"/>
-      <c r="D128" s="360">
-        <v>465749</v>
-      </c>
-      <c r="E128" s="78" t="str">
-        <f>E127</f>
-        <v>Transf 10/08</v>
-      </c>
-      <c r="F128" s="30"/>
-      <c r="G128" s="30"/>
-    </row>
-    <row r="129" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="370" t="s">
-        <v>427</v>
-      </c>
-      <c r="B129" s="371"/>
+      <c r="B129" s="408"/>
       <c r="C129" s="22"/>
       <c r="D129" s="360">
-        <v>126745</v>
-      </c>
-      <c r="E129" s="78" t="str">
-        <f>E128</f>
-        <v>Transf 10/08</v>
+        <v>1314489</v>
+      </c>
+      <c r="E129" s="78" t="s">
+        <v>335</v>
       </c>
       <c r="F129" s="30"/>
       <c r="G129" s="30"/>
     </row>
-    <row r="130" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="370" t="s">
-        <v>450</v>
-      </c>
-      <c r="B130" s="371"/>
+    <row r="130" spans="1:7" ht="36.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="407" t="s">
+        <v>428</v>
+      </c>
+      <c r="B130" s="408"/>
       <c r="C130" s="22"/>
       <c r="D130" s="360">
-        <v>94353</v>
+        <v>465749</v>
       </c>
       <c r="E130" s="78" t="str">
         <f>E129</f>
         <v>Transf 10/08</v>
       </c>
-      <c r="F130" s="250">
-        <f>SUM(D127:D130)</f>
-        <v>2001336</v>
-      </c>
+      <c r="F130" s="30"/>
       <c r="G130" s="30"/>
     </row>
-    <row r="131" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="370" t="s">
-        <v>189</v>
-      </c>
-      <c r="B131" s="371"/>
+    <row r="131" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="407" t="s">
+        <v>427</v>
+      </c>
+      <c r="B131" s="408"/>
       <c r="C131" s="22"/>
       <c r="D131" s="360">
-        <v>31266.93</v>
-      </c>
-      <c r="E131" s="52" t="s">
-        <v>268</v>
+        <v>126745</v>
+      </c>
+      <c r="E131" s="78" t="str">
+        <f>E130</f>
+        <v>Transf 10/08</v>
       </c>
       <c r="F131" s="30"/>
       <c r="G131" s="30"/>
     </row>
-    <row r="132" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="370" t="s">
-        <v>340</v>
-      </c>
-      <c r="B132" s="371"/>
+    <row r="132" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="407" t="s">
+        <v>450</v>
+      </c>
+      <c r="B132" s="408"/>
       <c r="C132" s="22"/>
       <c r="D132" s="360">
-        <v>9137.2099999999991</v>
-      </c>
-      <c r="E132" s="52" t="s">
+        <v>94353</v>
+      </c>
+      <c r="E132" s="78" t="str">
+        <f>E131</f>
+        <v>Transf 10/08</v>
+      </c>
+      <c r="F132" s="250">
+        <f>SUM(D129:D132)</f>
+        <v>2001336</v>
+      </c>
+      <c r="G132" s="30"/>
+    </row>
+    <row r="133" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="407" t="s">
+        <v>189</v>
+      </c>
+      <c r="B133" s="408"/>
+      <c r="C133" s="22"/>
+      <c r="D133" s="360">
+        <v>31266.93</v>
+      </c>
+      <c r="E133" s="52" t="s">
         <v>268</v>
-      </c>
-      <c r="F132" s="30"/>
-      <c r="G132" s="30" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A133" s="107" t="s">
-        <v>4</v>
-      </c>
-      <c r="B133" s="40"/>
-      <c r="C133" s="40"/>
-      <c r="D133" s="40"/>
-      <c r="E133" s="82">
-        <f>SUM(D115:D132)</f>
-        <v>7887432.5499999998</v>
       </c>
       <c r="F133" s="30"/>
       <c r="G133" s="30"/>
     </row>
-    <row r="134" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="30"/>
-      <c r="B134" s="30"/>
-      <c r="C134" s="30"/>
-      <c r="D134" s="30"/>
-      <c r="E134" s="30"/>
+    <row r="134" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="407" t="s">
+        <v>340</v>
+      </c>
+      <c r="B134" s="408"/>
+      <c r="C134" s="22"/>
+      <c r="D134" s="360">
+        <v>9137.2099999999991</v>
+      </c>
+      <c r="E134" s="52" t="s">
+        <v>268</v>
+      </c>
       <c r="F134" s="30"/>
-      <c r="G134" s="30"/>
+      <c r="G134" s="30" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A135" s="108" t="s">
-        <v>21</v>
-      </c>
-      <c r="B135" s="109"/>
-      <c r="C135" s="110"/>
-      <c r="D135" s="218"/>
-      <c r="E135" s="48"/>
+      <c r="A135" s="107" t="s">
+        <v>4</v>
+      </c>
+      <c r="B135" s="40"/>
+      <c r="C135" s="40"/>
+      <c r="D135" s="40"/>
+      <c r="E135" s="82">
+        <f>SUM(D117:D134)</f>
+        <v>7887432.5499999998</v>
+      </c>
       <c r="F135" s="30"/>
       <c r="G135" s="30"/>
     </row>
-    <row r="136" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="370" t="s">
-        <v>396</v>
-      </c>
-      <c r="B136" s="371"/>
-      <c r="C136" s="22"/>
-      <c r="D136" s="364">
-        <v>9914839.9499999993</v>
-      </c>
-      <c r="E136" s="78" t="s">
-        <v>412</v>
-      </c>
+    <row r="136" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="30"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="30"/>
+      <c r="D136" s="30"/>
+      <c r="E136" s="30"/>
       <c r="F136" s="30"/>
       <c r="G136" s="30"/>
     </row>
-    <row r="137" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="355" t="s">
-        <v>4</v>
-      </c>
-      <c r="B137" s="356"/>
-      <c r="C137" s="356"/>
-      <c r="D137" s="357"/>
-      <c r="E137" s="358">
-        <f>SUM(D136:D136)</f>
-        <v>9914839.9499999993</v>
-      </c>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A137" s="108" t="s">
+        <v>21</v>
+      </c>
+      <c r="B137" s="109"/>
+      <c r="C137" s="110"/>
+      <c r="D137" s="218"/>
+      <c r="E137" s="48"/>
       <c r="F137" s="30"/>
       <c r="G137" s="30"/>
     </row>
-    <row r="138" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="30"/>
-      <c r="B138" s="30"/>
-      <c r="C138" s="30"/>
-      <c r="D138" s="30"/>
-      <c r="E138" s="30"/>
+    <row r="138" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="407" t="s">
+        <v>396</v>
+      </c>
+      <c r="B138" s="408"/>
+      <c r="C138" s="22"/>
+      <c r="D138" s="364">
+        <v>9914839.9499999993</v>
+      </c>
+      <c r="E138" s="78" t="s">
+        <v>412</v>
+      </c>
       <c r="F138" s="30"/>
       <c r="G138" s="30"/>
     </row>
-    <row r="139" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="30"/>
-      <c r="B139" s="30"/>
-      <c r="C139" s="30"/>
-      <c r="D139" s="30"/>
-      <c r="E139" s="30"/>
+    <row r="139" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="355" t="s">
+        <v>4</v>
+      </c>
+      <c r="B139" s="356"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="358">
+        <f>SUM(D138:D138)</f>
+        <v>9914839.9499999993</v>
+      </c>
       <c r="F139" s="30"/>
       <c r="G139" s="30"/>
     </row>
-    <row r="140" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="30"/>
       <c r="B140" s="30"/>
       <c r="C140" s="30"/>
@@ -5479,17 +5509,12 @@
       <c r="F140" s="30"/>
       <c r="G140" s="30"/>
     </row>
-    <row r="141" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="111" t="s">
-        <v>13</v>
-      </c>
-      <c r="B141" s="112"/>
-      <c r="C141" s="113"/>
-      <c r="D141" s="113"/>
-      <c r="E141" s="114">
-        <f>E137</f>
-        <v>9914839.9499999993</v>
-      </c>
+    <row r="141" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="30"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="30"/>
+      <c r="D141" s="30"/>
+      <c r="E141" s="30"/>
       <c r="F141" s="30"/>
       <c r="G141" s="30"/>
     </row>
@@ -5502,527 +5527,526 @@
       <c r="F142" s="30"/>
       <c r="G142" s="30"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A143" s="115" t="s">
-        <v>187</v>
-      </c>
-      <c r="B143" s="116"/>
-      <c r="C143" s="117"/>
-      <c r="D143" s="53"/>
-      <c r="E143" s="54"/>
+    <row r="143" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="111" t="s">
+        <v>13</v>
+      </c>
+      <c r="B143" s="112"/>
+      <c r="C143" s="113"/>
+      <c r="D143" s="113"/>
+      <c r="E143" s="114">
+        <f>E139</f>
+        <v>9914839.9499999993</v>
+      </c>
       <c r="F143" s="30"/>
       <c r="G143" s="30"/>
     </row>
-    <row r="144" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="378" t="s">
+    <row r="144" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="30"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="30"/>
+      <c r="D144" s="30"/>
+      <c r="E144" s="30"/>
+      <c r="F144" s="30"/>
+      <c r="G144" s="30"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A145" s="115" t="s">
+        <v>187</v>
+      </c>
+      <c r="B145" s="116"/>
+      <c r="C145" s="117"/>
+      <c r="D145" s="53"/>
+      <c r="E145" s="54"/>
+      <c r="F145" s="30"/>
+      <c r="G145" s="30"/>
+    </row>
+    <row r="146" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="402" t="s">
         <v>420</v>
       </c>
-      <c r="B144" s="378"/>
-      <c r="C144" s="22"/>
-      <c r="D144" s="360">
+      <c r="B146" s="402"/>
+      <c r="C146" s="22"/>
+      <c r="D146" s="360">
         <f>2947450-2450000</f>
         <v>497450</v>
       </c>
-      <c r="E144" s="26" t="str">
+      <c r="E146" s="26" t="str">
         <f>E28</f>
         <v>Transf 03/09</v>
       </c>
-      <c r="F144" s="250"/>
-      <c r="G144" s="250"/>
-    </row>
-    <row r="145" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="354" t="s">
+      <c r="F146" s="250"/>
+      <c r="G146" s="250"/>
+    </row>
+    <row r="147" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="354" t="s">
         <v>447</v>
       </c>
-      <c r="B145" s="257"/>
-      <c r="C145" s="22"/>
-      <c r="D145" s="360">
+      <c r="B147" s="257"/>
+      <c r="C147" s="22"/>
+      <c r="D147" s="360">
         <v>122554.24000000001</v>
       </c>
-      <c r="E145" s="26" t="str">
+      <c r="E147" s="26" t="str">
         <f>E44</f>
         <v>Transf 07/09</v>
       </c>
-      <c r="F145" s="250"/>
-      <c r="G145" s="250"/>
-    </row>
-    <row r="146" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="354" t="s">
+      <c r="F147" s="250"/>
+      <c r="G147" s="250"/>
+    </row>
+    <row r="148" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="354" t="s">
         <v>446</v>
       </c>
-      <c r="B146" s="257"/>
-      <c r="C146" s="22"/>
-      <c r="D146" s="360">
+      <c r="B148" s="257"/>
+      <c r="C148" s="22"/>
+      <c r="D148" s="360">
         <v>91915.68</v>
       </c>
-      <c r="E146" s="26" t="str">
-        <f>E145</f>
+      <c r="E148" s="26" t="str">
+        <f>E147</f>
         <v>Transf 07/09</v>
       </c>
-      <c r="F146" s="250"/>
-      <c r="G146" s="250"/>
-    </row>
-    <row r="147" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="372" t="s">
+      <c r="F148" s="250"/>
+      <c r="G148" s="250"/>
+    </row>
+    <row r="149" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="371" t="s">
         <v>445</v>
       </c>
-      <c r="B147" s="373"/>
-      <c r="C147" s="97"/>
-      <c r="D147" s="360">
+      <c r="B149" s="372"/>
+      <c r="C149" s="97"/>
+      <c r="D149" s="360">
         <v>107234.96</v>
       </c>
-      <c r="E147" s="26" t="str">
-        <f>E146</f>
+      <c r="E149" s="26" t="str">
+        <f>E148</f>
         <v>Transf 07/09</v>
       </c>
-      <c r="F147" s="30"/>
-      <c r="G147" s="254"/>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A148" s="201" t="s">
+      <c r="F149" s="30"/>
+      <c r="G149" s="254"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A150" s="201" t="s">
         <v>4</v>
       </c>
-      <c r="B148" s="202"/>
-      <c r="C148" s="202"/>
-      <c r="D148" s="132"/>
-      <c r="E148" s="203">
-        <f>SUM(D144:D147)</f>
+      <c r="B150" s="202"/>
+      <c r="C150" s="202"/>
+      <c r="D150" s="132"/>
+      <c r="E150" s="203">
+        <f>SUM(D146:D149)</f>
         <v>819154.87999999989</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A149" s="30"/>
-      <c r="B149" s="30"/>
-      <c r="C149" s="30"/>
-      <c r="D149" s="30"/>
-      <c r="E149" s="30"/>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A150" s="30"/>
-      <c r="B150" s="30"/>
-      <c r="C150" s="30"/>
-      <c r="D150" s="30"/>
-      <c r="E150" s="30"/>
-    </row>
-    <row r="151" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="30"/>
       <c r="B151" s="30"/>
       <c r="C151" s="30"/>
       <c r="D151" s="30"/>
       <c r="E151" s="30"/>
     </row>
-    <row r="152" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="204" t="s">
-        <v>188</v>
-      </c>
-      <c r="B152" s="205"/>
-      <c r="C152" s="206"/>
-      <c r="D152" s="206"/>
-      <c r="E152" s="207">
-        <f>E148</f>
-        <v>819154.87999999989</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A152" s="30"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="30"/>
+      <c r="D152" s="30"/>
+      <c r="E152" s="30"/>
+    </row>
+    <row r="153" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="30"/>
       <c r="B153" s="30"/>
       <c r="C153" s="30"/>
       <c r="D153" s="30"/>
       <c r="E153" s="30"/>
     </row>
-    <row r="154" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="30"/>
-      <c r="B154" s="30"/>
-      <c r="C154" s="30"/>
-      <c r="D154" s="30"/>
-      <c r="E154" s="30"/>
-    </row>
-    <row r="155" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="208" t="s">
-        <v>180</v>
-      </c>
-      <c r="B155" s="209">
-        <f>E111</f>
-        <v>123129661.33999999</v>
-      </c>
+    <row r="154" spans="1:7" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A154" s="204" t="s">
+        <v>188</v>
+      </c>
+      <c r="B154" s="205"/>
+      <c r="C154" s="206"/>
+      <c r="D154" s="206"/>
+      <c r="E154" s="207">
+        <f>E150</f>
+        <v>819154.87999999989</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
       <c r="C155" s="30"/>
       <c r="D155" s="30"/>
       <c r="E155" s="30"/>
     </row>
     <row r="156" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="208" t="s">
-        <v>21</v>
-      </c>
-      <c r="B156" s="209">
-        <f>E141</f>
-        <v>9914839.9499999993</v>
-      </c>
+      <c r="A156" s="30"/>
+      <c r="B156" s="30"/>
       <c r="C156" s="30"/>
       <c r="D156" s="30"/>
       <c r="E156" s="30"/>
     </row>
     <row r="157" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="210" t="s">
-        <v>151</v>
-      </c>
-      <c r="B157" s="211">
-        <f>E133</f>
-        <v>7887432.5499999998</v>
+      <c r="A157" s="208" t="s">
+        <v>180</v>
+      </c>
+      <c r="B157" s="209">
+        <f>E113</f>
+        <v>127016241.33999999</v>
       </c>
       <c r="C157" s="30"/>
       <c r="D157" s="30"/>
       <c r="E157" s="30"/>
     </row>
-    <row r="158" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="212" t="s">
-        <v>226</v>
-      </c>
-      <c r="B158" s="211">
-        <f>B157+B155</f>
-        <v>131017093.88999999</v>
+    <row r="158" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A158" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="B158" s="209">
+        <f>E143</f>
+        <v>9914839.9499999993</v>
       </c>
       <c r="C158" s="30"/>
       <c r="D158" s="30"/>
       <c r="E158" s="30"/>
     </row>
-    <row r="159" spans="1:7" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="261" t="s">
-        <v>331</v>
+    <row r="159" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="210" t="s">
+        <v>151</v>
       </c>
       <c r="B159" s="211">
-        <f>SUM(B155:B157)</f>
-        <v>140931933.84</v>
+        <f>E135</f>
+        <v>7887432.5499999998</v>
       </c>
       <c r="C159" s="30"/>
       <c r="D159" s="30"/>
       <c r="E159" s="30"/>
     </row>
-    <row r="160" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A160" s="212" t="s">
+        <v>226</v>
+      </c>
+      <c r="B160" s="211">
+        <f>B159+B157</f>
+        <v>134903673.88999999</v>
+      </c>
       <c r="C160" s="30"/>
       <c r="D160" s="30"/>
       <c r="E160" s="30"/>
     </row>
-    <row r="161" spans="1:6" ht="54.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="261" t="s">
+        <v>331</v>
+      </c>
+      <c r="B161" s="211">
+        <f>SUM(B157:B159)</f>
+        <v>144818513.84</v>
+      </c>
       <c r="C161" s="30"/>
       <c r="D161" s="30"/>
       <c r="E161" s="30"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" s="127" t="s">
+    <row r="162" spans="1:6" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C162" s="30"/>
+      <c r="D162" s="30"/>
+      <c r="E162" s="30"/>
+    </row>
+    <row r="163" spans="1:6" ht="54.75" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C163" s="30"/>
+      <c r="D163" s="30"/>
+      <c r="E163" s="30"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="127" t="s">
         <v>233</v>
       </c>
-      <c r="B162" s="118"/>
-      <c r="C162" s="5"/>
-      <c r="D162" s="30"/>
-    </row>
-    <row r="163" spans="1:6" s="145" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="142" t="s">
+      <c r="B164" s="118"/>
+      <c r="C164" s="5"/>
+      <c r="D164" s="30"/>
+    </row>
+    <row r="165" spans="1:6" s="145" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="142" t="s">
         <v>229</v>
       </c>
-      <c r="B163" s="143">
+      <c r="B165" s="143">
         <v>26580407.379999999</v>
       </c>
-      <c r="C163" s="144"/>
-      <c r="D163" s="283"/>
-      <c r="E163" s="146"/>
-    </row>
-    <row r="164" spans="1:6" s="145" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="147" t="s">
+      <c r="C165" s="144"/>
+      <c r="D165" s="283"/>
+      <c r="E165" s="146"/>
+    </row>
+    <row r="166" spans="1:6" s="145" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="147" t="s">
         <v>230</v>
       </c>
-      <c r="B164" s="148">
+      <c r="B166" s="148">
         <f>PRORRATEO!F161</f>
         <v>110540945.85999997</v>
       </c>
-      <c r="C164" s="149"/>
-      <c r="D164" s="283"/>
-    </row>
-    <row r="165" spans="1:6" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="7" t="s">
+      <c r="C166" s="149"/>
+      <c r="D166" s="283"/>
+    </row>
+    <row r="167" spans="1:6" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A167" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="B165" s="150">
-        <v>0</v>
-      </c>
-      <c r="C165" s="149"/>
-      <c r="D165" s="284"/>
-    </row>
-    <row r="166" spans="1:6" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="7" t="str">
-        <f>A205</f>
-        <v>Rescate 03/08</v>
-      </c>
-      <c r="B166" s="279">
-        <v>0</v>
-      </c>
-      <c r="C166" s="149"/>
-      <c r="D166" s="284"/>
-    </row>
-    <row r="167" spans="1:6" s="145" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="B167" s="279">
-        <f>B214</f>
-        <v>751000</v>
+      <c r="B167" s="150">
+        <v>0</v>
       </c>
       <c r="C167" s="149"/>
       <c r="D167" s="284"/>
     </row>
-    <row r="168" spans="1:6" s="145" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="130" t="s">
-        <v>292</v>
-      </c>
-      <c r="B168" s="150">
-        <f>-B189</f>
+    <row r="168" spans="1:6" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="7" t="str">
+        <f>A209</f>
+        <v>Rescate 03/08</v>
+      </c>
+      <c r="B168" s="279">
         <v>0</v>
       </c>
       <c r="C168" s="149"/>
       <c r="D168" s="284"/>
     </row>
-    <row r="169" spans="1:6" s="145" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="130" t="s">
-        <v>481</v>
-      </c>
-      <c r="B169" s="150">
-        <v>-763100</v>
+    <row r="169" spans="1:6" s="145" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A169" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="B169" s="279">
+        <f>B218</f>
+        <v>751000</v>
       </c>
       <c r="C169" s="149"/>
       <c r="D169" s="284"/>
     </row>
     <row r="170" spans="1:6" s="145" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="130" t="s">
-        <v>482</v>
+        <v>292</v>
       </c>
       <c r="B170" s="150">
-        <v>-21321</v>
+        <f>-B191</f>
+        <v>0</v>
       </c>
       <c r="C170" s="149"/>
       <c r="D170" s="284"/>
     </row>
-    <row r="171" spans="1:6" s="145" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="32" t="s">
-        <v>480</v>
+    <row r="171" spans="1:6" s="145" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="130" t="s">
+        <v>481</v>
       </c>
       <c r="B171" s="150">
-        <v>-799419</v>
+        <v>-763100</v>
       </c>
       <c r="C171" s="149"/>
       <c r="D171" s="284"/>
     </row>
-    <row r="172" spans="1:6" s="145" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="7" t="s">
-        <v>321</v>
+    <row r="172" spans="1:6" s="145" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A172" s="130" t="s">
+        <v>482</v>
       </c>
       <c r="B172" s="150">
-        <f>-B182</f>
-        <v>-1098403.25</v>
+        <v>-21321</v>
       </c>
       <c r="C172" s="149"/>
       <c r="D172" s="284"/>
     </row>
-    <row r="173" spans="1:6" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6" s="145" customFormat="1" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="32" t="s">
+        <v>480</v>
+      </c>
+      <c r="B173" s="150">
+        <v>-799419</v>
+      </c>
+      <c r="C173" s="149"/>
+      <c r="D173" s="284"/>
+    </row>
+    <row r="174" spans="1:6" s="145" customFormat="1" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B174" s="150">
+        <f>-B184</f>
+        <v>-1098403.25</v>
+      </c>
+      <c r="C174" s="149"/>
+      <c r="D174" s="284"/>
+    </row>
+    <row r="175" spans="1:6" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A175" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="B173" s="150">
-        <f>-E152</f>
+      <c r="B175" s="150">
+        <f>-E154</f>
         <v>-819154.87999999989</v>
       </c>
-      <c r="C173" s="149"/>
-      <c r="D173" s="283"/>
-      <c r="F173" s="151"/>
-    </row>
-    <row r="174" spans="1:6" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B174" s="150">
-        <f>-E133</f>
-        <v>-7887432.5499999998</v>
-      </c>
-      <c r="C174" s="149"/>
-      <c r="D174" s="285"/>
-    </row>
-    <row r="175" spans="1:6" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B175" s="150">
-        <f>-E111</f>
-        <v>-123129661.33999999</v>
-      </c>
       <c r="C175" s="149"/>
-      <c r="D175" s="286"/>
-      <c r="E175" s="152"/>
-      <c r="F175" s="224"/>
+      <c r="D175" s="283"/>
+      <c r="F175" s="151"/>
     </row>
     <row r="176" spans="1:6" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B176" s="150">
+        <f>-E135</f>
+        <v>-7887432.5499999998</v>
+      </c>
+      <c r="C176" s="149"/>
+      <c r="D176" s="285"/>
+    </row>
+    <row r="177" spans="1:7" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B177" s="150">
+        <f>-E113</f>
+        <v>-127016241.33999999</v>
+      </c>
+      <c r="C177" s="149"/>
+      <c r="D177" s="286"/>
+      <c r="E177" s="152"/>
+      <c r="F177" s="224"/>
+    </row>
+    <row r="178" spans="1:7" s="145" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="B176" s="150">
-        <f>-E141</f>
+      <c r="B178" s="150">
+        <f>-E143</f>
         <v>-9914839.9499999993</v>
       </c>
-      <c r="C176" s="149"/>
-      <c r="D176" s="283"/>
-      <c r="E176" s="152"/>
-      <c r="F176" s="224"/>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A177" s="128" t="s">
+      <c r="C178" s="149"/>
+      <c r="D178" s="283"/>
+      <c r="E178" s="152"/>
+      <c r="F178" s="224"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A179" s="128" t="s">
         <v>4</v>
       </c>
-      <c r="B177" s="36">
-        <f>SUM(B163:B176)</f>
-        <v>-6560978.7300000004</v>
-      </c>
-      <c r="C177" s="6"/>
-      <c r="D177" s="250"/>
-      <c r="E177" s="37"/>
-      <c r="F177" s="37"/>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A178" s="129"/>
-      <c r="B178" s="11"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="250"/>
-      <c r="E178" s="34"/>
-      <c r="F178" s="74"/>
-    </row>
-    <row r="179" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="129"/>
-      <c r="B179" s="11"/>
+      <c r="B179" s="36">
+        <f>SUM(B165:B178)</f>
+        <v>-10447558.73</v>
+      </c>
       <c r="C179" s="6"/>
       <c r="D179" s="250"/>
-      <c r="E179" s="34"/>
-      <c r="F179" s="74"/>
+      <c r="E179" s="37"/>
+      <c r="F179" s="37"/>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A180" s="381" t="s">
-        <v>322</v>
-      </c>
-      <c r="B180" s="382"/>
+      <c r="A180" s="129"/>
+      <c r="B180" s="11"/>
       <c r="C180" s="6"/>
       <c r="D180" s="250"/>
       <c r="E180" s="34"/>
       <c r="F180" s="74"/>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A181" s="123" t="s">
-        <v>291</v>
-      </c>
-      <c r="B181" s="124">
-        <v>6414557.6699999999</v>
-      </c>
+    <row r="181" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="129"/>
+      <c r="B181" s="11"/>
       <c r="C181" s="6"/>
       <c r="D181" s="250"/>
       <c r="E181" s="34"/>
       <c r="F181" s="74"/>
     </row>
-    <row r="182" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="227" t="s">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A182" s="405" t="s">
+        <v>322</v>
+      </c>
+      <c r="B182" s="406"/>
+      <c r="C182" s="6"/>
+      <c r="D182" s="250"/>
+      <c r="E182" s="34"/>
+      <c r="F182" s="74"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A183" s="123" t="s">
+        <v>291</v>
+      </c>
+      <c r="B183" s="124">
+        <v>6414557.6699999999</v>
+      </c>
+      <c r="C183" s="6"/>
+      <c r="D183" s="250"/>
+      <c r="E183" s="34"/>
+      <c r="F183" s="74"/>
+    </row>
+    <row r="184" spans="1:7" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="227" t="s">
         <v>323</v>
       </c>
-      <c r="B182" s="187">
+      <c r="B184" s="187">
         <f>2196806.5/2</f>
         <v>1098403.25</v>
-      </c>
-      <c r="C182" s="6"/>
-      <c r="D182" s="13"/>
-      <c r="E182" s="34"/>
-      <c r="F182" s="74"/>
-    </row>
-    <row r="183" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="123"/>
-      <c r="B183" s="124"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="13"/>
-      <c r="E183" s="34"/>
-      <c r="F183" s="74"/>
-    </row>
-    <row r="184" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="228" t="s">
-        <v>4</v>
-      </c>
-      <c r="B184" s="229">
-        <f>SUM(B181:B183)</f>
-        <v>7512960.9199999999</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="13"/>
       <c r="E184" s="34"/>
       <c r="F184" s="74"/>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A185" s="129"/>
-      <c r="B185" s="11"/>
+    <row r="185" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="123"/>
+      <c r="B185" s="124"/>
       <c r="C185" s="6"/>
       <c r="D185" s="13"/>
       <c r="E185" s="34"/>
       <c r="F185" s="74"/>
     </row>
     <row r="186" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="129"/>
-      <c r="B186" s="11"/>
+      <c r="A186" s="228" t="s">
+        <v>4</v>
+      </c>
+      <c r="B186" s="229">
+        <f>SUM(B183:B185)</f>
+        <v>7512960.9199999999</v>
+      </c>
       <c r="C186" s="6"/>
       <c r="D186" s="13"/>
       <c r="E186" s="34"/>
       <c r="F186" s="74"/>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A187" s="379" t="s">
-        <v>290</v>
-      </c>
-      <c r="B187" s="380"/>
+      <c r="A187" s="129"/>
+      <c r="B187" s="11"/>
       <c r="C187" s="6"/>
       <c r="D187" s="13"/>
       <c r="E187" s="34"/>
       <c r="F187" s="74"/>
-      <c r="G187" s="225"/>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A188" s="123" t="s">
-        <v>291</v>
-      </c>
-      <c r="B188" s="124">
-        <v>4607864.5312480005</v>
-      </c>
+    </row>
+    <row r="188" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="129"/>
+      <c r="B188" s="11"/>
       <c r="C188" s="6"/>
       <c r="D188" s="13"/>
       <c r="E188" s="34"/>
       <c r="F188" s="74"/>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A189" s="123" t="s">
-        <v>292</v>
-      </c>
-      <c r="B189" s="187">
-        <v>0</v>
-      </c>
+      <c r="A189" s="403" t="s">
+        <v>290</v>
+      </c>
+      <c r="B189" s="404"/>
       <c r="C189" s="6"/>
       <c r="D189" s="13"/>
       <c r="E189" s="34"/>
       <c r="F189" s="74"/>
-    </row>
-    <row r="190" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="227" t="s">
-        <v>470</v>
-      </c>
-      <c r="B190" s="366">
-        <v>-91394.2</v>
+      <c r="G189" s="225"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" s="123" t="s">
+        <v>291</v>
+      </c>
+      <c r="B190" s="124">
+        <v>4607864.5312480005</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="13"/>
       <c r="E190" s="34"/>
       <c r="F190" s="74"/>
     </row>
-    <row r="191" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="123" t="s">
-        <v>330</v>
-      </c>
-      <c r="B191" s="124">
+        <v>292</v>
+      </c>
+      <c r="B191" s="187">
         <v>0</v>
       </c>
       <c r="C191" s="6"/>
@@ -6030,13 +6054,12 @@
       <c r="E191" s="34"/>
       <c r="F191" s="74"/>
     </row>
-    <row r="192" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="125" t="s">
-        <v>4</v>
-      </c>
-      <c r="B192" s="126">
-        <f>SUM(B188:B191)</f>
-        <v>4516470.3312480003</v>
+    <row r="192" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="227" t="s">
+        <v>470</v>
+      </c>
+      <c r="B192" s="366">
+        <v>-91394.2</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="13"/>
@@ -6044,63 +6067,64 @@
       <c r="F192" s="74"/>
     </row>
     <row r="193" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="121"/>
-      <c r="B193" s="122"/>
+      <c r="A193" s="123" t="s">
+        <v>330</v>
+      </c>
+      <c r="B193" s="124">
+        <v>0</v>
+      </c>
       <c r="C193" s="6"/>
       <c r="D193" s="13"/>
       <c r="E193" s="34"/>
       <c r="F193" s="74"/>
     </row>
-    <row r="194" spans="1:15" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="137" t="s">
-        <v>325</v>
-      </c>
-      <c r="B194" s="136">
-        <f>B192+B177+B184</f>
-        <v>5468452.5212479997</v>
+    <row r="194" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A194" s="125" t="s">
+        <v>4</v>
+      </c>
+      <c r="B194" s="126">
+        <f>SUM(B190:B193)</f>
+        <v>4516470.3312480003</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="13"/>
       <c r="E194" s="34"/>
       <c r="F194" s="74"/>
-      <c r="G194" s="35"/>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B195" s="11"/>
+    </row>
+    <row r="195" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A195" s="121"/>
+      <c r="B195" s="122"/>
       <c r="C195" s="6"/>
       <c r="D195" s="13"/>
       <c r="E195" s="34"/>
       <c r="F195" s="74"/>
     </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A196" s="69" t="s">
-        <v>232</v>
-      </c>
-      <c r="B196" s="70"/>
+    <row r="196" spans="1:15" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A196" s="137" t="s">
+        <v>325</v>
+      </c>
+      <c r="B196" s="136">
+        <f>B194+B179+B186</f>
+        <v>1581872.5212479997</v>
+      </c>
       <c r="C196" s="6"/>
       <c r="D196" s="13"/>
       <c r="E196" s="34"/>
-      <c r="F196" s="35"/>
-    </row>
-    <row r="197" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="87" t="s">
-        <v>291</v>
-      </c>
-      <c r="B197" s="131">
-        <v>-115227.5</v>
-      </c>
+      <c r="F196" s="74"/>
+      <c r="G196" s="35"/>
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B197" s="11"/>
       <c r="C197" s="6"/>
       <c r="D197" s="13"/>
       <c r="E197" s="34"/>
-      <c r="F197" s="35"/>
-    </row>
-    <row r="198" spans="1:15" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="87" t="s">
-        <v>437</v>
-      </c>
-      <c r="B198" s="360">
-        <v>-140427.84</v>
-      </c>
+      <c r="F197" s="74"/>
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A198" s="69" t="s">
+        <v>232</v>
+      </c>
+      <c r="B198" s="70"/>
       <c r="C198" s="6"/>
       <c r="D198" s="13"/>
       <c r="E198" s="34"/>
@@ -6108,123 +6132,87 @@
     </row>
     <row r="199" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="B199" s="194"/>
+        <v>291</v>
+      </c>
+      <c r="B199" s="131">
+        <v>-115227.5</v>
+      </c>
       <c r="C199" s="6"/>
       <c r="D199" s="13"/>
       <c r="E199" s="34"/>
       <c r="F199" s="35"/>
     </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A200" s="69" t="s">
-        <v>4</v>
-      </c>
-      <c r="B200" s="70">
-        <f>SUM(B196:B199)</f>
-        <v>-255655.34</v>
+    <row r="200" spans="1:15" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="87" t="s">
+        <v>437</v>
+      </c>
+      <c r="B200" s="360">
+        <v>-140427.84</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="13"/>
       <c r="E200" s="34"/>
       <c r="F200" s="35"/>
     </row>
-    <row r="201" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B201" s="11"/>
+    <row r="201" spans="1:15" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="87" t="s">
+        <v>491</v>
+      </c>
+      <c r="B201" s="360">
+        <v>-7000</v>
+      </c>
       <c r="C201" s="6"/>
       <c r="D201" s="13"/>
       <c r="E201" s="34"/>
       <c r="F201" s="35"/>
     </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A202" s="119" t="s">
+    <row r="202" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="87" t="s">
+        <v>490</v>
+      </c>
+      <c r="B202" s="360">
+        <v>-34500</v>
+      </c>
+      <c r="C202" s="6"/>
+      <c r="D202" s="13"/>
+      <c r="E202" s="34"/>
+      <c r="F202" s="35"/>
+    </row>
+    <row r="203" spans="1:15" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="B203" s="194"/>
+      <c r="C203" s="6"/>
+      <c r="D203" s="13"/>
+      <c r="E203" s="34"/>
+      <c r="F203" s="35"/>
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A204" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="B204" s="70">
+        <f>SUM(B198:B203)</f>
+        <v>-297155.33999999997</v>
+      </c>
+      <c r="C204" s="6"/>
+      <c r="D204" s="13"/>
+      <c r="E204" s="34"/>
+      <c r="F204" s="35"/>
+    </row>
+    <row r="205" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B205" s="11"/>
+      <c r="C205" s="6"/>
+      <c r="D205" s="13"/>
+      <c r="E205" s="34"/>
+      <c r="F205" s="35"/>
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A206" s="119" t="s">
         <v>227</v>
       </c>
-      <c r="B202" s="65"/>
-      <c r="C202" s="6"/>
-      <c r="D202" s="73"/>
-      <c r="E202" s="134"/>
-      <c r="F202" s="135"/>
-      <c r="G202" s="33"/>
-      <c r="H202" s="33"/>
-      <c r="I202" s="33"/>
-      <c r="J202" s="33"/>
-      <c r="K202" s="33"/>
-      <c r="L202" s="33"/>
-      <c r="M202" s="33"/>
-      <c r="N202" s="33"/>
-      <c r="O202" s="33"/>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A203" s="67" t="s">
-        <v>329</v>
-      </c>
-      <c r="B203" s="68">
-        <v>106403918.55</v>
-      </c>
-      <c r="C203" s="6"/>
-      <c r="D203" s="73"/>
-      <c r="E203" s="134"/>
-      <c r="F203" s="135"/>
-      <c r="G203" s="33"/>
-      <c r="H203" s="33"/>
-      <c r="I203" s="33"/>
-      <c r="J203" s="33"/>
-      <c r="K203" s="33"/>
-      <c r="L203" s="33"/>
-      <c r="M203" s="33"/>
-      <c r="N203" s="33"/>
-      <c r="O203" s="33"/>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A204" s="67" t="s">
-        <v>347</v>
-      </c>
-      <c r="B204" s="68">
-        <v>0</v>
-      </c>
-      <c r="C204" s="6"/>
-      <c r="D204" s="73"/>
-      <c r="E204" s="134"/>
-      <c r="F204" s="135"/>
-      <c r="G204" s="33"/>
-      <c r="H204" s="33"/>
-      <c r="I204" s="33"/>
-      <c r="J204" s="33"/>
-      <c r="K204" s="33"/>
-      <c r="L204" s="33"/>
-      <c r="M204" s="33"/>
-      <c r="N204" s="33"/>
-      <c r="O204" s="33"/>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A205" s="67" t="s">
-        <v>337</v>
-      </c>
-      <c r="B205" s="260">
-        <v>0</v>
-      </c>
-      <c r="C205" s="6"/>
-      <c r="D205" s="73"/>
-      <c r="E205" s="134"/>
-      <c r="F205" s="135"/>
-      <c r="G205" s="33"/>
-      <c r="H205" s="33"/>
-      <c r="I205" s="33"/>
-      <c r="J205" s="33"/>
-      <c r="K205" s="33"/>
-      <c r="L205" s="33"/>
-      <c r="M205" s="33"/>
-      <c r="N205" s="33"/>
-      <c r="O205" s="33"/>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A206" s="67" t="s">
-        <v>333</v>
-      </c>
-      <c r="B206" s="68">
-        <v>0</v>
-      </c>
+      <c r="B206" s="65"/>
       <c r="C206" s="6"/>
       <c r="D206" s="73"/>
       <c r="E206" s="134"/>
@@ -6239,13 +6227,12 @@
       <c r="N206" s="33"/>
       <c r="O206" s="33"/>
     </row>
-    <row r="207" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="120" t="s">
-        <v>332</v>
-      </c>
-      <c r="B207" s="243">
-        <f>118020953.46</f>
-        <v>118020953.45999999</v>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A207" s="67" t="s">
+        <v>329</v>
+      </c>
+      <c r="B207" s="68">
+        <v>106403918.55</v>
       </c>
       <c r="C207" s="6"/>
       <c r="D207" s="73"/>
@@ -6262,7 +6249,12 @@
       <c r="O207" s="33"/>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B208" s="11"/>
+      <c r="A208" s="67" t="s">
+        <v>347</v>
+      </c>
+      <c r="B208" s="68">
+        <v>0</v>
+      </c>
       <c r="C208" s="6"/>
       <c r="D208" s="73"/>
       <c r="E208" s="134"/>
@@ -6277,84 +6269,189 @@
       <c r="N208" s="33"/>
       <c r="O208" s="33"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B209" s="11"/>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A209" s="67" t="s">
+        <v>337</v>
+      </c>
+      <c r="B209" s="260">
+        <v>0</v>
+      </c>
       <c r="C209" s="6"/>
-      <c r="D209" s="13"/>
-      <c r="E209" s="34"/>
-      <c r="F209" s="35"/>
-    </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B210" s="11"/>
+      <c r="D209" s="73"/>
+      <c r="E209" s="134"/>
+      <c r="F209" s="135"/>
+      <c r="G209" s="33"/>
+      <c r="H209" s="33"/>
+      <c r="I209" s="33"/>
+      <c r="J209" s="33"/>
+      <c r="K209" s="33"/>
+      <c r="L209" s="33"/>
+      <c r="M209" s="33"/>
+      <c r="N209" s="33"/>
+      <c r="O209" s="33"/>
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A210" s="67" t="s">
+        <v>333</v>
+      </c>
+      <c r="B210" s="68">
+        <v>0</v>
+      </c>
       <c r="C210" s="6"/>
-      <c r="D210" s="13"/>
-      <c r="E210" s="34"/>
-      <c r="F210" s="35"/>
-    </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A211" s="377" t="s">
+      <c r="D210" s="73"/>
+      <c r="E210" s="134"/>
+      <c r="F210" s="135"/>
+      <c r="G210" s="33"/>
+      <c r="H210" s="33"/>
+      <c r="I210" s="33"/>
+      <c r="J210" s="33"/>
+      <c r="K210" s="33"/>
+      <c r="L210" s="33"/>
+      <c r="M210" s="33"/>
+      <c r="N210" s="33"/>
+      <c r="O210" s="33"/>
+    </row>
+    <row r="211" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A211" s="120" t="s">
+        <v>332</v>
+      </c>
+      <c r="B211" s="243">
+        <f>118020953.46</f>
+        <v>118020953.45999999</v>
+      </c>
+      <c r="C211" s="6"/>
+      <c r="D211" s="73"/>
+      <c r="E211" s="134"/>
+      <c r="F211" s="135"/>
+      <c r="G211" s="33"/>
+      <c r="H211" s="33"/>
+      <c r="I211" s="33"/>
+      <c r="J211" s="33"/>
+      <c r="K211" s="33"/>
+      <c r="L211" s="33"/>
+      <c r="M211" s="33"/>
+      <c r="N211" s="33"/>
+      <c r="O211" s="33"/>
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B212" s="11"/>
+      <c r="C212" s="6"/>
+      <c r="D212" s="73"/>
+      <c r="E212" s="134"/>
+      <c r="F212" s="135"/>
+      <c r="G212" s="33"/>
+      <c r="H212" s="33"/>
+      <c r="I212" s="33"/>
+      <c r="J212" s="33"/>
+      <c r="K212" s="33"/>
+      <c r="L212" s="33"/>
+      <c r="M212" s="33"/>
+      <c r="N212" s="33"/>
+      <c r="O212" s="33"/>
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B213" s="11"/>
+      <c r="C213" s="6"/>
+      <c r="D213" s="13"/>
+      <c r="E213" s="34"/>
+      <c r="F213" s="35"/>
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B214" s="11"/>
+      <c r="C214" s="6"/>
+      <c r="D214" s="13"/>
+      <c r="E214" s="34"/>
+      <c r="F214" s="35"/>
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A215" s="401" t="s">
         <v>17</v>
       </c>
-      <c r="B211" s="377"/>
-      <c r="C211" s="377"/>
-    </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A212" s="377"/>
-      <c r="B212" s="377"/>
-      <c r="C212" s="377"/>
-    </row>
-    <row r="213" spans="1:13" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="63" t="s">
+      <c r="B215" s="401"/>
+      <c r="C215" s="401"/>
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A216" s="401"/>
+      <c r="B216" s="401"/>
+      <c r="C216" s="401"/>
+    </row>
+    <row r="217" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="63" t="s">
         <v>489</v>
       </c>
-      <c r="B213" s="39">
+      <c r="B217" s="39">
         <v>751000</v>
       </c>
-      <c r="C213" s="62"/>
-    </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A214" s="14" t="s">
+      <c r="C217" s="62"/>
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A218" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B214" s="31">
-        <f>SUM(B213:B213)</f>
+      <c r="B218" s="31">
+        <f>SUM(B217:B217)</f>
         <v>751000</v>
       </c>
-      <c r="C214" s="15"/>
-    </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M215" s="3"/>
+      <c r="C218" s="15"/>
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="M219" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="92">
+  <mergeCells count="94">
+    <mergeCell ref="A138:B138"/>
+    <mergeCell ref="A134:B134"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="A101:B101"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A128:B128"/>
+    <mergeCell ref="A118:B118"/>
+    <mergeCell ref="A119:B119"/>
+    <mergeCell ref="A120:B120"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A93:B93"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A95:B95"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="A96:B96"/>
     <mergeCell ref="A88:B88"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="A83:B83"/>
+    <mergeCell ref="A215:C216"/>
+    <mergeCell ref="A146:B146"/>
+    <mergeCell ref="A189:B189"/>
+    <mergeCell ref="A149:B149"/>
+    <mergeCell ref="A182:B182"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A102:B102"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A130:B130"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="A121:B121"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A105:B105"/>
+    <mergeCell ref="A126:B126"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="A125:B125"/>
     <mergeCell ref="A48:B48"/>
     <mergeCell ref="A38:B38"/>
     <mergeCell ref="A59:B59"/>
@@ -6368,57 +6465,34 @@
     <mergeCell ref="A50:B50"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A120:B120"/>
-    <mergeCell ref="A121:B121"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A125:B125"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A211:C212"/>
-    <mergeCell ref="A144:B144"/>
-    <mergeCell ref="A187:B187"/>
-    <mergeCell ref="A147:B147"/>
-    <mergeCell ref="A180:B180"/>
-    <mergeCell ref="A130:B130"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A73:C73"/>
     <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A119:B119"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A79:B79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A136:B136"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A126:B126"/>
-    <mergeCell ref="A116:B116"/>
-    <mergeCell ref="A117:B117"/>
-    <mergeCell ref="A118:B118"/>
-    <mergeCell ref="A115:B115"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A97:B97"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -6458,27 +6532,27 @@
     <row r="1" spans="1:24" ht="251.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
-      <c r="C1" s="421" t="s">
+      <c r="C1" s="420" t="s">
         <v>334</v>
       </c>
-      <c r="D1" s="422"/>
-      <c r="E1" s="422"/>
-      <c r="F1" s="422"/>
-      <c r="G1" s="422"/>
-      <c r="H1" s="422"/>
-      <c r="I1" s="422"/>
-      <c r="J1" s="422"/>
-      <c r="K1" s="422"/>
-      <c r="L1" s="422"/>
+      <c r="D1" s="421"/>
+      <c r="E1" s="421"/>
+      <c r="F1" s="421"/>
+      <c r="G1" s="421"/>
+      <c r="H1" s="421"/>
+      <c r="I1" s="421"/>
+      <c r="J1" s="421"/>
+      <c r="K1" s="421"/>
+      <c r="L1" s="421"/>
       <c r="M1" s="139"/>
-      <c r="N1" s="423" t="s">
+      <c r="N1" s="422" t="s">
         <v>306</v>
       </c>
-      <c r="O1" s="423"/>
-      <c r="P1" s="418">
+      <c r="O1" s="422"/>
+      <c r="P1" s="417">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="418"/>
+      <c r="Q1" s="417"/>
       <c r="R1" s="160"/>
       <c r="S1" s="4"/>
       <c r="T1" s="2"/>
@@ -6492,35 +6566,35 @@
     <row r="2" spans="1:24" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="420" t="s">
+      <c r="C2" s="419" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="420"/>
-      <c r="E2" s="420"/>
+      <c r="D2" s="419"/>
+      <c r="E2" s="419"/>
       <c r="F2" s="139"/>
-      <c r="G2" s="415">
+      <c r="G2" s="416">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="415"/>
+      <c r="H2" s="416"/>
       <c r="I2" s="139" t="s">
         <v>272</v>
       </c>
       <c r="J2" s="139"/>
-      <c r="K2" s="415">
+      <c r="K2" s="416">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="415"/>
+      <c r="L2" s="416"/>
       <c r="M2" s="220"/>
       <c r="N2" s="221" t="s">
         <v>258</v>
       </c>
       <c r="O2" s="220"/>
-      <c r="P2" s="419">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="419"/>
+      <c r="P2" s="418">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="418"/>
       <c r="R2" s="161"/>
       <c r="T2" s="2"/>
       <c r="U2" t="s">
@@ -6532,112 +6606,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="428" t="str">
+      <c r="A3" s="427" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  16/10, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="429"/>
-      <c r="C3" s="429"/>
-      <c r="D3" s="429"/>
-      <c r="E3" s="429"/>
-      <c r="F3" s="429"/>
-      <c r="G3" s="429"/>
-      <c r="H3" s="429"/>
-      <c r="I3" s="429"/>
-      <c r="J3" s="429"/>
-      <c r="K3" s="429"/>
-      <c r="L3" s="429"/>
-      <c r="M3" s="429"/>
-      <c r="N3" s="429"/>
-      <c r="O3" s="429"/>
-      <c r="P3" s="429"/>
-      <c r="Q3" s="429"/>
-      <c r="R3" s="429"/>
-      <c r="S3" s="429"/>
-      <c r="T3" s="430"/>
+      <c r="B3" s="428"/>
+      <c r="C3" s="428"/>
+      <c r="D3" s="428"/>
+      <c r="E3" s="428"/>
+      <c r="F3" s="428"/>
+      <c r="G3" s="428"/>
+      <c r="H3" s="428"/>
+      <c r="I3" s="428"/>
+      <c r="J3" s="428"/>
+      <c r="K3" s="428"/>
+      <c r="L3" s="428"/>
+      <c r="M3" s="428"/>
+      <c r="N3" s="428"/>
+      <c r="O3" s="428"/>
+      <c r="P3" s="428"/>
+      <c r="Q3" s="428"/>
+      <c r="R3" s="428"/>
+      <c r="S3" s="428"/>
+      <c r="T3" s="429"/>
       <c r="X3" s="37"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="431" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="433" t="s">
+      <c r="A4" s="430" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="432" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="433" t="s">
+      <c r="C4" s="432" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="433" t="s">
+      <c r="D4" s="432" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="416" t="s">
+      <c r="E4" s="409" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="433" t="s">
+      <c r="F4" s="432" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="435" t="s">
+      <c r="G4" s="434" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="416" t="s">
+      <c r="H4" s="409" t="s">
         <v>231</v>
       </c>
-      <c r="I4" s="416" t="s">
+      <c r="I4" s="409" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="416"/>
-      <c r="K4" s="416" t="s">
+      <c r="J4" s="409"/>
+      <c r="K4" s="409" t="s">
         <v>182</v>
       </c>
-      <c r="L4" s="416" t="s">
+      <c r="L4" s="409" t="s">
         <v>146</v>
       </c>
-      <c r="M4" s="416" t="s">
+      <c r="M4" s="409" t="s">
         <v>184</v>
       </c>
-      <c r="N4" s="416" t="s">
+      <c r="N4" s="409" t="s">
         <v>183</v>
       </c>
-      <c r="O4" s="416" t="s">
+      <c r="O4" s="409" t="s">
         <v>316</v>
       </c>
-      <c r="P4" s="424" t="s">
+      <c r="P4" s="423" t="s">
         <v>314</v>
       </c>
-      <c r="Q4" s="425"/>
-      <c r="R4" s="424" t="s">
+      <c r="Q4" s="424"/>
+      <c r="R4" s="423" t="s">
         <v>309</v>
       </c>
-      <c r="S4" s="425"/>
-      <c r="T4" s="416" t="s">
+      <c r="S4" s="424"/>
+      <c r="T4" s="409" t="s">
         <v>256</v>
       </c>
       <c r="U4" s="13"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="432"/>
-      <c r="B5" s="434"/>
-      <c r="C5" s="434"/>
-      <c r="D5" s="434"/>
-      <c r="E5" s="417"/>
-      <c r="F5" s="434"/>
-      <c r="G5" s="436"/>
-      <c r="H5" s="417"/>
-      <c r="I5" s="417"/>
-      <c r="J5" s="417"/>
-      <c r="K5" s="417"/>
-      <c r="L5" s="417"/>
-      <c r="M5" s="417"/>
-      <c r="N5" s="417"/>
-      <c r="O5" s="417"/>
-      <c r="P5" s="426" t="str">
+      <c r="A5" s="431"/>
+      <c r="B5" s="433"/>
+      <c r="C5" s="433"/>
+      <c r="D5" s="433"/>
+      <c r="E5" s="410"/>
+      <c r="F5" s="433"/>
+      <c r="G5" s="435"/>
+      <c r="H5" s="410"/>
+      <c r="I5" s="410"/>
+      <c r="J5" s="410"/>
+      <c r="K5" s="410"/>
+      <c r="L5" s="410"/>
+      <c r="M5" s="410"/>
+      <c r="N5" s="410"/>
+      <c r="O5" s="410"/>
+      <c r="P5" s="425" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  16/10</v>
       </c>
-      <c r="Q5" s="427"/>
-      <c r="R5" s="426"/>
-      <c r="S5" s="427"/>
-      <c r="T5" s="417"/>
+      <c r="Q5" s="426"/>
+      <c r="R5" s="425"/>
+      <c r="S5" s="426"/>
+      <c r="T5" s="410"/>
     </row>
     <row r="6" spans="1:24" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="180"/>
@@ -6690,11 +6764,11 @@
       <c r="O6" s="181">
         <v>0</v>
       </c>
-      <c r="P6" s="437">
+      <c r="P6" s="411">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>759748.01</v>
       </c>
-      <c r="Q6" s="438"/>
+      <c r="Q6" s="412"/>
       <c r="R6" s="222">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>782791.01</v>
@@ -6762,11 +6836,11 @@
       <c r="O7" s="181">
         <v>0</v>
       </c>
-      <c r="P7" s="439">
+      <c r="P7" s="413">
         <f t="shared" si="2"/>
         <v>2853424.02</v>
       </c>
-      <c r="Q7" s="440"/>
+      <c r="Q7" s="414"/>
       <c r="R7" s="222">
         <f t="shared" si="3"/>
         <v>2939968.02</v>
@@ -6831,11 +6905,11 @@
       <c r="O8" s="181">
         <v>0</v>
       </c>
-      <c r="P8" s="408">
+      <c r="P8" s="415">
         <f t="shared" si="2"/>
         <v>737384.03</v>
       </c>
-      <c r="Q8" s="408"/>
+      <c r="Q8" s="415"/>
       <c r="R8" s="222">
         <f t="shared" si="3"/>
         <v>759749.03</v>
@@ -6901,11 +6975,11 @@
       <c r="O9" s="181">
         <v>0</v>
       </c>
-      <c r="P9" s="408">
+      <c r="P9" s="415">
         <f t="shared" si="2"/>
         <v>1078638.04</v>
       </c>
-      <c r="Q9" s="408"/>
+      <c r="Q9" s="415"/>
       <c r="R9" s="222">
         <f t="shared" si="3"/>
         <v>1111353.04</v>
@@ -6975,11 +7049,11 @@
       <c r="O10" s="181">
         <v>0</v>
       </c>
-      <c r="P10" s="408">
+      <c r="P10" s="415">
         <f t="shared" si="2"/>
         <v>767816.05</v>
       </c>
-      <c r="Q10" s="408"/>
+      <c r="Q10" s="415"/>
       <c r="R10" s="222">
         <f t="shared" si="3"/>
         <v>791104.05</v>
@@ -7046,11 +7120,11 @@
       <c r="O11" s="181">
         <v>0</v>
       </c>
-      <c r="P11" s="408">
+      <c r="P11" s="415">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="408"/>
+      <c r="Q11" s="415"/>
       <c r="R11" s="222">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -7119,11 +7193,11 @@
       <c r="O12" s="181">
         <v>0</v>
       </c>
-      <c r="P12" s="408">
+      <c r="P12" s="415">
         <f t="shared" si="2"/>
         <v>735546.07</v>
       </c>
-      <c r="Q12" s="408"/>
+      <c r="Q12" s="415"/>
       <c r="R12" s="222">
         <f t="shared" si="3"/>
         <v>757855.07</v>
@@ -7192,11 +7266,11 @@
       <c r="O13" s="181">
         <v>0</v>
       </c>
-      <c r="P13" s="408">
+      <c r="P13" s="415">
         <f t="shared" si="2"/>
         <v>767816.08</v>
       </c>
-      <c r="Q13" s="408"/>
+      <c r="Q13" s="415"/>
       <c r="R13" s="222">
         <f t="shared" si="3"/>
         <v>791104.08</v>
@@ -7262,11 +7336,11 @@
       <c r="O14" s="181">
         <v>0</v>
       </c>
-      <c r="P14" s="408">
+      <c r="P14" s="415">
         <f t="shared" si="2"/>
         <v>1558837.09</v>
       </c>
-      <c r="Q14" s="408"/>
+      <c r="Q14" s="415"/>
       <c r="R14" s="222">
         <f t="shared" si="3"/>
         <v>1606117.09</v>
@@ -7332,11 +7406,11 @@
       <c r="O15" s="181">
         <v>0</v>
       </c>
-      <c r="P15" s="408">
+      <c r="P15" s="415">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="408"/>
+      <c r="Q15" s="415"/>
       <c r="R15" s="222">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -7404,11 +7478,11 @@
       <c r="O16" s="181">
         <v>0</v>
       </c>
-      <c r="P16" s="408">
+      <c r="P16" s="415">
         <f t="shared" si="2"/>
         <v>745214.11</v>
       </c>
-      <c r="Q16" s="408"/>
+      <c r="Q16" s="415"/>
       <c r="R16" s="222">
         <f t="shared" si="3"/>
         <v>767816.11</v>
@@ -7474,11 +7548,11 @@
       <c r="O17" s="181">
         <v>0</v>
       </c>
-      <c r="P17" s="408">
+      <c r="P17" s="415">
         <f t="shared" si="2"/>
         <v>6344888.1200000001</v>
       </c>
-      <c r="Q17" s="408"/>
+      <c r="Q17" s="415"/>
       <c r="R17" s="222">
         <f t="shared" si="3"/>
         <v>6537329.1200000001</v>
@@ -7547,11 +7621,11 @@
       <c r="O18" s="181">
         <v>0</v>
       </c>
-      <c r="P18" s="408">
+      <c r="P18" s="415">
         <f t="shared" si="2"/>
         <v>759748.13</v>
       </c>
-      <c r="Q18" s="408"/>
+      <c r="Q18" s="415"/>
       <c r="R18" s="222">
         <f t="shared" si="3"/>
         <v>782791.13</v>
@@ -7616,11 +7690,11 @@
       <c r="O19" s="181">
         <v>0</v>
       </c>
-      <c r="P19" s="408">
+      <c r="P19" s="415">
         <f t="shared" si="2"/>
         <v>998350.14</v>
       </c>
-      <c r="Q19" s="408"/>
+      <c r="Q19" s="415"/>
       <c r="R19" s="222">
         <f t="shared" si="3"/>
         <v>1028630.14</v>
@@ -7686,11 +7760,11 @@
       <c r="O20" s="181">
         <v>0</v>
       </c>
-      <c r="P20" s="408">
+      <c r="P20" s="415">
         <f t="shared" si="2"/>
         <v>1510182.15</v>
       </c>
-      <c r="Q20" s="408"/>
+      <c r="Q20" s="415"/>
       <c r="R20" s="222">
         <f t="shared" si="3"/>
         <v>1555986.15</v>
@@ -7723,7 +7797,7 @@
         <v>759748.16</v>
       </c>
       <c r="F21" s="367">
-        <f t="shared" ref="F20:F21" si="11">E21</f>
+        <f t="shared" ref="F21" si="11">E21</f>
         <v>759748.16</v>
       </c>
       <c r="G21" s="56">
@@ -7759,11 +7833,11 @@
       <c r="O21" s="181">
         <v>0</v>
       </c>
-      <c r="P21" s="408">
+      <c r="P21" s="415">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="408"/>
+      <c r="Q21" s="415"/>
       <c r="R21" s="222">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7829,11 +7903,11 @@
       <c r="O22" s="181">
         <v>0</v>
       </c>
-      <c r="P22" s="408">
+      <c r="P22" s="415">
         <f t="shared" si="2"/>
         <v>649195.17000000004</v>
       </c>
-      <c r="Q22" s="408"/>
+      <c r="Q22" s="415"/>
       <c r="R22" s="222">
         <f t="shared" si="3"/>
         <v>668885.17000000004</v>
@@ -7902,11 +7976,11 @@
       <c r="O23" s="181">
         <v>0</v>
       </c>
-      <c r="P23" s="408">
+      <c r="P23" s="415">
         <f t="shared" si="2"/>
         <v>759748.18</v>
       </c>
-      <c r="Q23" s="408"/>
+      <c r="Q23" s="415"/>
       <c r="R23" s="222">
         <f t="shared" si="3"/>
         <v>782791.18</v>
@@ -7974,11 +8048,11 @@
       <c r="O24" s="181">
         <v>0</v>
       </c>
-      <c r="P24" s="408">
+      <c r="P24" s="415">
         <f t="shared" si="2"/>
         <v>745234.19</v>
       </c>
-      <c r="Q24" s="408"/>
+      <c r="Q24" s="415"/>
       <c r="R24" s="222">
         <f t="shared" si="3"/>
         <v>767837.19</v>
@@ -8044,11 +8118,11 @@
       <c r="O25" s="181">
         <v>0</v>
       </c>
-      <c r="P25" s="408">
+      <c r="P25" s="415">
         <f t="shared" si="2"/>
         <v>767816.2</v>
       </c>
-      <c r="Q25" s="408"/>
+      <c r="Q25" s="415"/>
       <c r="R25" s="222">
         <f t="shared" si="3"/>
         <v>791104.2</v>
@@ -8114,11 +8188,11 @@
       <c r="O26" s="181">
         <v>0</v>
       </c>
-      <c r="P26" s="408">
+      <c r="P26" s="415">
         <f t="shared" si="2"/>
         <v>767816.21</v>
       </c>
-      <c r="Q26" s="408"/>
+      <c r="Q26" s="415"/>
       <c r="R26" s="222">
         <f t="shared" si="3"/>
         <v>791104.21</v>
@@ -8190,11 +8264,11 @@
       <c r="O27" s="181">
         <v>0</v>
       </c>
-      <c r="P27" s="408">
+      <c r="P27" s="415">
         <f t="shared" si="2"/>
         <v>767816.22</v>
       </c>
-      <c r="Q27" s="408"/>
+      <c r="Q27" s="415"/>
       <c r="R27" s="222">
         <f t="shared" si="3"/>
         <v>791104.22</v>
@@ -8262,11 +8336,11 @@
       <c r="O28" s="181">
         <v>0</v>
       </c>
-      <c r="P28" s="408">
+      <c r="P28" s="415">
         <f t="shared" si="2"/>
         <v>745213.23</v>
       </c>
-      <c r="Q28" s="408"/>
+      <c r="Q28" s="415"/>
       <c r="R28" s="222">
         <f t="shared" si="3"/>
         <v>767816.23</v>
@@ -8334,11 +8408,11 @@
       <c r="O29" s="181">
         <v>0</v>
       </c>
-      <c r="P29" s="408">
+      <c r="P29" s="415">
         <f t="shared" si="2"/>
         <v>721228.24</v>
       </c>
-      <c r="Q29" s="408"/>
+      <c r="Q29" s="415"/>
       <c r="R29" s="222">
         <f t="shared" si="3"/>
         <v>743103.24</v>
@@ -8407,11 +8481,11 @@
       <c r="O30" s="181">
         <v>0</v>
       </c>
-      <c r="P30" s="408">
+      <c r="P30" s="415">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="408"/>
+      <c r="Q30" s="415"/>
       <c r="R30" s="222">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8479,11 +8553,11 @@
       <c r="O31" s="181">
         <v>0</v>
       </c>
-      <c r="P31" s="408">
+      <c r="P31" s="415">
         <f t="shared" si="2"/>
         <v>775884.26</v>
       </c>
-      <c r="Q31" s="408"/>
+      <c r="Q31" s="415"/>
       <c r="R31" s="222">
         <f t="shared" si="3"/>
         <v>799417.26</v>
@@ -8552,11 +8626,11 @@
       <c r="O32" s="181">
         <v>0</v>
       </c>
-      <c r="P32" s="408">
+      <c r="P32" s="415">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="408"/>
+      <c r="Q32" s="415"/>
       <c r="R32" s="222">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -8621,11 +8695,11 @@
       <c r="O33" s="181">
         <v>0</v>
       </c>
-      <c r="P33" s="408">
+      <c r="P33" s="415">
         <f t="shared" si="2"/>
         <v>573644.28</v>
       </c>
-      <c r="Q33" s="408"/>
+      <c r="Q33" s="415"/>
       <c r="R33" s="222">
         <f t="shared" si="3"/>
         <v>591043.28</v>
@@ -8694,11 +8768,11 @@
       <c r="O34" s="181">
         <v>0</v>
       </c>
-      <c r="P34" s="408">
+      <c r="P34" s="415">
         <f t="shared" si="2"/>
         <v>775884.29</v>
       </c>
-      <c r="Q34" s="408"/>
+      <c r="Q34" s="415"/>
       <c r="R34" s="222">
         <f t="shared" si="3"/>
         <v>799417.29</v>
@@ -8767,11 +8841,11 @@
       <c r="O35" s="181">
         <v>0</v>
       </c>
-      <c r="P35" s="408">
+      <c r="P35" s="415">
         <f t="shared" si="2"/>
         <v>751681.3</v>
       </c>
-      <c r="Q35" s="408"/>
+      <c r="Q35" s="415"/>
       <c r="R35" s="222">
         <f t="shared" si="3"/>
         <v>774480.3</v>
@@ -8837,11 +8911,11 @@
       <c r="O36" s="181">
         <v>0</v>
       </c>
-      <c r="P36" s="408">
+      <c r="P36" s="415">
         <f t="shared" si="2"/>
         <v>4080719.31</v>
       </c>
-      <c r="Q36" s="408"/>
+      <c r="Q36" s="415"/>
       <c r="R36" s="222">
         <f t="shared" si="3"/>
         <v>4204488.3099999996</v>
@@ -8910,11 +8984,11 @@
       <c r="O37" s="181">
         <v>0</v>
       </c>
-      <c r="P37" s="408">
+      <c r="P37" s="415">
         <f t="shared" si="2"/>
         <v>618436.31999999995</v>
       </c>
-      <c r="Q37" s="408"/>
+      <c r="Q37" s="415"/>
       <c r="R37" s="222">
         <f t="shared" si="3"/>
         <v>637193.31999999995</v>
@@ -8979,11 +9053,11 @@
       <c r="O38" s="181">
         <v>0</v>
       </c>
-      <c r="P38" s="408">
+      <c r="P38" s="415">
         <f t="shared" ref="P38:P69" si="13">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="408"/>
+      <c r="Q38" s="415"/>
       <c r="R38" s="222">
         <f t="shared" ref="R38:R69" si="14">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -9047,11 +9121,11 @@
       <c r="O39" s="181">
         <v>0</v>
       </c>
-      <c r="P39" s="408">
+      <c r="P39" s="415">
         <f t="shared" si="13"/>
         <v>4128501.34</v>
       </c>
-      <c r="Q39" s="408"/>
+      <c r="Q39" s="415"/>
       <c r="R39" s="222">
         <f t="shared" si="14"/>
         <v>4253719.34</v>
@@ -9121,11 +9195,11 @@
       <c r="O40" s="181">
         <v>0</v>
       </c>
-      <c r="P40" s="408">
+      <c r="P40" s="415">
         <f t="shared" si="13"/>
         <v>759748.35</v>
       </c>
-      <c r="Q40" s="408"/>
+      <c r="Q40" s="415"/>
       <c r="R40" s="222">
         <f t="shared" si="14"/>
         <v>782792.35</v>
@@ -9194,11 +9268,11 @@
       <c r="O41" s="181">
         <v>0</v>
       </c>
-      <c r="P41" s="408">
+      <c r="P41" s="415">
         <f t="shared" si="13"/>
         <v>732078.36</v>
       </c>
-      <c r="Q41" s="408"/>
+      <c r="Q41" s="415"/>
       <c r="R41" s="222">
         <f t="shared" si="14"/>
         <v>754282.36</v>
@@ -9265,11 +9339,11 @@
       <c r="O42" s="181">
         <v>0</v>
       </c>
-      <c r="P42" s="408">
+      <c r="P42" s="415">
         <f t="shared" si="13"/>
         <v>775184.37</v>
       </c>
-      <c r="Q42" s="408"/>
+      <c r="Q42" s="415"/>
       <c r="R42" s="222">
         <f t="shared" si="14"/>
         <v>798696.37</v>
@@ -9334,11 +9408,11 @@
       <c r="O43" s="181">
         <v>0</v>
       </c>
-      <c r="P43" s="408">
+      <c r="P43" s="415">
         <f t="shared" si="13"/>
         <v>1503064.38</v>
       </c>
-      <c r="Q43" s="408"/>
+      <c r="Q43" s="415"/>
       <c r="R43" s="222">
         <f t="shared" si="14"/>
         <v>1548652.38</v>
@@ -9407,11 +9481,11 @@
       <c r="O44" s="181">
         <v>0</v>
       </c>
-      <c r="P44" s="408">
+      <c r="P44" s="415">
         <f t="shared" si="13"/>
         <v>751605.39</v>
       </c>
-      <c r="Q44" s="408"/>
+      <c r="Q44" s="415"/>
       <c r="R44" s="222">
         <f t="shared" si="14"/>
         <v>774402.39</v>
@@ -9478,11 +9552,11 @@
       <c r="O45" s="181">
         <v>0</v>
       </c>
-      <c r="P45" s="408">
+      <c r="P45" s="415">
         <f t="shared" si="13"/>
         <v>1526567.4</v>
       </c>
-      <c r="Q45" s="408"/>
+      <c r="Q45" s="415"/>
       <c r="R45" s="222">
         <f t="shared" si="14"/>
         <v>1572868.4</v>
@@ -9548,11 +9622,11 @@
       <c r="O46" s="181">
         <v>0</v>
       </c>
-      <c r="P46" s="408">
+      <c r="P46" s="415">
         <f t="shared" si="13"/>
         <v>751362.41</v>
       </c>
-      <c r="Q46" s="408"/>
+      <c r="Q46" s="415"/>
       <c r="R46" s="222">
         <f t="shared" si="14"/>
         <v>774151.41</v>
@@ -9622,11 +9696,11 @@
       <c r="O47" s="181">
         <v>0</v>
       </c>
-      <c r="P47" s="408">
+      <c r="P47" s="415">
         <f t="shared" si="13"/>
         <v>751681.42</v>
       </c>
-      <c r="Q47" s="408"/>
+      <c r="Q47" s="415"/>
       <c r="R47" s="222">
         <f t="shared" si="14"/>
         <v>774480.42</v>
@@ -9696,11 +9770,11 @@
       <c r="O48" s="181">
         <v>0</v>
       </c>
-      <c r="P48" s="408">
+      <c r="P48" s="415">
         <f t="shared" si="13"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="408"/>
+      <c r="Q48" s="415"/>
       <c r="R48" s="222">
         <f t="shared" si="14"/>
         <v>699669.43</v>
@@ -9764,11 +9838,11 @@
       <c r="O49" s="181">
         <v>0</v>
       </c>
-      <c r="P49" s="408">
+      <c r="P49" s="415">
         <f t="shared" si="13"/>
         <v>531782.43999999994</v>
       </c>
-      <c r="Q49" s="408"/>
+      <c r="Q49" s="415"/>
       <c r="R49" s="222">
         <f t="shared" si="14"/>
         <v>547911.43999999994</v>
@@ -9837,11 +9911,11 @@
       <c r="O50" s="181">
         <v>0</v>
       </c>
-      <c r="P50" s="408">
+      <c r="P50" s="415">
         <f t="shared" si="13"/>
         <v>1469203.45</v>
       </c>
-      <c r="Q50" s="408"/>
+      <c r="Q50" s="415"/>
       <c r="R50" s="222">
         <f t="shared" si="14"/>
         <v>1513764.45</v>
@@ -9907,11 +9981,11 @@
       <c r="O51" s="181">
         <v>0</v>
       </c>
-      <c r="P51" s="408">
+      <c r="P51" s="415">
         <f t="shared" si="13"/>
         <v>1451354.46</v>
       </c>
-      <c r="Q51" s="408"/>
+      <c r="Q51" s="415"/>
       <c r="R51" s="222">
         <f t="shared" si="14"/>
         <v>1495374.46</v>
@@ -9978,11 +10052,11 @@
       <c r="O52" s="181">
         <v>0</v>
       </c>
-      <c r="P52" s="408">
+      <c r="P52" s="415">
         <f t="shared" si="13"/>
         <v>1526567.47</v>
       </c>
-      <c r="Q52" s="408"/>
+      <c r="Q52" s="415"/>
       <c r="R52" s="222">
         <f t="shared" si="14"/>
         <v>1572868.47</v>
@@ -10050,11 +10124,11 @@
       <c r="O53" s="181">
         <v>0</v>
       </c>
-      <c r="P53" s="408">
+      <c r="P53" s="415">
         <f t="shared" si="13"/>
         <v>2411317.48</v>
       </c>
-      <c r="Q53" s="408"/>
+      <c r="Q53" s="415"/>
       <c r="R53" s="222">
         <f t="shared" si="14"/>
         <v>2484453.48</v>
@@ -10122,11 +10196,11 @@
       <c r="O54" s="181">
         <v>0</v>
       </c>
-      <c r="P54" s="408">
+      <c r="P54" s="415">
         <f t="shared" si="13"/>
         <v>751681.49</v>
       </c>
-      <c r="Q54" s="408"/>
+      <c r="Q54" s="415"/>
       <c r="R54" s="222">
         <f t="shared" si="14"/>
         <v>774480.49</v>
@@ -10195,11 +10269,11 @@
       <c r="O55" s="181">
         <v>0</v>
       </c>
-      <c r="P55" s="408">
+      <c r="P55" s="415">
         <f t="shared" si="13"/>
         <v>751681.5</v>
       </c>
-      <c r="Q55" s="408"/>
+      <c r="Q55" s="415"/>
       <c r="R55" s="222">
         <f t="shared" si="14"/>
         <v>774480.5</v>
@@ -10268,11 +10342,11 @@
       <c r="O56" s="181">
         <v>0</v>
       </c>
-      <c r="P56" s="408">
+      <c r="P56" s="415">
         <f t="shared" si="13"/>
         <v>1526985.51</v>
       </c>
-      <c r="Q56" s="408"/>
+      <c r="Q56" s="415"/>
       <c r="R56" s="222">
         <f t="shared" si="14"/>
         <v>1573299.51</v>
@@ -10342,11 +10416,11 @@
       <c r="O57" s="181">
         <v>0</v>
       </c>
-      <c r="P57" s="408">
+      <c r="P57" s="415">
         <f t="shared" si="13"/>
         <v>759748.52</v>
       </c>
-      <c r="Q57" s="408"/>
+      <c r="Q57" s="415"/>
       <c r="R57" s="222">
         <f t="shared" si="14"/>
         <v>782792.52</v>
@@ -10413,11 +10487,11 @@
       <c r="O58" s="181">
         <v>0</v>
       </c>
-      <c r="P58" s="408">
+      <c r="P58" s="415">
         <f t="shared" si="13"/>
         <v>4249221.53</v>
       </c>
-      <c r="Q58" s="408"/>
+      <c r="Q58" s="415"/>
       <c r="R58" s="222">
         <f t="shared" si="14"/>
         <v>4378100.53</v>
@@ -10484,11 +10558,11 @@
         <f>2047*100</f>
         <v>204700</v>
       </c>
-      <c r="P59" s="408">
+      <c r="P59" s="415">
         <f t="shared" si="13"/>
         <v>986284.54</v>
       </c>
-      <c r="Q59" s="408"/>
+      <c r="Q59" s="415"/>
       <c r="R59" s="222">
         <f t="shared" si="14"/>
         <v>1016199.54</v>
@@ -10557,11 +10631,11 @@
       <c r="O60" s="181">
         <v>0</v>
       </c>
-      <c r="P60" s="408">
+      <c r="P60" s="415">
         <f t="shared" si="13"/>
         <v>730463.55</v>
       </c>
-      <c r="Q60" s="408"/>
+      <c r="Q60" s="415"/>
       <c r="R60" s="222">
         <f t="shared" si="14"/>
         <v>752619.55</v>
@@ -10631,11 +10705,11 @@
       <c r="O61" s="181">
         <v>0</v>
       </c>
-      <c r="P61" s="408">
+      <c r="P61" s="415">
         <f t="shared" si="13"/>
         <v>751681.56</v>
       </c>
-      <c r="Q61" s="408"/>
+      <c r="Q61" s="415"/>
       <c r="R61" s="222">
         <f t="shared" si="14"/>
         <v>774480.56</v>
@@ -10705,11 +10779,11 @@
       <c r="O62" s="181">
         <v>0</v>
       </c>
-      <c r="P62" s="408">
+      <c r="P62" s="415">
         <f t="shared" si="13"/>
         <v>751681.57</v>
       </c>
-      <c r="Q62" s="408"/>
+      <c r="Q62" s="415"/>
       <c r="R62" s="222">
         <f t="shared" si="14"/>
         <v>774480.57</v>
@@ -10776,11 +10850,11 @@
       <c r="O63" s="181">
         <v>0</v>
       </c>
-      <c r="P63" s="408">
+      <c r="P63" s="415">
         <f t="shared" si="13"/>
         <v>706071.58</v>
       </c>
-      <c r="Q63" s="408"/>
+      <c r="Q63" s="415"/>
       <c r="R63" s="222">
         <f t="shared" si="14"/>
         <v>727487.58</v>
@@ -10847,11 +10921,11 @@
       <c r="O64" s="181">
         <v>0</v>
       </c>
-      <c r="P64" s="408">
+      <c r="P64" s="415">
         <f t="shared" si="13"/>
         <v>698821.59</v>
       </c>
-      <c r="Q64" s="408"/>
+      <c r="Q64" s="415"/>
       <c r="R64" s="222">
         <f t="shared" si="14"/>
         <v>720017.59</v>
@@ -10918,11 +10992,11 @@
       <c r="O65" s="181">
         <v>0</v>
       </c>
-      <c r="P65" s="408">
+      <c r="P65" s="415">
         <f t="shared" si="13"/>
         <v>1502581.6</v>
       </c>
-      <c r="Q65" s="408"/>
+      <c r="Q65" s="415"/>
       <c r="R65" s="222">
         <f t="shared" si="14"/>
         <v>1548155.6</v>
@@ -10991,11 +11065,11 @@
       <c r="O66" s="181">
         <v>0</v>
       </c>
-      <c r="P66" s="408">
+      <c r="P66" s="415">
         <f t="shared" si="13"/>
         <v>751387.61</v>
       </c>
-      <c r="Q66" s="408"/>
+      <c r="Q66" s="415"/>
       <c r="R66" s="222">
         <f t="shared" si="14"/>
         <v>774177.61</v>
@@ -11065,11 +11139,11 @@
       <c r="O67" s="181">
         <v>0</v>
       </c>
-      <c r="P67" s="408">
+      <c r="P67" s="415">
         <f t="shared" si="13"/>
         <v>719410.62</v>
       </c>
-      <c r="Q67" s="408"/>
+      <c r="Q67" s="415"/>
       <c r="R67" s="222">
         <f t="shared" si="14"/>
         <v>741230.62</v>
@@ -11136,11 +11210,11 @@
         <f>2047*100</f>
         <v>204700</v>
       </c>
-      <c r="P68" s="408">
+      <c r="P68" s="415">
         <f t="shared" si="13"/>
         <v>1167400.6299999999</v>
       </c>
-      <c r="Q68" s="408"/>
+      <c r="Q68" s="415"/>
       <c r="R68" s="222">
         <f t="shared" si="14"/>
         <v>1202808.6299999999</v>
@@ -11210,11 +11284,11 @@
       <c r="O69" s="181">
         <v>0</v>
       </c>
-      <c r="P69" s="408">
+      <c r="P69" s="415">
         <f t="shared" si="13"/>
         <v>751681.64</v>
       </c>
-      <c r="Q69" s="408"/>
+      <c r="Q69" s="415"/>
       <c r="R69" s="222">
         <f t="shared" si="14"/>
         <v>774480.64</v>
@@ -11284,11 +11358,11 @@
       <c r="O70" s="181">
         <v>0</v>
       </c>
-      <c r="P70" s="408">
+      <c r="P70" s="415">
         <f t="shared" ref="P70:P101" si="21">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="408"/>
+      <c r="Q70" s="415"/>
       <c r="R70" s="222">
         <f t="shared" ref="R70:R101" si="22">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -11355,11 +11429,11 @@
       <c r="O71" s="181">
         <v>0</v>
       </c>
-      <c r="P71" s="408">
+      <c r="P71" s="415">
         <f t="shared" si="21"/>
         <v>751681.66</v>
       </c>
-      <c r="Q71" s="408"/>
+      <c r="Q71" s="415"/>
       <c r="R71" s="222">
         <f t="shared" si="22"/>
         <v>774480.66</v>
@@ -11426,11 +11500,11 @@
       <c r="O72" s="181">
         <v>0</v>
       </c>
-      <c r="P72" s="408">
+      <c r="P72" s="415">
         <f t="shared" si="21"/>
         <v>2405492.67</v>
       </c>
-      <c r="Q72" s="408"/>
+      <c r="Q72" s="415"/>
       <c r="R72" s="222">
         <f t="shared" si="22"/>
         <v>2478451.67</v>
@@ -11497,11 +11571,11 @@
       <c r="O73" s="181">
         <v>0</v>
       </c>
-      <c r="P73" s="408">
+      <c r="P73" s="415">
         <f t="shared" si="21"/>
         <v>7696932.6799999997</v>
       </c>
-      <c r="Q73" s="408"/>
+      <c r="Q73" s="415"/>
       <c r="R73" s="222">
         <f t="shared" si="22"/>
         <v>7930381.6799999997</v>
@@ -11564,11 +11638,11 @@
       <c r="O74" s="181">
         <v>0</v>
       </c>
-      <c r="P74" s="408">
+      <c r="P74" s="415">
         <f t="shared" si="21"/>
         <v>1379108.69</v>
       </c>
-      <c r="Q74" s="408"/>
+      <c r="Q74" s="415"/>
       <c r="R74" s="222">
         <f t="shared" si="22"/>
         <v>1420937.69</v>
@@ -11634,11 +11708,11 @@
       <c r="O75" s="181">
         <v>0</v>
       </c>
-      <c r="P75" s="408">
+      <c r="P75" s="415">
         <f t="shared" si="21"/>
         <v>3380376.7</v>
       </c>
-      <c r="Q75" s="408"/>
+      <c r="Q75" s="415"/>
       <c r="R75" s="222">
         <f t="shared" si="22"/>
         <v>3482904.7</v>
@@ -11706,11 +11780,11 @@
       <c r="O76" s="181">
         <v>0</v>
       </c>
-      <c r="P76" s="408">
+      <c r="P76" s="415">
         <f t="shared" si="21"/>
         <v>1975071.71</v>
       </c>
-      <c r="Q76" s="408"/>
+      <c r="Q76" s="415"/>
       <c r="R76" s="222">
         <f t="shared" si="22"/>
         <v>2034976.71</v>
@@ -11779,11 +11853,11 @@
       <c r="O77" s="181">
         <v>0</v>
       </c>
-      <c r="P77" s="408">
+      <c r="P77" s="415">
         <f t="shared" si="21"/>
         <v>711343.72</v>
       </c>
-      <c r="Q77" s="408"/>
+      <c r="Q77" s="415"/>
       <c r="R77" s="222">
         <f t="shared" si="22"/>
         <v>732919.72</v>
@@ -11852,11 +11926,11 @@
       <c r="O78" s="181">
         <v>0</v>
       </c>
-      <c r="P78" s="408">
+      <c r="P78" s="415">
         <f t="shared" si="21"/>
         <v>711343.73</v>
       </c>
-      <c r="Q78" s="408"/>
+      <c r="Q78" s="415"/>
       <c r="R78" s="222">
         <f t="shared" si="22"/>
         <v>732919.73</v>
@@ -11922,11 +11996,11 @@
       <c r="O79" s="181">
         <v>0</v>
       </c>
-      <c r="P79" s="408">
+      <c r="P79" s="415">
         <f t="shared" si="21"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="408"/>
+      <c r="Q79" s="415"/>
       <c r="R79" s="222">
         <f t="shared" si="22"/>
         <v>766168.74</v>
@@ -11993,11 +12067,11 @@
         <f>I80/2</f>
         <v>165385.72603600001</v>
       </c>
-      <c r="P80" s="408">
+      <c r="P80" s="415">
         <f t="shared" si="21"/>
         <v>884796.75</v>
       </c>
-      <c r="Q80" s="408"/>
+      <c r="Q80" s="415"/>
       <c r="R80" s="222">
         <f t="shared" si="22"/>
         <v>911633.75</v>
@@ -12066,11 +12140,11 @@
       <c r="O81" s="181">
         <v>0</v>
       </c>
-      <c r="P81" s="408">
+      <c r="P81" s="415">
         <f t="shared" si="21"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="408"/>
+      <c r="Q81" s="415"/>
       <c r="R81" s="222">
         <f t="shared" si="22"/>
         <v>774480.76</v>
@@ -12135,11 +12209,11 @@
       <c r="O82" s="181">
         <v>0</v>
       </c>
-      <c r="P82" s="408">
+      <c r="P82" s="415">
         <f t="shared" si="21"/>
         <v>879525.77</v>
       </c>
-      <c r="Q82" s="408"/>
+      <c r="Q82" s="415"/>
       <c r="R82" s="222">
         <f t="shared" si="22"/>
         <v>906202.77</v>
@@ -12208,11 +12282,11 @@
       <c r="O83" s="181">
         <v>0</v>
       </c>
-      <c r="P83" s="408">
+      <c r="P83" s="415">
         <f t="shared" si="21"/>
         <v>752701.78</v>
       </c>
-      <c r="Q83" s="408"/>
+      <c r="Q83" s="415"/>
       <c r="R83" s="222">
         <f t="shared" si="22"/>
         <v>775531.78</v>
@@ -12280,11 +12354,11 @@
       <c r="O84" s="181">
         <v>0</v>
       </c>
-      <c r="P84" s="408">
+      <c r="P84" s="415">
         <f t="shared" si="21"/>
         <v>1525697.79</v>
       </c>
-      <c r="Q84" s="408"/>
+      <c r="Q84" s="415"/>
       <c r="R84" s="222">
         <f t="shared" si="22"/>
         <v>1571972.79</v>
@@ -12355,11 +12429,11 @@
       <c r="O85" s="181">
         <v>0</v>
       </c>
-      <c r="P85" s="408">
+      <c r="P85" s="415">
         <f t="shared" si="21"/>
         <v>728882.8</v>
       </c>
-      <c r="Q85" s="408"/>
+      <c r="Q85" s="415"/>
       <c r="R85" s="222">
         <f t="shared" si="22"/>
         <v>750990.8</v>
@@ -12428,11 +12502,11 @@
       <c r="O86" s="181">
         <v>0</v>
       </c>
-      <c r="P86" s="408">
+      <c r="P86" s="415">
         <f t="shared" si="21"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="408"/>
+      <c r="Q86" s="415"/>
       <c r="R86" s="222">
         <f t="shared" si="22"/>
         <v>774480.81</v>
@@ -12501,11 +12575,11 @@
       <c r="O87" s="181">
         <v>0</v>
       </c>
-      <c r="P87" s="408">
+      <c r="P87" s="415">
         <f t="shared" si="21"/>
         <v>706909.82</v>
       </c>
-      <c r="Q87" s="408"/>
+      <c r="Q87" s="415"/>
       <c r="R87" s="222">
         <f t="shared" si="22"/>
         <v>728350.82</v>
@@ -12574,11 +12648,11 @@
       <c r="O88" s="181">
         <v>0</v>
       </c>
-      <c r="P88" s="408">
+      <c r="P88" s="415">
         <f t="shared" si="21"/>
         <v>752351.83</v>
       </c>
-      <c r="Q88" s="408"/>
+      <c r="Q88" s="415"/>
       <c r="R88" s="222">
         <f t="shared" si="22"/>
         <v>775171.83</v>
@@ -12643,11 +12717,11 @@
       <c r="O89" s="181">
         <v>0</v>
       </c>
-      <c r="P89" s="408">
+      <c r="P89" s="415">
         <f t="shared" si="21"/>
         <v>752351.84</v>
       </c>
-      <c r="Q89" s="408"/>
+      <c r="Q89" s="415"/>
       <c r="R89" s="222">
         <f t="shared" si="22"/>
         <v>775171.84</v>
@@ -12713,11 +12787,11 @@
       <c r="O90" s="181">
         <v>0</v>
       </c>
-      <c r="P90" s="408">
+      <c r="P90" s="415">
         <f t="shared" si="21"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="408"/>
+      <c r="Q90" s="415"/>
       <c r="R90" s="222">
         <f t="shared" si="22"/>
         <v>799417.85</v>
@@ -12787,11 +12861,11 @@
       <c r="O91" s="181">
         <v>0</v>
       </c>
-      <c r="P91" s="408">
+      <c r="P91" s="415">
         <f t="shared" si="21"/>
         <v>1240578.8600000001</v>
       </c>
-      <c r="Q91" s="408"/>
+      <c r="Q91" s="415"/>
       <c r="R91" s="222">
         <f t="shared" si="22"/>
         <v>1278206.8600000001</v>
@@ -12860,11 +12934,11 @@
       <c r="O92" s="181">
         <v>0</v>
       </c>
-      <c r="P92" s="408">
+      <c r="P92" s="415">
         <f t="shared" si="21"/>
         <v>775884.87</v>
       </c>
-      <c r="Q92" s="408"/>
+      <c r="Q92" s="415"/>
       <c r="R92" s="222">
         <f t="shared" si="22"/>
         <v>799417.87</v>
@@ -12929,11 +13003,11 @@
       <c r="O93" s="181">
         <v>0</v>
       </c>
-      <c r="P93" s="408">
+      <c r="P93" s="415">
         <f t="shared" si="21"/>
         <v>775424.88</v>
       </c>
-      <c r="Q93" s="408"/>
+      <c r="Q93" s="415"/>
       <c r="R93" s="222">
         <f t="shared" si="22"/>
         <v>798944.88</v>
@@ -12997,11 +13071,11 @@
         <f>2047*100</f>
         <v>204700</v>
       </c>
-      <c r="P94" s="408">
+      <c r="P94" s="415">
         <f t="shared" si="21"/>
         <v>1991439.89</v>
       </c>
-      <c r="Q94" s="408"/>
+      <c r="Q94" s="415"/>
       <c r="R94" s="222">
         <f t="shared" si="22"/>
         <v>2051840.89</v>
@@ -13070,11 +13144,11 @@
         <f>2047*100</f>
         <v>204700</v>
       </c>
-      <c r="P95" s="408">
+      <c r="P95" s="415">
         <f t="shared" si="21"/>
         <v>1611807.9</v>
       </c>
-      <c r="Q95" s="408"/>
+      <c r="Q95" s="415"/>
       <c r="R95" s="222">
         <f t="shared" si="22"/>
         <v>1660694.9</v>
@@ -13143,11 +13217,11 @@
       <c r="O96" s="181">
         <v>0</v>
       </c>
-      <c r="P96" s="408">
+      <c r="P96" s="415">
         <f t="shared" si="21"/>
         <v>775884.91</v>
       </c>
-      <c r="Q96" s="408"/>
+      <c r="Q96" s="415"/>
       <c r="R96" s="222">
         <f t="shared" si="22"/>
         <v>799417.91</v>
@@ -13216,11 +13290,11 @@
       <c r="O97" s="181">
         <v>0</v>
       </c>
-      <c r="P97" s="408">
+      <c r="P97" s="415">
         <f t="shared" si="21"/>
         <v>775884.92</v>
       </c>
-      <c r="Q97" s="408"/>
+      <c r="Q97" s="415"/>
       <c r="R97" s="222">
         <f t="shared" si="22"/>
         <v>799418.92</v>
@@ -13288,11 +13362,11 @@
       <c r="O98" s="181">
         <v>0</v>
       </c>
-      <c r="P98" s="408">
+      <c r="P98" s="415">
         <f t="shared" si="21"/>
         <v>1524078.93</v>
       </c>
-      <c r="Q98" s="408"/>
+      <c r="Q98" s="415"/>
       <c r="R98" s="222">
         <f t="shared" si="22"/>
         <v>1570304.93</v>
@@ -13361,11 +13435,11 @@
       <c r="O99" s="181">
         <v>0</v>
       </c>
-      <c r="P99" s="408">
+      <c r="P99" s="415">
         <f t="shared" si="21"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="408"/>
+      <c r="Q99" s="415"/>
       <c r="R99" s="222">
         <f t="shared" si="22"/>
         <v>799418.94</v>
@@ -13431,11 +13505,11 @@
       <c r="O100" s="181">
         <v>0</v>
       </c>
-      <c r="P100" s="408">
+      <c r="P100" s="415">
         <f t="shared" si="21"/>
         <v>7379940.9500000002</v>
       </c>
-      <c r="Q100" s="408"/>
+      <c r="Q100" s="415"/>
       <c r="R100" s="222">
         <f t="shared" si="22"/>
         <v>7603775.9500000002</v>
@@ -13500,11 +13574,11 @@
       <c r="O101" s="181">
         <v>0</v>
       </c>
-      <c r="P101" s="408">
+      <c r="P101" s="415">
         <f t="shared" si="21"/>
         <v>703583.96</v>
       </c>
-      <c r="Q101" s="408"/>
+      <c r="Q101" s="415"/>
       <c r="R101" s="222">
         <f t="shared" si="22"/>
         <v>724924.96</v>
@@ -13573,11 +13647,11 @@
       <c r="O102" s="181">
         <v>0</v>
       </c>
-      <c r="P102" s="408">
+      <c r="P102" s="415">
         <f t="shared" ref="P102:P133" si="30">ROUND(SUM(G102:O102),0) + S102</f>
         <v>727186.97</v>
       </c>
-      <c r="Q102" s="408"/>
+      <c r="Q102" s="415"/>
       <c r="R102" s="222">
         <f t="shared" ref="R102:R133" si="31">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>749243.97</v>
@@ -13646,11 +13720,11 @@
       <c r="O103" s="181">
         <v>0</v>
       </c>
-      <c r="P103" s="408">
+      <c r="P103" s="415">
         <f t="shared" si="30"/>
         <v>775884.98</v>
       </c>
-      <c r="Q103" s="408"/>
+      <c r="Q103" s="415"/>
       <c r="R103" s="222">
         <f t="shared" si="31"/>
         <v>799418.98</v>
@@ -13713,11 +13787,11 @@
       <c r="O104" s="181">
         <v>0</v>
       </c>
-      <c r="P104" s="408">
+      <c r="P104" s="415">
         <f t="shared" si="30"/>
         <v>1575720.99</v>
       </c>
-      <c r="Q104" s="408"/>
+      <c r="Q104" s="415"/>
       <c r="R104" s="222">
         <f t="shared" si="31"/>
         <v>1623513.99</v>
@@ -13786,11 +13860,11 @@
       <c r="O105" s="181">
         <v>0</v>
       </c>
-      <c r="P105" s="408">
+      <c r="P105" s="415">
         <f t="shared" si="30"/>
         <v>775885</v>
       </c>
-      <c r="Q105" s="408"/>
+      <c r="Q105" s="415"/>
       <c r="R105" s="222">
         <f t="shared" si="31"/>
         <v>799419</v>
@@ -13857,11 +13931,11 @@
         <f>I106/2</f>
         <v>193622.31340799999</v>
       </c>
-      <c r="P106" s="408">
+      <c r="P106" s="415">
         <f t="shared" si="30"/>
         <v>969507.01</v>
       </c>
-      <c r="Q106" s="408"/>
+      <c r="Q106" s="415"/>
       <c r="R106" s="222">
         <f t="shared" si="31"/>
         <v>998913.01</v>
@@ -13926,11 +14000,11 @@
       <c r="O107" s="181">
         <v>0</v>
       </c>
-      <c r="P107" s="408">
+      <c r="P107" s="415">
         <f t="shared" si="30"/>
         <v>776326.02</v>
       </c>
-      <c r="Q107" s="408"/>
+      <c r="Q107" s="415"/>
       <c r="R107" s="222">
         <f t="shared" si="31"/>
         <v>799873.02</v>
@@ -13999,11 +14073,11 @@
       <c r="O108" s="181">
         <v>0</v>
       </c>
-      <c r="P108" s="408">
+      <c r="P108" s="415">
         <f t="shared" si="30"/>
         <v>775885.03</v>
       </c>
-      <c r="Q108" s="408"/>
+      <c r="Q108" s="415"/>
       <c r="R108" s="222">
         <f t="shared" si="31"/>
         <v>799419.03</v>
@@ -14069,11 +14143,11 @@
       <c r="O109" s="181">
         <v>0</v>
       </c>
-      <c r="P109" s="408">
+      <c r="P109" s="415">
         <f t="shared" si="30"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="408"/>
+      <c r="Q109" s="415"/>
       <c r="R109" s="222">
         <f t="shared" si="31"/>
         <v>791106.04</v>
@@ -14141,11 +14215,11 @@
       <c r="O110" s="181">
         <v>0</v>
       </c>
-      <c r="P110" s="408">
+      <c r="P110" s="415">
         <f t="shared" si="30"/>
         <v>727479.05</v>
       </c>
-      <c r="Q110" s="408"/>
+      <c r="Q110" s="415"/>
       <c r="R110" s="222">
         <f t="shared" si="31"/>
         <v>749544.05</v>
@@ -14213,11 +14287,11 @@
       <c r="O111" s="181">
         <v>0</v>
       </c>
-      <c r="P111" s="408">
+      <c r="P111" s="415">
         <f t="shared" si="30"/>
         <v>6220287.0599999996</v>
       </c>
-      <c r="Q111" s="408"/>
+      <c r="Q111" s="415"/>
       <c r="R111" s="222">
         <f t="shared" si="31"/>
         <v>6408949.0599999996</v>
@@ -14286,11 +14360,11 @@
       <c r="O112" s="181">
         <v>0</v>
       </c>
-      <c r="P112" s="408">
+      <c r="P112" s="415">
         <f t="shared" si="30"/>
         <v>743614.07</v>
       </c>
-      <c r="Q112" s="408"/>
+      <c r="Q112" s="415"/>
       <c r="R112" s="222">
         <f t="shared" si="31"/>
         <v>766169.07</v>
@@ -14359,11 +14433,11 @@
       <c r="O113" s="181">
         <v>0</v>
       </c>
-      <c r="P113" s="408">
+      <c r="P113" s="415">
         <f t="shared" si="30"/>
         <v>743614.08</v>
       </c>
-      <c r="Q113" s="408"/>
+      <c r="Q113" s="415"/>
       <c r="R113" s="222">
         <f t="shared" si="31"/>
         <v>766169.08</v>
@@ -14428,11 +14502,11 @@
       <c r="O114" s="181">
         <v>0</v>
       </c>
-      <c r="P114" s="408">
+      <c r="P114" s="415">
         <f t="shared" si="30"/>
         <v>1614062.09</v>
       </c>
-      <c r="Q114" s="408"/>
+      <c r="Q114" s="415"/>
       <c r="R114" s="222">
         <f t="shared" si="31"/>
         <v>1663018.09</v>
@@ -14501,11 +14575,11 @@
       <c r="O115" s="181">
         <v>0</v>
       </c>
-      <c r="P115" s="408">
+      <c r="P115" s="415">
         <f t="shared" si="30"/>
         <v>759749.1</v>
       </c>
-      <c r="Q115" s="408"/>
+      <c r="Q115" s="415"/>
       <c r="R115" s="222">
         <f t="shared" si="31"/>
         <v>782793.1</v>
@@ -14575,11 +14649,11 @@
       <c r="O116" s="181">
         <v>0</v>
       </c>
-      <c r="P116" s="408">
+      <c r="P116" s="415">
         <f t="shared" si="30"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="408"/>
+      <c r="Q116" s="415"/>
       <c r="R116" s="222">
         <f t="shared" si="31"/>
         <v>774482.11</v>
@@ -14644,11 +14718,11 @@
       <c r="O117" s="181">
         <v>0</v>
       </c>
-      <c r="P117" s="408">
+      <c r="P117" s="415">
         <f t="shared" si="30"/>
         <v>1473295.12</v>
       </c>
-      <c r="Q117" s="408"/>
+      <c r="Q117" s="415"/>
       <c r="R117" s="222">
         <f t="shared" si="31"/>
         <v>1517981.12</v>
@@ -14716,11 +14790,11 @@
       <c r="O118" s="181">
         <v>0</v>
       </c>
-      <c r="P118" s="408">
+      <c r="P118" s="415">
         <f t="shared" si="30"/>
         <v>745215.13</v>
       </c>
-      <c r="Q118" s="408"/>
+      <c r="Q118" s="415"/>
       <c r="R118" s="222">
         <f t="shared" si="31"/>
         <v>767819.13</v>
@@ -14786,11 +14860,11 @@
       <c r="O119" s="181">
         <v>0</v>
       </c>
-      <c r="P119" s="408">
+      <c r="P119" s="415">
         <f t="shared" si="30"/>
         <v>751682.14</v>
       </c>
-      <c r="Q119" s="408"/>
+      <c r="Q119" s="415"/>
       <c r="R119" s="222">
         <f t="shared" si="31"/>
         <v>774482.14</v>
@@ -14856,11 +14930,11 @@
       <c r="O120" s="181">
         <v>0</v>
       </c>
-      <c r="P120" s="408">
+      <c r="P120" s="415">
         <f t="shared" si="30"/>
         <v>904966.15</v>
       </c>
-      <c r="Q120" s="408"/>
+      <c r="Q120" s="415"/>
       <c r="R120" s="222">
         <f t="shared" si="31"/>
         <v>932415.15</v>
@@ -14929,11 +15003,11 @@
         <f>I121/2</f>
         <v>233960.29536799999</v>
       </c>
-      <c r="P121" s="408">
+      <c r="P121" s="415">
         <f t="shared" si="30"/>
         <v>1058209.1599999999</v>
       </c>
-      <c r="Q121" s="408"/>
+      <c r="Q121" s="415"/>
       <c r="R121" s="222">
         <f t="shared" si="31"/>
         <v>1090306.1599999999</v>
@@ -14999,11 +15073,11 @@
       <c r="O122" s="181">
         <v>0</v>
       </c>
-      <c r="P122" s="408">
+      <c r="P122" s="415">
         <f t="shared" si="30"/>
         <v>880763.17</v>
       </c>
-      <c r="Q122" s="408"/>
+      <c r="Q122" s="415"/>
       <c r="R122" s="222">
         <f t="shared" si="31"/>
         <v>907478.17</v>
@@ -15072,11 +15146,11 @@
       <c r="O123" s="181">
         <v>0</v>
       </c>
-      <c r="P123" s="408">
+      <c r="P123" s="415">
         <f t="shared" si="30"/>
         <v>856559.18</v>
       </c>
-      <c r="Q123" s="408"/>
+      <c r="Q123" s="415"/>
       <c r="R123" s="222">
         <f t="shared" si="31"/>
         <v>882540.18</v>
@@ -15144,11 +15218,11 @@
       <c r="O124" s="181">
         <v>0</v>
       </c>
-      <c r="P124" s="408">
+      <c r="P124" s="415">
         <f t="shared" si="30"/>
         <v>824588.19</v>
       </c>
-      <c r="Q124" s="408"/>
+      <c r="Q124" s="415"/>
       <c r="R124" s="222">
         <f t="shared" si="31"/>
         <v>849599.19</v>
@@ -15217,11 +15291,11 @@
       <c r="O125" s="181">
         <v>0</v>
       </c>
-      <c r="P125" s="408">
+      <c r="P125" s="415">
         <f t="shared" si="30"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="408"/>
+      <c r="Q125" s="415"/>
       <c r="R125" s="222">
         <f t="shared" si="31"/>
         <v>782793.2</v>
@@ -15290,11 +15364,11 @@
       <c r="O126" s="181">
         <v>0</v>
       </c>
-      <c r="P126" s="408">
+      <c r="P126" s="415">
         <f t="shared" si="30"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="408"/>
+      <c r="Q126" s="415"/>
       <c r="R126" s="222">
         <f t="shared" si="31"/>
         <v>782793.21</v>
@@ -15363,11 +15437,11 @@
       <c r="O127" s="181">
         <v>0</v>
       </c>
-      <c r="P127" s="408">
+      <c r="P127" s="415">
         <f t="shared" si="30"/>
         <v>759749.22</v>
       </c>
-      <c r="Q127" s="408"/>
+      <c r="Q127" s="415"/>
       <c r="R127" s="222">
         <f t="shared" si="31"/>
         <v>782793.22</v>
@@ -15430,11 +15504,11 @@
       <c r="O128" s="181">
         <v>0</v>
       </c>
-      <c r="P128" s="408">
+      <c r="P128" s="415">
         <f t="shared" si="30"/>
         <v>1542952.23</v>
       </c>
-      <c r="Q128" s="408"/>
+      <c r="Q128" s="415"/>
       <c r="R128" s="222">
         <f t="shared" si="31"/>
         <v>1589751.23</v>
@@ -15502,11 +15576,11 @@
       <c r="O129" s="181">
         <v>0</v>
       </c>
-      <c r="P129" s="408">
+      <c r="P129" s="415">
         <f t="shared" si="30"/>
         <v>737383.24</v>
       </c>
-      <c r="Q129" s="408"/>
+      <c r="Q129" s="415"/>
       <c r="R129" s="222">
         <f t="shared" si="31"/>
         <v>759749.24</v>
@@ -15572,11 +15646,11 @@
       <c r="O130" s="181">
         <v>0</v>
       </c>
-      <c r="P130" s="408">
+      <c r="P130" s="415">
         <f t="shared" si="30"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="408"/>
+      <c r="Q130" s="415"/>
       <c r="R130" s="222">
         <f t="shared" si="31"/>
         <v>782793.25</v>
@@ -15645,11 +15719,11 @@
       <c r="O131" s="181">
         <v>0</v>
       </c>
-      <c r="P131" s="408">
+      <c r="P131" s="415">
         <f t="shared" si="30"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="408"/>
+      <c r="Q131" s="415"/>
       <c r="R131" s="222">
         <f t="shared" si="31"/>
         <v>782793.26</v>
@@ -15715,11 +15789,11 @@
       <c r="O132" s="181">
         <v>0</v>
       </c>
-      <c r="P132" s="408">
+      <c r="P132" s="415">
         <f t="shared" si="30"/>
         <v>840425.27</v>
       </c>
-      <c r="Q132" s="408"/>
+      <c r="Q132" s="415"/>
       <c r="R132" s="222">
         <f t="shared" si="31"/>
         <v>865916.27</v>
@@ -15788,11 +15862,11 @@
       <c r="O133" s="181">
         <v>0</v>
       </c>
-      <c r="P133" s="408">
+      <c r="P133" s="415">
         <f t="shared" si="30"/>
         <v>880763.28</v>
       </c>
-      <c r="Q133" s="408"/>
+      <c r="Q133" s="415"/>
       <c r="R133" s="222">
         <f t="shared" si="31"/>
         <v>907478.28</v>
@@ -15858,11 +15932,11 @@
       <c r="O134" s="181">
         <v>0</v>
       </c>
-      <c r="P134" s="408">
+      <c r="P134" s="415">
         <f t="shared" ref="P134:P144" si="36">ROUND(SUM(G134:O134),0) + S134</f>
         <v>880763.29</v>
       </c>
-      <c r="Q134" s="408"/>
+      <c r="Q134" s="415"/>
       <c r="R134" s="222">
         <f t="shared" ref="R134:R144" si="37">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>907478.29</v>
@@ -15930,11 +16004,11 @@
       <c r="O135" s="181">
         <v>0</v>
       </c>
-      <c r="P135" s="408">
+      <c r="P135" s="415">
         <f t="shared" si="36"/>
         <v>848316.3</v>
       </c>
-      <c r="Q135" s="408"/>
+      <c r="Q135" s="415"/>
       <c r="R135" s="222">
         <f t="shared" si="37"/>
         <v>874047.3</v>
@@ -16003,11 +16077,11 @@
       <c r="O136" s="181">
         <v>0</v>
       </c>
-      <c r="P136" s="408">
+      <c r="P136" s="415">
         <f t="shared" si="36"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="408"/>
+      <c r="Q136" s="415"/>
       <c r="R136" s="222">
         <f t="shared" si="37"/>
         <v>907478.31</v>
@@ -16076,11 +16150,11 @@
       <c r="O137" s="181">
         <v>0</v>
       </c>
-      <c r="P137" s="408">
+      <c r="P137" s="415">
         <f t="shared" si="36"/>
         <v>872696.31999999995</v>
       </c>
-      <c r="Q137" s="408"/>
+      <c r="Q137" s="415"/>
       <c r="R137" s="222">
         <f t="shared" si="37"/>
         <v>899166.32</v>
@@ -16149,11 +16223,11 @@
       <c r="O138" s="181">
         <v>0</v>
       </c>
-      <c r="P138" s="408">
+      <c r="P138" s="415">
         <f t="shared" si="36"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="408"/>
+      <c r="Q138" s="415"/>
       <c r="R138" s="222">
         <f t="shared" si="37"/>
         <v>932415.33</v>
@@ -16221,11 +16295,11 @@
       <c r="O139" s="181">
         <v>0</v>
       </c>
-      <c r="P139" s="408">
+      <c r="P139" s="415">
         <f t="shared" si="36"/>
         <v>792194.34</v>
       </c>
-      <c r="Q139" s="408"/>
+      <c r="Q139" s="415"/>
       <c r="R139" s="222">
         <f t="shared" si="37"/>
         <v>816223.34</v>
@@ -16293,11 +16367,11 @@
       <c r="O140" s="181">
         <v>0</v>
       </c>
-      <c r="P140" s="408">
+      <c r="P140" s="415">
         <f t="shared" si="36"/>
         <v>854834.35</v>
       </c>
-      <c r="Q140" s="408"/>
+      <c r="Q140" s="415"/>
       <c r="R140" s="222">
         <f t="shared" si="37"/>
         <v>880762.35</v>
@@ -16366,11 +16440,11 @@
       <c r="O141" s="181">
         <v>0</v>
       </c>
-      <c r="P141" s="408">
+      <c r="P141" s="415">
         <f t="shared" si="36"/>
         <v>888831.36</v>
       </c>
-      <c r="Q141" s="408"/>
+      <c r="Q141" s="415"/>
       <c r="R141" s="222">
         <f t="shared" si="37"/>
         <v>915791.35999999999</v>
@@ -16439,11 +16513,11 @@
       <c r="O142" s="181">
         <v>0</v>
       </c>
-      <c r="P142" s="408">
+      <c r="P142" s="415">
         <f t="shared" si="36"/>
         <v>824290.37</v>
       </c>
-      <c r="Q142" s="408"/>
+      <c r="Q142" s="415"/>
       <c r="R142" s="222">
         <f t="shared" si="37"/>
         <v>849292.37</v>
@@ -16509,11 +16583,11 @@
       <c r="O143" s="181">
         <v>0</v>
       </c>
-      <c r="P143" s="408">
+      <c r="P143" s="415">
         <f t="shared" si="36"/>
         <v>877401.38</v>
       </c>
-      <c r="Q143" s="408"/>
+      <c r="Q143" s="415"/>
       <c r="R143" s="222">
         <f t="shared" si="37"/>
         <v>904014.38</v>
@@ -16581,11 +16655,11 @@
       <c r="O144" s="181">
         <v>0</v>
       </c>
-      <c r="P144" s="408">
+      <c r="P144" s="415">
         <f t="shared" si="36"/>
         <v>785399.39</v>
       </c>
-      <c r="Q144" s="408"/>
+      <c r="Q144" s="415"/>
       <c r="R144" s="222">
         <f t="shared" si="37"/>
         <v>809222.39</v>
@@ -16631,8 +16705,8 @@
       <c r="O145" s="181">
         <v>0</v>
       </c>
-      <c r="P145" s="408"/>
-      <c r="Q145" s="408"/>
+      <c r="P145" s="415"/>
+      <c r="Q145" s="415"/>
       <c r="R145" s="223"/>
       <c r="S145" s="13">
         <f t="shared" si="38"/>
@@ -16672,8 +16746,8 @@
       <c r="O146" s="181">
         <v>0</v>
       </c>
-      <c r="P146" s="408"/>
-      <c r="Q146" s="408"/>
+      <c r="P146" s="415"/>
+      <c r="Q146" s="415"/>
       <c r="R146" s="223"/>
       <c r="S146" s="13">
         <f t="shared" si="38"/>
@@ -16706,8 +16780,8 @@
       <c r="O147" s="181">
         <v>0</v>
       </c>
-      <c r="P147" s="408"/>
-      <c r="Q147" s="408"/>
+      <c r="P147" s="415"/>
+      <c r="Q147" s="415"/>
       <c r="R147" s="223"/>
       <c r="S147" s="13">
         <f t="shared" si="38"/>
@@ -16740,8 +16814,8 @@
       <c r="O148" s="181">
         <v>0</v>
       </c>
-      <c r="P148" s="408"/>
-      <c r="Q148" s="408"/>
+      <c r="P148" s="415"/>
+      <c r="Q148" s="415"/>
       <c r="R148" s="223"/>
       <c r="S148" s="13">
         <f t="shared" si="38"/>
@@ -16803,11 +16877,11 @@
       <c r="O149" s="181">
         <v>0</v>
       </c>
-      <c r="P149" s="408">
+      <c r="P149" s="415">
         <f t="shared" ref="P149:P158" si="46">ROUND(SUM(G149:O149),0) + S149</f>
         <v>695209.46</v>
       </c>
-      <c r="Q149" s="408"/>
+      <c r="Q149" s="415"/>
       <c r="R149" s="222">
         <f t="shared" ref="R149:R158" si="47">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>716296.46</v>
@@ -16870,11 +16944,11 @@
       <c r="O150" s="181">
         <v>0</v>
       </c>
-      <c r="P150" s="408">
+      <c r="P150" s="415">
         <f t="shared" si="46"/>
         <v>1139411.55</v>
       </c>
-      <c r="Q150" s="408"/>
+      <c r="Q150" s="415"/>
       <c r="R150" s="222">
         <f t="shared" si="47"/>
         <v>1173971.55</v>
@@ -16942,11 +17016,11 @@
       <c r="O151" s="181">
         <v>0</v>
       </c>
-      <c r="P151" s="408">
+      <c r="P151" s="415">
         <f t="shared" si="46"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="408"/>
+      <c r="Q151" s="415"/>
       <c r="R151" s="222">
         <f t="shared" si="47"/>
         <v>782794.58</v>
@@ -17011,11 +17085,11 @@
       <c r="O152" s="181">
         <v>0</v>
       </c>
-      <c r="P152" s="408">
+      <c r="P152" s="415">
         <f t="shared" si="46"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="408"/>
+      <c r="Q152" s="415"/>
       <c r="R152" s="222">
         <f t="shared" si="47"/>
         <v>782794.59</v>
@@ -17080,11 +17154,11 @@
       <c r="O153" s="181">
         <v>0</v>
       </c>
-      <c r="P153" s="408">
+      <c r="P153" s="415">
         <f t="shared" si="46"/>
         <v>759749.63</v>
       </c>
-      <c r="Q153" s="408"/>
+      <c r="Q153" s="415"/>
       <c r="R153" s="222">
         <f t="shared" si="47"/>
         <v>782794.63</v>
@@ -17149,11 +17223,11 @@
       <c r="O154" s="181">
         <v>0</v>
       </c>
-      <c r="P154" s="408">
+      <c r="P154" s="415">
         <f t="shared" si="46"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="408"/>
+      <c r="Q154" s="415"/>
       <c r="R154" s="222">
         <f t="shared" si="47"/>
         <v>766170.68</v>
@@ -17217,11 +17291,11 @@
       <c r="O155" s="181">
         <v>0</v>
       </c>
-      <c r="P155" s="408">
+      <c r="P155" s="415">
         <f t="shared" si="46"/>
         <v>759750.73</v>
       </c>
-      <c r="Q155" s="408"/>
+      <c r="Q155" s="415"/>
       <c r="R155" s="222">
         <f t="shared" si="47"/>
         <v>782795.73</v>
@@ -17288,11 +17362,11 @@
       <c r="O156" s="181">
         <v>0</v>
       </c>
-      <c r="P156" s="408">
+      <c r="P156" s="415">
         <f t="shared" si="46"/>
         <v>759750.75</v>
       </c>
-      <c r="Q156" s="408"/>
+      <c r="Q156" s="415"/>
       <c r="R156" s="222">
         <f t="shared" si="47"/>
         <v>782795.75</v>
@@ -17360,11 +17434,11 @@
       <c r="O157" s="181">
         <v>0</v>
       </c>
-      <c r="P157" s="408">
+      <c r="P157" s="415">
         <f t="shared" si="46"/>
         <v>759749.76</v>
       </c>
-      <c r="Q157" s="408"/>
+      <c r="Q157" s="415"/>
       <c r="R157" s="222">
         <f t="shared" si="47"/>
         <v>782794.76</v>
@@ -17428,11 +17502,11 @@
       <c r="O158" s="181">
         <v>0</v>
       </c>
-      <c r="P158" s="408">
+      <c r="P158" s="415">
         <f t="shared" si="46"/>
         <v>760873.04</v>
       </c>
-      <c r="Q158" s="408"/>
+      <c r="Q158" s="415"/>
       <c r="R158" s="222">
         <f t="shared" si="47"/>
         <v>783952.04</v>
@@ -17465,8 +17539,8 @@
       <c r="M159" s="20"/>
       <c r="N159" s="20"/>
       <c r="O159" s="66"/>
-      <c r="P159" s="413"/>
-      <c r="Q159" s="413"/>
+      <c r="P159" s="440"/>
+      <c r="Q159" s="440"/>
       <c r="R159" s="159"/>
       <c r="S159" s="13"/>
       <c r="T159" s="1"/>
@@ -17487,8 +17561,8 @@
       <c r="M160" s="170"/>
       <c r="N160" s="170"/>
       <c r="O160" s="219"/>
-      <c r="P160" s="414"/>
-      <c r="Q160" s="414"/>
+      <c r="P160" s="441"/>
+      <c r="Q160" s="441"/>
       <c r="R160" s="162"/>
       <c r="S160" s="13"/>
       <c r="T160" s="171"/>
@@ -17542,150 +17616,312 @@
         <f t="shared" si="50"/>
         <v>1411768.3348119999</v>
       </c>
-      <c r="P161" s="411">
+      <c r="P161" s="438">
         <f>SUM(P6:P160)</f>
         <v>174414304.07000002</v>
       </c>
-      <c r="Q161" s="412"/>
+      <c r="Q161" s="439"/>
       <c r="R161" s="163">
         <f>SUM(R6:R160)</f>
         <v>179704410.07000002</v>
       </c>
-      <c r="S161" s="411"/>
-      <c r="T161" s="412"/>
+      <c r="S161" s="438"/>
+      <c r="T161" s="439"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="409" t="s">
+      <c r="B162" s="436" t="s">
         <v>310</v>
       </c>
-      <c r="C162" s="409"/>
-      <c r="D162" s="409"/>
-      <c r="E162" s="409"/>
-      <c r="F162" s="409"/>
-      <c r="G162" s="409"/>
-      <c r="H162" s="409"/>
-      <c r="I162" s="409"/>
-      <c r="J162" s="409"/>
-      <c r="K162" s="409"/>
-      <c r="L162" s="409"/>
-      <c r="M162" s="409"/>
-      <c r="N162" s="409"/>
-      <c r="O162" s="409"/>
-      <c r="P162" s="409"/>
-      <c r="Q162" s="409"/>
-      <c r="R162" s="409"/>
-      <c r="S162" s="409"/>
-      <c r="T162" s="409"/>
+      <c r="C162" s="436"/>
+      <c r="D162" s="436"/>
+      <c r="E162" s="436"/>
+      <c r="F162" s="436"/>
+      <c r="G162" s="436"/>
+      <c r="H162" s="436"/>
+      <c r="I162" s="436"/>
+      <c r="J162" s="436"/>
+      <c r="K162" s="436"/>
+      <c r="L162" s="436"/>
+      <c r="M162" s="436"/>
+      <c r="N162" s="436"/>
+      <c r="O162" s="436"/>
+      <c r="P162" s="436"/>
+      <c r="Q162" s="436"/>
+      <c r="R162" s="436"/>
+      <c r="S162" s="436"/>
+      <c r="T162" s="436"/>
     </row>
     <row r="163" spans="1:20" ht="49.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="410"/>
-      <c r="C163" s="410"/>
-      <c r="D163" s="410"/>
-      <c r="E163" s="410"/>
-      <c r="F163" s="410"/>
-      <c r="G163" s="410"/>
-      <c r="H163" s="410"/>
-      <c r="I163" s="410"/>
-      <c r="J163" s="410"/>
-      <c r="K163" s="410"/>
-      <c r="L163" s="410"/>
-      <c r="M163" s="410"/>
-      <c r="N163" s="410"/>
-      <c r="O163" s="410"/>
-      <c r="P163" s="410"/>
-      <c r="Q163" s="410"/>
-      <c r="R163" s="410"/>
-      <c r="S163" s="410"/>
-      <c r="T163" s="410"/>
+      <c r="B163" s="437"/>
+      <c r="C163" s="437"/>
+      <c r="D163" s="437"/>
+      <c r="E163" s="437"/>
+      <c r="F163" s="437"/>
+      <c r="G163" s="437"/>
+      <c r="H163" s="437"/>
+      <c r="I163" s="437"/>
+      <c r="J163" s="437"/>
+      <c r="K163" s="437"/>
+      <c r="L163" s="437"/>
+      <c r="M163" s="437"/>
+      <c r="N163" s="437"/>
+      <c r="O163" s="437"/>
+      <c r="P163" s="437"/>
+      <c r="Q163" s="437"/>
+      <c r="R163" s="437"/>
+      <c r="S163" s="437"/>
+      <c r="T163" s="437"/>
     </row>
     <row r="164" spans="1:20" ht="13.7" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="410" t="s">
+      <c r="B164" s="437" t="s">
         <v>257</v>
       </c>
-      <c r="C164" s="410"/>
-      <c r="D164" s="410"/>
-      <c r="E164" s="410"/>
-      <c r="F164" s="410"/>
-      <c r="G164" s="410"/>
-      <c r="H164" s="410"/>
-      <c r="I164" s="410"/>
-      <c r="J164" s="410"/>
-      <c r="K164" s="410"/>
-      <c r="L164" s="410"/>
-      <c r="M164" s="410"/>
-      <c r="N164" s="410"/>
-      <c r="O164" s="410"/>
-      <c r="P164" s="410"/>
-      <c r="Q164" s="410"/>
-      <c r="R164" s="410"/>
-      <c r="S164" s="410"/>
-      <c r="T164" s="410"/>
+      <c r="C164" s="437"/>
+      <c r="D164" s="437"/>
+      <c r="E164" s="437"/>
+      <c r="F164" s="437"/>
+      <c r="G164" s="437"/>
+      <c r="H164" s="437"/>
+      <c r="I164" s="437"/>
+      <c r="J164" s="437"/>
+      <c r="K164" s="437"/>
+      <c r="L164" s="437"/>
+      <c r="M164" s="437"/>
+      <c r="N164" s="437"/>
+      <c r="O164" s="437"/>
+      <c r="P164" s="437"/>
+      <c r="Q164" s="437"/>
+      <c r="R164" s="437"/>
+      <c r="S164" s="437"/>
+      <c r="T164" s="437"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="410"/>
-      <c r="C165" s="410"/>
-      <c r="D165" s="410"/>
-      <c r="E165" s="410"/>
-      <c r="F165" s="410"/>
-      <c r="G165" s="410"/>
-      <c r="H165" s="410"/>
-      <c r="I165" s="410"/>
-      <c r="J165" s="410"/>
-      <c r="K165" s="410"/>
-      <c r="L165" s="410"/>
-      <c r="M165" s="410"/>
-      <c r="N165" s="410"/>
-      <c r="O165" s="410"/>
-      <c r="P165" s="410"/>
-      <c r="Q165" s="410"/>
-      <c r="R165" s="410"/>
-      <c r="S165" s="410"/>
-      <c r="T165" s="410"/>
+      <c r="B165" s="437"/>
+      <c r="C165" s="437"/>
+      <c r="D165" s="437"/>
+      <c r="E165" s="437"/>
+      <c r="F165" s="437"/>
+      <c r="G165" s="437"/>
+      <c r="H165" s="437"/>
+      <c r="I165" s="437"/>
+      <c r="J165" s="437"/>
+      <c r="K165" s="437"/>
+      <c r="L165" s="437"/>
+      <c r="M165" s="437"/>
+      <c r="N165" s="437"/>
+      <c r="O165" s="437"/>
+      <c r="P165" s="437"/>
+      <c r="Q165" s="437"/>
+      <c r="R165" s="437"/>
+      <c r="S165" s="437"/>
+      <c r="T165" s="437"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="410"/>
-      <c r="C166" s="410"/>
-      <c r="D166" s="410"/>
-      <c r="E166" s="410"/>
-      <c r="F166" s="410"/>
-      <c r="G166" s="410"/>
-      <c r="H166" s="410"/>
-      <c r="I166" s="410"/>
-      <c r="J166" s="410"/>
-      <c r="K166" s="410"/>
-      <c r="L166" s="410"/>
-      <c r="M166" s="410"/>
-      <c r="N166" s="410"/>
-      <c r="O166" s="410"/>
-      <c r="P166" s="410"/>
-      <c r="Q166" s="410"/>
-      <c r="R166" s="410"/>
-      <c r="S166" s="410"/>
-      <c r="T166" s="410"/>
+      <c r="B166" s="437"/>
+      <c r="C166" s="437"/>
+      <c r="D166" s="437"/>
+      <c r="E166" s="437"/>
+      <c r="F166" s="437"/>
+      <c r="G166" s="437"/>
+      <c r="H166" s="437"/>
+      <c r="I166" s="437"/>
+      <c r="J166" s="437"/>
+      <c r="K166" s="437"/>
+      <c r="L166" s="437"/>
+      <c r="M166" s="437"/>
+      <c r="N166" s="437"/>
+      <c r="O166" s="437"/>
+      <c r="P166" s="437"/>
+      <c r="Q166" s="437"/>
+      <c r="R166" s="437"/>
+      <c r="S166" s="437"/>
+      <c r="T166" s="437"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="410"/>
-      <c r="C167" s="410"/>
-      <c r="D167" s="410"/>
-      <c r="E167" s="410"/>
-      <c r="F167" s="410"/>
-      <c r="G167" s="410"/>
-      <c r="H167" s="410"/>
-      <c r="I167" s="410"/>
-      <c r="J167" s="410"/>
-      <c r="K167" s="410"/>
-      <c r="L167" s="410"/>
-      <c r="M167" s="410"/>
-      <c r="N167" s="410"/>
-      <c r="O167" s="410"/>
-      <c r="P167" s="410"/>
-      <c r="Q167" s="410"/>
-      <c r="R167" s="410"/>
-      <c r="S167" s="410"/>
-      <c r="T167" s="410"/>
+      <c r="B167" s="437"/>
+      <c r="C167" s="437"/>
+      <c r="D167" s="437"/>
+      <c r="E167" s="437"/>
+      <c r="F167" s="437"/>
+      <c r="G167" s="437"/>
+      <c r="H167" s="437"/>
+      <c r="I167" s="437"/>
+      <c r="J167" s="437"/>
+      <c r="K167" s="437"/>
+      <c r="L167" s="437"/>
+      <c r="M167" s="437"/>
+      <c r="N167" s="437"/>
+      <c r="O167" s="437"/>
+      <c r="P167" s="437"/>
+      <c r="Q167" s="437"/>
+      <c r="R167" s="437"/>
+      <c r="S167" s="437"/>
+      <c r="T167" s="437"/>
     </row>
   </sheetData>
   <mergeCells count="186">
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="P28:Q28"/>
+    <mergeCell ref="P29:Q29"/>
+    <mergeCell ref="P30:Q30"/>
+    <mergeCell ref="P46:Q46"/>
+    <mergeCell ref="P47:Q47"/>
+    <mergeCell ref="P48:Q48"/>
+    <mergeCell ref="P49:Q49"/>
+    <mergeCell ref="P50:Q50"/>
+    <mergeCell ref="P41:Q41"/>
+    <mergeCell ref="P42:Q42"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="P44:Q44"/>
+    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="P36:Q36"/>
+    <mergeCell ref="P37:Q37"/>
+    <mergeCell ref="P38:Q38"/>
+    <mergeCell ref="P39:Q39"/>
+    <mergeCell ref="P40:Q40"/>
+    <mergeCell ref="P31:Q31"/>
+    <mergeCell ref="P32:Q32"/>
+    <mergeCell ref="P33:Q33"/>
+    <mergeCell ref="P34:Q34"/>
+    <mergeCell ref="P35:Q35"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="P6:Q6"/>
@@ -17710,168 +17946,6 @@
     <mergeCell ref="P23:Q23"/>
     <mergeCell ref="P24:Q24"/>
     <mergeCell ref="P25:Q25"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="P28:Q28"/>
-    <mergeCell ref="P29:Q29"/>
-    <mergeCell ref="P30:Q30"/>
-    <mergeCell ref="P46:Q46"/>
-    <mergeCell ref="P47:Q47"/>
-    <mergeCell ref="P48:Q48"/>
-    <mergeCell ref="P49:Q49"/>
-    <mergeCell ref="P50:Q50"/>
-    <mergeCell ref="P41:Q41"/>
-    <mergeCell ref="P42:Q42"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="P44:Q44"/>
-    <mergeCell ref="P45:Q45"/>
-    <mergeCell ref="P36:Q36"/>
-    <mergeCell ref="P37:Q37"/>
-    <mergeCell ref="P38:Q38"/>
-    <mergeCell ref="P39:Q39"/>
-    <mergeCell ref="P40:Q40"/>
-    <mergeCell ref="P31:Q31"/>
-    <mergeCell ref="P32:Q32"/>
-    <mergeCell ref="P33:Q33"/>
-    <mergeCell ref="P34:Q34"/>
-    <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
@@ -17943,11 +18017,11 @@
       <c r="G4" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H4" s="450">
+      <c r="H4" s="442">
         <v>8</v>
       </c>
-      <c r="I4" s="450"/>
-      <c r="J4" s="451"/>
+      <c r="I4" s="442"/>
+      <c r="J4" s="443"/>
       <c r="K4" s="353"/>
       <c r="L4" s="353"/>
     </row>
@@ -17966,40 +18040,40 @@
       <c r="L5" s="353"/>
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="441" t="s">
+      <c r="C6" s="444" t="s">
         <v>378</v>
       </c>
-      <c r="D6" s="442"/>
-      <c r="E6" s="442"/>
-      <c r="F6" s="442"/>
-      <c r="G6" s="442"/>
-      <c r="H6" s="442"/>
-      <c r="I6" s="442"/>
-      <c r="J6" s="443"/>
+      <c r="D6" s="445"/>
+      <c r="E6" s="445"/>
+      <c r="F6" s="445"/>
+      <c r="G6" s="445"/>
+      <c r="H6" s="445"/>
+      <c r="I6" s="445"/>
+      <c r="J6" s="446"/>
       <c r="K6" s="353"/>
       <c r="L6" s="353"/>
     </row>
     <row r="7" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="444"/>
-      <c r="D7" s="445"/>
-      <c r="E7" s="445"/>
-      <c r="F7" s="445"/>
-      <c r="G7" s="445"/>
-      <c r="H7" s="445"/>
-      <c r="I7" s="445"/>
-      <c r="J7" s="446"/>
+      <c r="C7" s="447"/>
+      <c r="D7" s="448"/>
+      <c r="E7" s="448"/>
+      <c r="F7" s="448"/>
+      <c r="G7" s="448"/>
+      <c r="H7" s="448"/>
+      <c r="I7" s="448"/>
+      <c r="J7" s="449"/>
       <c r="K7" s="353"/>
       <c r="L7" s="353"/>
     </row>
     <row r="8" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="447"/>
-      <c r="D8" s="448"/>
-      <c r="E8" s="448"/>
-      <c r="F8" s="448"/>
-      <c r="G8" s="448"/>
-      <c r="H8" s="448"/>
-      <c r="I8" s="448"/>
-      <c r="J8" s="449"/>
+      <c r="C8" s="450"/>
+      <c r="D8" s="451"/>
+      <c r="E8" s="451"/>
+      <c r="F8" s="451"/>
+      <c r="G8" s="451"/>
+      <c r="H8" s="451"/>
+      <c r="I8" s="451"/>
+      <c r="J8" s="452"/>
       <c r="K8" s="353"/>
       <c r="L8" s="353"/>
     </row>
@@ -18053,11 +18127,11 @@
       <c r="G13" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H13" s="450">
+      <c r="H13" s="442">
         <v>72</v>
       </c>
-      <c r="I13" s="450"/>
-      <c r="J13" s="451"/>
+      <c r="I13" s="442"/>
+      <c r="J13" s="443"/>
       <c r="K13" s="353"/>
       <c r="L13" s="353"/>
     </row>
@@ -18076,40 +18150,40 @@
       <c r="L14" s="353"/>
     </row>
     <row r="15" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C15" s="441" t="s">
+      <c r="C15" s="444" t="s">
         <v>356</v>
       </c>
-      <c r="D15" s="442"/>
-      <c r="E15" s="442"/>
-      <c r="F15" s="442"/>
-      <c r="G15" s="442"/>
-      <c r="H15" s="442"/>
-      <c r="I15" s="442"/>
-      <c r="J15" s="443"/>
+      <c r="D15" s="445"/>
+      <c r="E15" s="445"/>
+      <c r="F15" s="445"/>
+      <c r="G15" s="445"/>
+      <c r="H15" s="445"/>
+      <c r="I15" s="445"/>
+      <c r="J15" s="446"/>
       <c r="K15" s="353"/>
       <c r="L15" s="353"/>
     </row>
     <row r="16" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C16" s="444"/>
-      <c r="D16" s="445"/>
-      <c r="E16" s="445"/>
-      <c r="F16" s="445"/>
-      <c r="G16" s="445"/>
-      <c r="H16" s="445"/>
-      <c r="I16" s="445"/>
-      <c r="J16" s="446"/>
+      <c r="C16" s="447"/>
+      <c r="D16" s="448"/>
+      <c r="E16" s="448"/>
+      <c r="F16" s="448"/>
+      <c r="G16" s="448"/>
+      <c r="H16" s="448"/>
+      <c r="I16" s="448"/>
+      <c r="J16" s="449"/>
       <c r="K16" s="353"/>
       <c r="L16" s="353"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="447"/>
-      <c r="D17" s="448"/>
-      <c r="E17" s="448"/>
-      <c r="F17" s="448"/>
-      <c r="G17" s="448"/>
-      <c r="H17" s="448"/>
-      <c r="I17" s="448"/>
-      <c r="J17" s="449"/>
+      <c r="C17" s="450"/>
+      <c r="D17" s="451"/>
+      <c r="E17" s="451"/>
+      <c r="F17" s="451"/>
+      <c r="G17" s="451"/>
+      <c r="H17" s="451"/>
+      <c r="I17" s="451"/>
+      <c r="J17" s="452"/>
       <c r="K17" s="353"/>
       <c r="L17" s="353"/>
     </row>
@@ -18165,11 +18239,11 @@
       <c r="G22" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H22" s="450" t="s">
+      <c r="H22" s="442" t="s">
         <v>357</v>
       </c>
-      <c r="I22" s="450"/>
-      <c r="J22" s="451"/>
+      <c r="I22" s="442"/>
+      <c r="J22" s="443"/>
       <c r="K22" s="353"/>
       <c r="L22" s="353"/>
     </row>
@@ -18188,40 +18262,40 @@
       <c r="L23" s="353"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C24" s="441" t="s">
+      <c r="C24" s="444" t="s">
         <v>382</v>
       </c>
-      <c r="D24" s="442"/>
-      <c r="E24" s="442"/>
-      <c r="F24" s="442"/>
-      <c r="G24" s="442"/>
-      <c r="H24" s="442"/>
-      <c r="I24" s="442"/>
-      <c r="J24" s="443"/>
+      <c r="D24" s="445"/>
+      <c r="E24" s="445"/>
+      <c r="F24" s="445"/>
+      <c r="G24" s="445"/>
+      <c r="H24" s="445"/>
+      <c r="I24" s="445"/>
+      <c r="J24" s="446"/>
       <c r="K24" s="353"/>
       <c r="L24" s="353"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C25" s="444"/>
-      <c r="D25" s="445"/>
-      <c r="E25" s="445"/>
-      <c r="F25" s="445"/>
-      <c r="G25" s="445"/>
-      <c r="H25" s="445"/>
-      <c r="I25" s="445"/>
-      <c r="J25" s="446"/>
+      <c r="C25" s="447"/>
+      <c r="D25" s="448"/>
+      <c r="E25" s="448"/>
+      <c r="F25" s="448"/>
+      <c r="G25" s="448"/>
+      <c r="H25" s="448"/>
+      <c r="I25" s="448"/>
+      <c r="J25" s="449"/>
       <c r="K25" s="353"/>
       <c r="L25" s="353"/>
     </row>
     <row r="26" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="447"/>
-      <c r="D26" s="448"/>
-      <c r="E26" s="448"/>
-      <c r="F26" s="448"/>
-      <c r="G26" s="448"/>
-      <c r="H26" s="448"/>
-      <c r="I26" s="448"/>
-      <c r="J26" s="449"/>
+      <c r="C26" s="450"/>
+      <c r="D26" s="451"/>
+      <c r="E26" s="451"/>
+      <c r="F26" s="451"/>
+      <c r="G26" s="451"/>
+      <c r="H26" s="451"/>
+      <c r="I26" s="451"/>
+      <c r="J26" s="452"/>
       <c r="K26" s="353"/>
       <c r="L26" s="353"/>
     </row>
@@ -18276,11 +18350,11 @@
       <c r="G31" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H31" s="450" t="s">
+      <c r="H31" s="442" t="s">
         <v>359</v>
       </c>
-      <c r="I31" s="450"/>
-      <c r="J31" s="451"/>
+      <c r="I31" s="442"/>
+      <c r="J31" s="443"/>
       <c r="K31" s="353"/>
       <c r="L31" s="353"/>
     </row>
@@ -18299,40 +18373,40 @@
       <c r="L32" s="353"/>
     </row>
     <row r="33" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C33" s="441" t="s">
+      <c r="C33" s="444" t="s">
         <v>358</v>
       </c>
-      <c r="D33" s="442"/>
-      <c r="E33" s="442"/>
-      <c r="F33" s="442"/>
-      <c r="G33" s="442"/>
-      <c r="H33" s="442"/>
-      <c r="I33" s="442"/>
-      <c r="J33" s="443"/>
+      <c r="D33" s="445"/>
+      <c r="E33" s="445"/>
+      <c r="F33" s="445"/>
+      <c r="G33" s="445"/>
+      <c r="H33" s="445"/>
+      <c r="I33" s="445"/>
+      <c r="J33" s="446"/>
       <c r="K33" s="353"/>
       <c r="L33" s="353"/>
     </row>
     <row r="34" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C34" s="444"/>
-      <c r="D34" s="445"/>
-      <c r="E34" s="445"/>
-      <c r="F34" s="445"/>
-      <c r="G34" s="445"/>
-      <c r="H34" s="445"/>
-      <c r="I34" s="445"/>
-      <c r="J34" s="446"/>
+      <c r="C34" s="447"/>
+      <c r="D34" s="448"/>
+      <c r="E34" s="448"/>
+      <c r="F34" s="448"/>
+      <c r="G34" s="448"/>
+      <c r="H34" s="448"/>
+      <c r="I34" s="448"/>
+      <c r="J34" s="449"/>
       <c r="K34" s="353"/>
       <c r="L34" s="353"/>
     </row>
     <row r="35" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="447"/>
-      <c r="D35" s="448"/>
-      <c r="E35" s="448"/>
-      <c r="F35" s="448"/>
-      <c r="G35" s="448"/>
-      <c r="H35" s="448"/>
-      <c r="I35" s="448"/>
-      <c r="J35" s="449"/>
+      <c r="C35" s="450"/>
+      <c r="D35" s="451"/>
+      <c r="E35" s="451"/>
+      <c r="F35" s="451"/>
+      <c r="G35" s="451"/>
+      <c r="H35" s="451"/>
+      <c r="I35" s="451"/>
+      <c r="J35" s="452"/>
       <c r="K35" s="353"/>
       <c r="L35" s="353"/>
     </row>
@@ -18383,11 +18457,11 @@
       <c r="G40" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H40" s="450">
+      <c r="H40" s="442">
         <v>78</v>
       </c>
-      <c r="I40" s="450"/>
-      <c r="J40" s="451"/>
+      <c r="I40" s="442"/>
+      <c r="J40" s="443"/>
       <c r="K40" s="353"/>
       <c r="L40" s="353"/>
     </row>
@@ -18406,40 +18480,40 @@
       <c r="L41" s="353"/>
     </row>
     <row r="42" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C42" s="441" t="s">
+      <c r="C42" s="444" t="s">
         <v>360</v>
       </c>
-      <c r="D42" s="442"/>
-      <c r="E42" s="442"/>
-      <c r="F42" s="442"/>
-      <c r="G42" s="442"/>
-      <c r="H42" s="442"/>
-      <c r="I42" s="442"/>
-      <c r="J42" s="443"/>
+      <c r="D42" s="445"/>
+      <c r="E42" s="445"/>
+      <c r="F42" s="445"/>
+      <c r="G42" s="445"/>
+      <c r="H42" s="445"/>
+      <c r="I42" s="445"/>
+      <c r="J42" s="446"/>
       <c r="K42" s="353"/>
       <c r="L42" s="353"/>
     </row>
     <row r="43" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C43" s="444"/>
-      <c r="D43" s="445"/>
-      <c r="E43" s="445"/>
-      <c r="F43" s="445"/>
-      <c r="G43" s="445"/>
-      <c r="H43" s="445"/>
-      <c r="I43" s="445"/>
-      <c r="J43" s="446"/>
+      <c r="C43" s="447"/>
+      <c r="D43" s="448"/>
+      <c r="E43" s="448"/>
+      <c r="F43" s="448"/>
+      <c r="G43" s="448"/>
+      <c r="H43" s="448"/>
+      <c r="I43" s="448"/>
+      <c r="J43" s="449"/>
       <c r="K43" s="353"/>
       <c r="L43" s="353"/>
     </row>
     <row r="44" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="447"/>
-      <c r="D44" s="448"/>
-      <c r="E44" s="448"/>
-      <c r="F44" s="448"/>
-      <c r="G44" s="448"/>
-      <c r="H44" s="448"/>
-      <c r="I44" s="448"/>
-      <c r="J44" s="449"/>
+      <c r="C44" s="450"/>
+      <c r="D44" s="451"/>
+      <c r="E44" s="451"/>
+      <c r="F44" s="451"/>
+      <c r="G44" s="451"/>
+      <c r="H44" s="451"/>
+      <c r="I44" s="451"/>
+      <c r="J44" s="452"/>
     </row>
     <row r="45" spans="3:12" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="349"/>
@@ -18508,11 +18582,11 @@
       <c r="G49" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H49" s="450" t="s">
+      <c r="H49" s="442" t="s">
         <v>381</v>
       </c>
-      <c r="I49" s="450"/>
-      <c r="J49" s="451"/>
+      <c r="I49" s="442"/>
+      <c r="J49" s="443"/>
       <c r="K49" s="353"/>
       <c r="L49" s="353"/>
     </row>
@@ -18531,40 +18605,40 @@
       <c r="L50" s="353"/>
     </row>
     <row r="51" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C51" s="441" t="s">
+      <c r="C51" s="444" t="s">
         <v>380</v>
       </c>
-      <c r="D51" s="442"/>
-      <c r="E51" s="442"/>
-      <c r="F51" s="442"/>
-      <c r="G51" s="442"/>
-      <c r="H51" s="442"/>
-      <c r="I51" s="442"/>
-      <c r="J51" s="443"/>
+      <c r="D51" s="445"/>
+      <c r="E51" s="445"/>
+      <c r="F51" s="445"/>
+      <c r="G51" s="445"/>
+      <c r="H51" s="445"/>
+      <c r="I51" s="445"/>
+      <c r="J51" s="446"/>
       <c r="K51" s="353"/>
       <c r="L51" s="353"/>
     </row>
     <row r="52" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C52" s="444"/>
-      <c r="D52" s="445"/>
-      <c r="E52" s="445"/>
-      <c r="F52" s="445"/>
-      <c r="G52" s="445"/>
-      <c r="H52" s="445"/>
-      <c r="I52" s="445"/>
-      <c r="J52" s="446"/>
+      <c r="C52" s="447"/>
+      <c r="D52" s="448"/>
+      <c r="E52" s="448"/>
+      <c r="F52" s="448"/>
+      <c r="G52" s="448"/>
+      <c r="H52" s="448"/>
+      <c r="I52" s="448"/>
+      <c r="J52" s="449"/>
       <c r="K52" s="353"/>
       <c r="L52" s="353"/>
     </row>
     <row r="53" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="447"/>
-      <c r="D53" s="448"/>
-      <c r="E53" s="448"/>
-      <c r="F53" s="448"/>
-      <c r="G53" s="448"/>
-      <c r="H53" s="448"/>
-      <c r="I53" s="448"/>
-      <c r="J53" s="449"/>
+      <c r="C53" s="450"/>
+      <c r="D53" s="451"/>
+      <c r="E53" s="451"/>
+      <c r="F53" s="451"/>
+      <c r="G53" s="451"/>
+      <c r="H53" s="451"/>
+      <c r="I53" s="451"/>
+      <c r="J53" s="452"/>
       <c r="K53" s="353"/>
       <c r="L53" s="353"/>
     </row>
@@ -18616,11 +18690,11 @@
       <c r="G57" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H57" s="450">
+      <c r="H57" s="442">
         <v>112</v>
       </c>
-      <c r="I57" s="450"/>
-      <c r="J57" s="451"/>
+      <c r="I57" s="442"/>
+      <c r="J57" s="443"/>
       <c r="K57" s="353"/>
       <c r="L57" s="353"/>
     </row>
@@ -18639,38 +18713,38 @@
       <c r="L58" s="353"/>
     </row>
     <row r="59" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C59" s="441" t="s">
+      <c r="C59" s="444" t="s">
         <v>361</v>
       </c>
-      <c r="D59" s="442"/>
-      <c r="E59" s="442"/>
-      <c r="F59" s="442"/>
-      <c r="G59" s="442"/>
-      <c r="H59" s="442"/>
-      <c r="I59" s="442"/>
-      <c r="J59" s="443"/>
+      <c r="D59" s="445"/>
+      <c r="E59" s="445"/>
+      <c r="F59" s="445"/>
+      <c r="G59" s="445"/>
+      <c r="H59" s="445"/>
+      <c r="I59" s="445"/>
+      <c r="J59" s="446"/>
       <c r="K59" s="353"/>
       <c r="L59" s="353"/>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C60" s="444"/>
-      <c r="D60" s="445"/>
-      <c r="E60" s="445"/>
-      <c r="F60" s="445"/>
-      <c r="G60" s="445"/>
-      <c r="H60" s="445"/>
-      <c r="I60" s="445"/>
-      <c r="J60" s="446"/>
+      <c r="C60" s="447"/>
+      <c r="D60" s="448"/>
+      <c r="E60" s="448"/>
+      <c r="F60" s="448"/>
+      <c r="G60" s="448"/>
+      <c r="H60" s="448"/>
+      <c r="I60" s="448"/>
+      <c r="J60" s="449"/>
     </row>
     <row r="61" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C61" s="447"/>
-      <c r="D61" s="448"/>
-      <c r="E61" s="448"/>
-      <c r="F61" s="448"/>
-      <c r="G61" s="448"/>
-      <c r="H61" s="448"/>
-      <c r="I61" s="448"/>
-      <c r="J61" s="449"/>
+      <c r="C61" s="450"/>
+      <c r="D61" s="451"/>
+      <c r="E61" s="451"/>
+      <c r="F61" s="451"/>
+      <c r="G61" s="451"/>
+      <c r="H61" s="451"/>
+      <c r="I61" s="451"/>
+      <c r="J61" s="452"/>
     </row>
     <row r="63" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="64" spans="3:12" x14ac:dyDescent="0.25">
@@ -18686,8 +18760,8 @@
       <c r="H64" s="231"/>
       <c r="I64" s="232"/>
       <c r="J64" s="233"/>
-      <c r="K64" s="454"/>
-      <c r="L64" s="455"/>
+      <c r="K64" s="455"/>
+      <c r="L64" s="456"/>
     </row>
     <row r="65" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C65" s="307"/>
@@ -18703,8 +18777,8 @@
         <v>7</v>
       </c>
       <c r="J65" s="60"/>
-      <c r="K65" s="454"/>
-      <c r="L65" s="455"/>
+      <c r="K65" s="455"/>
+      <c r="L65" s="456"/>
     </row>
     <row r="66" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C66" s="307" t="s">
@@ -18720,13 +18794,13 @@
       <c r="G66" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H66" s="450" t="s">
+      <c r="H66" s="442" t="s">
         <v>362</v>
       </c>
-      <c r="I66" s="450"/>
-      <c r="J66" s="451"/>
-      <c r="K66" s="454"/>
-      <c r="L66" s="455"/>
+      <c r="I66" s="442"/>
+      <c r="J66" s="443"/>
+      <c r="K66" s="455"/>
+      <c r="L66" s="456"/>
     </row>
     <row r="67" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C67" s="307" t="s">
@@ -18739,44 +18813,44 @@
       <c r="H67" s="33"/>
       <c r="I67" s="33"/>
       <c r="J67" s="61"/>
-      <c r="K67" s="454"/>
-      <c r="L67" s="455"/>
+      <c r="K67" s="455"/>
+      <c r="L67" s="456"/>
     </row>
     <row r="68" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C68" s="441" t="s">
+      <c r="C68" s="444" t="s">
         <v>488</v>
       </c>
-      <c r="D68" s="442"/>
-      <c r="E68" s="442"/>
-      <c r="F68" s="442"/>
-      <c r="G68" s="442"/>
-      <c r="H68" s="442"/>
-      <c r="I68" s="442"/>
-      <c r="J68" s="443"/>
-      <c r="K68" s="454"/>
-      <c r="L68" s="455"/>
+      <c r="D68" s="445"/>
+      <c r="E68" s="445"/>
+      <c r="F68" s="445"/>
+      <c r="G68" s="445"/>
+      <c r="H68" s="445"/>
+      <c r="I68" s="445"/>
+      <c r="J68" s="446"/>
+      <c r="K68" s="455"/>
+      <c r="L68" s="456"/>
     </row>
     <row r="69" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C69" s="444"/>
-      <c r="D69" s="445"/>
-      <c r="E69" s="445"/>
-      <c r="F69" s="445"/>
-      <c r="G69" s="445"/>
-      <c r="H69" s="445"/>
-      <c r="I69" s="445"/>
-      <c r="J69" s="446"/>
-      <c r="K69" s="454"/>
-      <c r="L69" s="455"/>
+      <c r="C69" s="447"/>
+      <c r="D69" s="448"/>
+      <c r="E69" s="448"/>
+      <c r="F69" s="448"/>
+      <c r="G69" s="448"/>
+      <c r="H69" s="448"/>
+      <c r="I69" s="448"/>
+      <c r="J69" s="449"/>
+      <c r="K69" s="455"/>
+      <c r="L69" s="456"/>
     </row>
     <row r="70" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C70" s="447"/>
-      <c r="D70" s="448"/>
-      <c r="E70" s="448"/>
-      <c r="F70" s="448"/>
-      <c r="G70" s="448"/>
-      <c r="H70" s="448"/>
-      <c r="I70" s="448"/>
-      <c r="J70" s="449"/>
+      <c r="C70" s="450"/>
+      <c r="D70" s="451"/>
+      <c r="E70" s="451"/>
+      <c r="F70" s="451"/>
+      <c r="G70" s="451"/>
+      <c r="H70" s="451"/>
+      <c r="I70" s="451"/>
+      <c r="J70" s="452"/>
     </row>
     <row r="72" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="73" spans="3:12" x14ac:dyDescent="0.25">
@@ -18824,11 +18898,11 @@
       <c r="G75" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H75" s="450">
+      <c r="H75" s="442">
         <v>138</v>
       </c>
-      <c r="I75" s="450"/>
-      <c r="J75" s="451"/>
+      <c r="I75" s="442"/>
+      <c r="J75" s="443"/>
       <c r="K75" s="353"/>
       <c r="L75" s="353"/>
     </row>
@@ -18847,40 +18921,40 @@
       <c r="L76" s="353"/>
     </row>
     <row r="77" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C77" s="441" t="s">
+      <c r="C77" s="444" t="s">
         <v>363</v>
       </c>
-      <c r="D77" s="442"/>
-      <c r="E77" s="442"/>
-      <c r="F77" s="442"/>
-      <c r="G77" s="442"/>
-      <c r="H77" s="442"/>
-      <c r="I77" s="442"/>
-      <c r="J77" s="443"/>
+      <c r="D77" s="445"/>
+      <c r="E77" s="445"/>
+      <c r="F77" s="445"/>
+      <c r="G77" s="445"/>
+      <c r="H77" s="445"/>
+      <c r="I77" s="445"/>
+      <c r="J77" s="446"/>
       <c r="K77" s="353"/>
       <c r="L77" s="353"/>
     </row>
     <row r="78" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C78" s="444"/>
-      <c r="D78" s="445"/>
-      <c r="E78" s="445"/>
-      <c r="F78" s="445"/>
-      <c r="G78" s="445"/>
-      <c r="H78" s="445"/>
-      <c r="I78" s="445"/>
-      <c r="J78" s="446"/>
+      <c r="C78" s="447"/>
+      <c r="D78" s="448"/>
+      <c r="E78" s="448"/>
+      <c r="F78" s="448"/>
+      <c r="G78" s="448"/>
+      <c r="H78" s="448"/>
+      <c r="I78" s="448"/>
+      <c r="J78" s="449"/>
       <c r="K78" s="353"/>
       <c r="L78" s="353"/>
     </row>
     <row r="79" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="447"/>
-      <c r="D79" s="448"/>
-      <c r="E79" s="448"/>
-      <c r="F79" s="448"/>
-      <c r="G79" s="448"/>
-      <c r="H79" s="448"/>
-      <c r="I79" s="448"/>
-      <c r="J79" s="449"/>
+      <c r="C79" s="450"/>
+      <c r="D79" s="451"/>
+      <c r="E79" s="451"/>
+      <c r="F79" s="451"/>
+      <c r="G79" s="451"/>
+      <c r="H79" s="451"/>
+      <c r="I79" s="451"/>
+      <c r="J79" s="452"/>
       <c r="K79" s="353"/>
       <c r="L79" s="353"/>
     </row>
@@ -18932,11 +19006,11 @@
       <c r="G84" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H84" s="450">
+      <c r="H84" s="442">
         <v>105</v>
       </c>
-      <c r="I84" s="450"/>
-      <c r="J84" s="451"/>
+      <c r="I84" s="442"/>
+      <c r="J84" s="443"/>
       <c r="K84" s="353"/>
       <c r="L84" s="353"/>
     </row>
@@ -18955,40 +19029,40 @@
       <c r="L85" s="353"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C86" s="441" t="s">
+      <c r="C86" s="444" t="s">
         <v>364</v>
       </c>
-      <c r="D86" s="442"/>
-      <c r="E86" s="442"/>
-      <c r="F86" s="442"/>
-      <c r="G86" s="442"/>
-      <c r="H86" s="442"/>
-      <c r="I86" s="442"/>
-      <c r="J86" s="443"/>
+      <c r="D86" s="445"/>
+      <c r="E86" s="445"/>
+      <c r="F86" s="445"/>
+      <c r="G86" s="445"/>
+      <c r="H86" s="445"/>
+      <c r="I86" s="445"/>
+      <c r="J86" s="446"/>
       <c r="K86" s="353"/>
       <c r="L86" s="353"/>
     </row>
     <row r="87" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C87" s="444"/>
-      <c r="D87" s="445"/>
-      <c r="E87" s="445"/>
-      <c r="F87" s="445"/>
-      <c r="G87" s="445"/>
-      <c r="H87" s="445"/>
-      <c r="I87" s="445"/>
-      <c r="J87" s="446"/>
+      <c r="C87" s="447"/>
+      <c r="D87" s="448"/>
+      <c r="E87" s="448"/>
+      <c r="F87" s="448"/>
+      <c r="G87" s="448"/>
+      <c r="H87" s="448"/>
+      <c r="I87" s="448"/>
+      <c r="J87" s="449"/>
       <c r="K87" s="353"/>
       <c r="L87" s="353"/>
     </row>
     <row r="88" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C88" s="447"/>
-      <c r="D88" s="448"/>
-      <c r="E88" s="448"/>
-      <c r="F88" s="448"/>
-      <c r="G88" s="448"/>
-      <c r="H88" s="448"/>
-      <c r="I88" s="448"/>
-      <c r="J88" s="449"/>
+      <c r="C88" s="450"/>
+      <c r="D88" s="451"/>
+      <c r="E88" s="451"/>
+      <c r="F88" s="451"/>
+      <c r="G88" s="451"/>
+      <c r="H88" s="451"/>
+      <c r="I88" s="451"/>
+      <c r="J88" s="452"/>
       <c r="K88" s="353"/>
       <c r="L88" s="353"/>
     </row>
@@ -19040,11 +19114,11 @@
       <c r="G93" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H93" s="450">
+      <c r="H93" s="442">
         <v>119</v>
       </c>
-      <c r="I93" s="450"/>
-      <c r="J93" s="451"/>
+      <c r="I93" s="442"/>
+      <c r="J93" s="443"/>
       <c r="K93" s="353"/>
       <c r="L93" s="353"/>
     </row>
@@ -19063,40 +19137,40 @@
       <c r="L94" s="353"/>
     </row>
     <row r="95" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C95" s="441" t="s">
+      <c r="C95" s="444" t="s">
         <v>365</v>
       </c>
-      <c r="D95" s="442"/>
-      <c r="E95" s="442"/>
-      <c r="F95" s="442"/>
-      <c r="G95" s="442"/>
-      <c r="H95" s="442"/>
-      <c r="I95" s="442"/>
-      <c r="J95" s="443"/>
+      <c r="D95" s="445"/>
+      <c r="E95" s="445"/>
+      <c r="F95" s="445"/>
+      <c r="G95" s="445"/>
+      <c r="H95" s="445"/>
+      <c r="I95" s="445"/>
+      <c r="J95" s="446"/>
       <c r="K95" s="353"/>
       <c r="L95" s="353"/>
     </row>
     <row r="96" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C96" s="444"/>
-      <c r="D96" s="445"/>
-      <c r="E96" s="445"/>
-      <c r="F96" s="445"/>
-      <c r="G96" s="445"/>
-      <c r="H96" s="445"/>
-      <c r="I96" s="445"/>
-      <c r="J96" s="446"/>
+      <c r="C96" s="447"/>
+      <c r="D96" s="448"/>
+      <c r="E96" s="448"/>
+      <c r="F96" s="448"/>
+      <c r="G96" s="448"/>
+      <c r="H96" s="448"/>
+      <c r="I96" s="448"/>
+      <c r="J96" s="449"/>
       <c r="K96" s="353"/>
       <c r="L96" s="353"/>
     </row>
     <row r="97" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C97" s="447"/>
-      <c r="D97" s="448"/>
-      <c r="E97" s="448"/>
-      <c r="F97" s="448"/>
-      <c r="G97" s="448"/>
-      <c r="H97" s="448"/>
-      <c r="I97" s="448"/>
-      <c r="J97" s="449"/>
+      <c r="C97" s="450"/>
+      <c r="D97" s="451"/>
+      <c r="E97" s="451"/>
+      <c r="F97" s="451"/>
+      <c r="G97" s="451"/>
+      <c r="H97" s="451"/>
+      <c r="I97" s="451"/>
+      <c r="J97" s="452"/>
       <c r="K97" s="353"/>
       <c r="L97" s="353"/>
     </row>
@@ -19152,11 +19226,11 @@
       <c r="G102" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H102" s="450">
+      <c r="H102" s="442">
         <v>102</v>
       </c>
-      <c r="I102" s="450"/>
-      <c r="J102" s="451"/>
+      <c r="I102" s="442"/>
+      <c r="J102" s="443"/>
       <c r="K102" s="353"/>
       <c r="L102" s="353"/>
     </row>
@@ -19175,40 +19249,40 @@
       <c r="L103" s="353"/>
     </row>
     <row r="104" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C104" s="441" t="s">
+      <c r="C104" s="444" t="s">
         <v>366</v>
       </c>
-      <c r="D104" s="442"/>
-      <c r="E104" s="442"/>
-      <c r="F104" s="442"/>
-      <c r="G104" s="442"/>
-      <c r="H104" s="442"/>
-      <c r="I104" s="442"/>
-      <c r="J104" s="443"/>
+      <c r="D104" s="445"/>
+      <c r="E104" s="445"/>
+      <c r="F104" s="445"/>
+      <c r="G104" s="445"/>
+      <c r="H104" s="445"/>
+      <c r="I104" s="445"/>
+      <c r="J104" s="446"/>
       <c r="K104" s="353"/>
       <c r="L104" s="353"/>
     </row>
     <row r="105" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C105" s="444"/>
-      <c r="D105" s="445"/>
-      <c r="E105" s="445"/>
-      <c r="F105" s="445"/>
-      <c r="G105" s="445"/>
-      <c r="H105" s="445"/>
-      <c r="I105" s="445"/>
-      <c r="J105" s="446"/>
+      <c r="C105" s="447"/>
+      <c r="D105" s="448"/>
+      <c r="E105" s="448"/>
+      <c r="F105" s="448"/>
+      <c r="G105" s="448"/>
+      <c r="H105" s="448"/>
+      <c r="I105" s="448"/>
+      <c r="J105" s="449"/>
       <c r="K105" s="353"/>
       <c r="L105" s="353"/>
     </row>
     <row r="106" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C106" s="447"/>
-      <c r="D106" s="448"/>
-      <c r="E106" s="448"/>
-      <c r="F106" s="448"/>
-      <c r="G106" s="448"/>
-      <c r="H106" s="448"/>
-      <c r="I106" s="448"/>
-      <c r="J106" s="449"/>
+      <c r="C106" s="450"/>
+      <c r="D106" s="451"/>
+      <c r="E106" s="451"/>
+      <c r="F106" s="451"/>
+      <c r="G106" s="451"/>
+      <c r="H106" s="451"/>
+      <c r="I106" s="451"/>
+      <c r="J106" s="452"/>
       <c r="K106" s="353"/>
       <c r="L106" s="353"/>
     </row>
@@ -19260,11 +19334,11 @@
       <c r="G111" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H111" s="450">
+      <c r="H111" s="442">
         <v>39</v>
       </c>
-      <c r="I111" s="450"/>
-      <c r="J111" s="451"/>
+      <c r="I111" s="442"/>
+      <c r="J111" s="443"/>
       <c r="K111" s="353"/>
       <c r="L111" s="353"/>
     </row>
@@ -19283,40 +19357,40 @@
       <c r="L112" s="353"/>
     </row>
     <row r="113" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C113" s="441" t="s">
+      <c r="C113" s="444" t="s">
         <v>367</v>
       </c>
-      <c r="D113" s="442"/>
-      <c r="E113" s="442"/>
-      <c r="F113" s="442"/>
-      <c r="G113" s="442"/>
-      <c r="H113" s="442"/>
-      <c r="I113" s="442"/>
-      <c r="J113" s="443"/>
+      <c r="D113" s="445"/>
+      <c r="E113" s="445"/>
+      <c r="F113" s="445"/>
+      <c r="G113" s="445"/>
+      <c r="H113" s="445"/>
+      <c r="I113" s="445"/>
+      <c r="J113" s="446"/>
       <c r="K113" s="353"/>
       <c r="L113" s="353"/>
     </row>
     <row r="114" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C114" s="444"/>
-      <c r="D114" s="445"/>
-      <c r="E114" s="445"/>
-      <c r="F114" s="445"/>
-      <c r="G114" s="445"/>
-      <c r="H114" s="445"/>
-      <c r="I114" s="445"/>
-      <c r="J114" s="446"/>
+      <c r="C114" s="447"/>
+      <c r="D114" s="448"/>
+      <c r="E114" s="448"/>
+      <c r="F114" s="448"/>
+      <c r="G114" s="448"/>
+      <c r="H114" s="448"/>
+      <c r="I114" s="448"/>
+      <c r="J114" s="449"/>
       <c r="K114" s="353"/>
       <c r="L114" s="353"/>
     </row>
     <row r="115" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C115" s="447"/>
-      <c r="D115" s="448"/>
-      <c r="E115" s="448"/>
-      <c r="F115" s="448"/>
-      <c r="G115" s="448"/>
-      <c r="H115" s="448"/>
-      <c r="I115" s="448"/>
-      <c r="J115" s="449"/>
+      <c r="C115" s="450"/>
+      <c r="D115" s="451"/>
+      <c r="E115" s="451"/>
+      <c r="F115" s="451"/>
+      <c r="G115" s="451"/>
+      <c r="H115" s="451"/>
+      <c r="I115" s="451"/>
+      <c r="J115" s="452"/>
     </row>
     <row r="117" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="118" spans="3:12" x14ac:dyDescent="0.25">
@@ -19366,11 +19440,11 @@
       <c r="G120" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H120" s="450">
+      <c r="H120" s="442">
         <v>96</v>
       </c>
-      <c r="I120" s="450"/>
-      <c r="J120" s="451"/>
+      <c r="I120" s="442"/>
+      <c r="J120" s="443"/>
       <c r="K120" s="353"/>
       <c r="L120" s="353"/>
     </row>
@@ -19389,40 +19463,40 @@
       <c r="L121" s="353"/>
     </row>
     <row r="122" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C122" s="441" t="s">
+      <c r="C122" s="444" t="s">
         <v>368</v>
       </c>
-      <c r="D122" s="442"/>
-      <c r="E122" s="442"/>
-      <c r="F122" s="442"/>
-      <c r="G122" s="442"/>
-      <c r="H122" s="442"/>
-      <c r="I122" s="442"/>
-      <c r="J122" s="443"/>
+      <c r="D122" s="445"/>
+      <c r="E122" s="445"/>
+      <c r="F122" s="445"/>
+      <c r="G122" s="445"/>
+      <c r="H122" s="445"/>
+      <c r="I122" s="445"/>
+      <c r="J122" s="446"/>
       <c r="K122" s="353"/>
       <c r="L122" s="353"/>
     </row>
     <row r="123" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C123" s="444"/>
-      <c r="D123" s="445"/>
-      <c r="E123" s="445"/>
-      <c r="F123" s="445"/>
-      <c r="G123" s="445"/>
-      <c r="H123" s="445"/>
-      <c r="I123" s="445"/>
-      <c r="J123" s="446"/>
+      <c r="C123" s="447"/>
+      <c r="D123" s="448"/>
+      <c r="E123" s="448"/>
+      <c r="F123" s="448"/>
+      <c r="G123" s="448"/>
+      <c r="H123" s="448"/>
+      <c r="I123" s="448"/>
+      <c r="J123" s="449"/>
       <c r="K123" s="353"/>
       <c r="L123" s="353"/>
     </row>
     <row r="124" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C124" s="447"/>
-      <c r="D124" s="448"/>
-      <c r="E124" s="448"/>
-      <c r="F124" s="448"/>
-      <c r="G124" s="448"/>
-      <c r="H124" s="448"/>
-      <c r="I124" s="448"/>
-      <c r="J124" s="449"/>
+      <c r="C124" s="450"/>
+      <c r="D124" s="451"/>
+      <c r="E124" s="451"/>
+      <c r="F124" s="451"/>
+      <c r="G124" s="451"/>
+      <c r="H124" s="451"/>
+      <c r="I124" s="451"/>
+      <c r="J124" s="452"/>
       <c r="K124" s="353"/>
       <c r="L124" s="353"/>
     </row>
@@ -19472,11 +19546,11 @@
       <c r="G129" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H129" s="450">
+      <c r="H129" s="442">
         <v>88</v>
       </c>
-      <c r="I129" s="450"/>
-      <c r="J129" s="451"/>
+      <c r="I129" s="442"/>
+      <c r="J129" s="443"/>
       <c r="K129" s="353"/>
       <c r="L129" s="353"/>
     </row>
@@ -19495,40 +19569,40 @@
       <c r="L130" s="353"/>
     </row>
     <row r="131" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C131" s="441" t="s">
+      <c r="C131" s="444" t="s">
         <v>369</v>
       </c>
-      <c r="D131" s="442"/>
-      <c r="E131" s="442"/>
-      <c r="F131" s="442"/>
-      <c r="G131" s="442"/>
-      <c r="H131" s="442"/>
-      <c r="I131" s="442"/>
-      <c r="J131" s="443"/>
+      <c r="D131" s="445"/>
+      <c r="E131" s="445"/>
+      <c r="F131" s="445"/>
+      <c r="G131" s="445"/>
+      <c r="H131" s="445"/>
+      <c r="I131" s="445"/>
+      <c r="J131" s="446"/>
       <c r="K131" s="353"/>
       <c r="L131" s="353"/>
     </row>
     <row r="132" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C132" s="444"/>
-      <c r="D132" s="445"/>
-      <c r="E132" s="445"/>
-      <c r="F132" s="445"/>
-      <c r="G132" s="445"/>
-      <c r="H132" s="445"/>
-      <c r="I132" s="445"/>
-      <c r="J132" s="446"/>
+      <c r="C132" s="447"/>
+      <c r="D132" s="448"/>
+      <c r="E132" s="448"/>
+      <c r="F132" s="448"/>
+      <c r="G132" s="448"/>
+      <c r="H132" s="448"/>
+      <c r="I132" s="448"/>
+      <c r="J132" s="449"/>
       <c r="K132" s="353"/>
       <c r="L132" s="353"/>
     </row>
     <row r="133" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C133" s="447"/>
-      <c r="D133" s="448"/>
-      <c r="E133" s="448"/>
-      <c r="F133" s="448"/>
-      <c r="G133" s="448"/>
-      <c r="H133" s="448"/>
-      <c r="I133" s="448"/>
-      <c r="J133" s="449"/>
+      <c r="C133" s="450"/>
+      <c r="D133" s="451"/>
+      <c r="E133" s="451"/>
+      <c r="F133" s="451"/>
+      <c r="G133" s="451"/>
+      <c r="H133" s="451"/>
+      <c r="I133" s="451"/>
+      <c r="J133" s="452"/>
       <c r="K133" s="353"/>
       <c r="L133" s="353"/>
     </row>
@@ -19584,11 +19658,11 @@
       <c r="G138" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H138" s="450">
+      <c r="H138" s="442">
         <v>77</v>
       </c>
-      <c r="I138" s="450"/>
-      <c r="J138" s="451"/>
+      <c r="I138" s="442"/>
+      <c r="J138" s="443"/>
       <c r="K138" s="353"/>
       <c r="L138" s="353"/>
     </row>
@@ -19607,40 +19681,40 @@
       <c r="L139" s="353"/>
     </row>
     <row r="140" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C140" s="441" t="s">
+      <c r="C140" s="444" t="s">
         <v>370</v>
       </c>
-      <c r="D140" s="442"/>
-      <c r="E140" s="442"/>
-      <c r="F140" s="442"/>
-      <c r="G140" s="442"/>
-      <c r="H140" s="442"/>
-      <c r="I140" s="442"/>
-      <c r="J140" s="443"/>
+      <c r="D140" s="445"/>
+      <c r="E140" s="445"/>
+      <c r="F140" s="445"/>
+      <c r="G140" s="445"/>
+      <c r="H140" s="445"/>
+      <c r="I140" s="445"/>
+      <c r="J140" s="446"/>
       <c r="K140" s="353"/>
       <c r="L140" s="353"/>
     </row>
     <row r="141" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C141" s="444"/>
-      <c r="D141" s="445"/>
-      <c r="E141" s="445"/>
-      <c r="F141" s="445"/>
-      <c r="G141" s="445"/>
-      <c r="H141" s="445"/>
-      <c r="I141" s="445"/>
-      <c r="J141" s="446"/>
+      <c r="C141" s="447"/>
+      <c r="D141" s="448"/>
+      <c r="E141" s="448"/>
+      <c r="F141" s="448"/>
+      <c r="G141" s="448"/>
+      <c r="H141" s="448"/>
+      <c r="I141" s="448"/>
+      <c r="J141" s="449"/>
       <c r="K141" s="353"/>
       <c r="L141" s="353"/>
     </row>
     <row r="142" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C142" s="447"/>
-      <c r="D142" s="448"/>
-      <c r="E142" s="448"/>
-      <c r="F142" s="448"/>
-      <c r="G142" s="448"/>
-      <c r="H142" s="448"/>
-      <c r="I142" s="448"/>
-      <c r="J142" s="449"/>
+      <c r="C142" s="450"/>
+      <c r="D142" s="451"/>
+      <c r="E142" s="451"/>
+      <c r="F142" s="451"/>
+      <c r="G142" s="451"/>
+      <c r="H142" s="451"/>
+      <c r="I142" s="451"/>
+      <c r="J142" s="452"/>
       <c r="K142" s="353"/>
       <c r="L142" s="353"/>
     </row>
@@ -19690,11 +19764,11 @@
       <c r="G147" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H147" s="450">
+      <c r="H147" s="442">
         <v>36</v>
       </c>
-      <c r="I147" s="450"/>
-      <c r="J147" s="451"/>
+      <c r="I147" s="442"/>
+      <c r="J147" s="443"/>
       <c r="K147" s="353"/>
       <c r="L147" s="353"/>
     </row>
@@ -19713,40 +19787,40 @@
       <c r="L148" s="353"/>
     </row>
     <row r="149" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C149" s="441" t="s">
+      <c r="C149" s="444" t="s">
         <v>371</v>
       </c>
-      <c r="D149" s="442"/>
-      <c r="E149" s="442"/>
-      <c r="F149" s="442"/>
-      <c r="G149" s="442"/>
-      <c r="H149" s="442"/>
-      <c r="I149" s="442"/>
-      <c r="J149" s="443"/>
+      <c r="D149" s="445"/>
+      <c r="E149" s="445"/>
+      <c r="F149" s="445"/>
+      <c r="G149" s="445"/>
+      <c r="H149" s="445"/>
+      <c r="I149" s="445"/>
+      <c r="J149" s="446"/>
       <c r="K149" s="353"/>
       <c r="L149" s="353"/>
     </row>
     <row r="150" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C150" s="444"/>
-      <c r="D150" s="445"/>
-      <c r="E150" s="445"/>
-      <c r="F150" s="445"/>
-      <c r="G150" s="445"/>
-      <c r="H150" s="445"/>
-      <c r="I150" s="445"/>
-      <c r="J150" s="446"/>
+      <c r="C150" s="447"/>
+      <c r="D150" s="448"/>
+      <c r="E150" s="448"/>
+      <c r="F150" s="448"/>
+      <c r="G150" s="448"/>
+      <c r="H150" s="448"/>
+      <c r="I150" s="448"/>
+      <c r="J150" s="449"/>
       <c r="K150" s="353"/>
       <c r="L150" s="353"/>
     </row>
     <row r="151" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C151" s="447"/>
-      <c r="D151" s="448"/>
-      <c r="E151" s="448"/>
-      <c r="F151" s="448"/>
-      <c r="G151" s="448"/>
-      <c r="H151" s="448"/>
-      <c r="I151" s="448"/>
-      <c r="J151" s="449"/>
+      <c r="C151" s="450"/>
+      <c r="D151" s="451"/>
+      <c r="E151" s="451"/>
+      <c r="F151" s="451"/>
+      <c r="G151" s="451"/>
+      <c r="H151" s="451"/>
+      <c r="I151" s="451"/>
+      <c r="J151" s="452"/>
     </row>
     <row r="153" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="154" spans="3:12" x14ac:dyDescent="0.25">
@@ -19794,11 +19868,11 @@
       <c r="G156" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H156" s="450">
+      <c r="H156" s="442">
         <v>130</v>
       </c>
-      <c r="I156" s="450"/>
-      <c r="J156" s="451"/>
+      <c r="I156" s="442"/>
+      <c r="J156" s="443"/>
       <c r="K156" s="353"/>
       <c r="L156" s="353"/>
     </row>
@@ -19817,40 +19891,40 @@
       <c r="L157" s="353"/>
     </row>
     <row r="158" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C158" s="441" t="s">
+      <c r="C158" s="444" t="s">
         <v>372</v>
       </c>
-      <c r="D158" s="442"/>
-      <c r="E158" s="442"/>
-      <c r="F158" s="442"/>
-      <c r="G158" s="442"/>
-      <c r="H158" s="442"/>
-      <c r="I158" s="442"/>
-      <c r="J158" s="443"/>
+      <c r="D158" s="445"/>
+      <c r="E158" s="445"/>
+      <c r="F158" s="445"/>
+      <c r="G158" s="445"/>
+      <c r="H158" s="445"/>
+      <c r="I158" s="445"/>
+      <c r="J158" s="446"/>
       <c r="K158" s="353"/>
       <c r="L158" s="353"/>
     </row>
     <row r="159" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C159" s="444"/>
-      <c r="D159" s="445"/>
-      <c r="E159" s="445"/>
-      <c r="F159" s="445"/>
-      <c r="G159" s="445"/>
-      <c r="H159" s="445"/>
-      <c r="I159" s="445"/>
-      <c r="J159" s="446"/>
+      <c r="C159" s="447"/>
+      <c r="D159" s="448"/>
+      <c r="E159" s="448"/>
+      <c r="F159" s="448"/>
+      <c r="G159" s="448"/>
+      <c r="H159" s="448"/>
+      <c r="I159" s="448"/>
+      <c r="J159" s="449"/>
       <c r="K159" s="353"/>
       <c r="L159" s="353"/>
     </row>
     <row r="160" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C160" s="447"/>
-      <c r="D160" s="448"/>
-      <c r="E160" s="448"/>
-      <c r="F160" s="448"/>
-      <c r="G160" s="448"/>
-      <c r="H160" s="448"/>
-      <c r="I160" s="448"/>
-      <c r="J160" s="449"/>
+      <c r="C160" s="450"/>
+      <c r="D160" s="451"/>
+      <c r="E160" s="451"/>
+      <c r="F160" s="451"/>
+      <c r="G160" s="451"/>
+      <c r="H160" s="451"/>
+      <c r="I160" s="451"/>
+      <c r="J160" s="452"/>
       <c r="K160" s="353"/>
       <c r="L160" s="353"/>
     </row>
@@ -19902,11 +19976,11 @@
       <c r="G165" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H165" s="450">
+      <c r="H165" s="442">
         <v>41</v>
       </c>
-      <c r="I165" s="450"/>
-      <c r="J165" s="451"/>
+      <c r="I165" s="442"/>
+      <c r="J165" s="443"/>
       <c r="K165" s="353"/>
       <c r="L165" s="353"/>
     </row>
@@ -19925,40 +19999,40 @@
       <c r="L166" s="353"/>
     </row>
     <row r="167" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C167" s="441" t="s">
+      <c r="C167" s="444" t="s">
         <v>373</v>
       </c>
-      <c r="D167" s="442"/>
-      <c r="E167" s="442"/>
-      <c r="F167" s="442"/>
-      <c r="G167" s="442"/>
-      <c r="H167" s="442"/>
-      <c r="I167" s="442"/>
-      <c r="J167" s="443"/>
+      <c r="D167" s="445"/>
+      <c r="E167" s="445"/>
+      <c r="F167" s="445"/>
+      <c r="G167" s="445"/>
+      <c r="H167" s="445"/>
+      <c r="I167" s="445"/>
+      <c r="J167" s="446"/>
       <c r="K167" s="353"/>
       <c r="L167" s="353"/>
     </row>
     <row r="168" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C168" s="444"/>
-      <c r="D168" s="445"/>
-      <c r="E168" s="445"/>
-      <c r="F168" s="445"/>
-      <c r="G168" s="445"/>
-      <c r="H168" s="445"/>
-      <c r="I168" s="445"/>
-      <c r="J168" s="446"/>
+      <c r="C168" s="447"/>
+      <c r="D168" s="448"/>
+      <c r="E168" s="448"/>
+      <c r="F168" s="448"/>
+      <c r="G168" s="448"/>
+      <c r="H168" s="448"/>
+      <c r="I168" s="448"/>
+      <c r="J168" s="449"/>
       <c r="K168" s="353"/>
       <c r="L168" s="353"/>
     </row>
     <row r="169" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C169" s="447"/>
-      <c r="D169" s="448"/>
-      <c r="E169" s="448"/>
-      <c r="F169" s="448"/>
-      <c r="G169" s="448"/>
-      <c r="H169" s="448"/>
-      <c r="I169" s="448"/>
-      <c r="J169" s="449"/>
+      <c r="C169" s="450"/>
+      <c r="D169" s="451"/>
+      <c r="E169" s="451"/>
+      <c r="F169" s="451"/>
+      <c r="G169" s="451"/>
+      <c r="H169" s="451"/>
+      <c r="I169" s="451"/>
+      <c r="J169" s="452"/>
       <c r="K169" s="353"/>
       <c r="L169" s="353"/>
     </row>
@@ -20012,11 +20086,11 @@
       <c r="G174" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H174" s="450">
+      <c r="H174" s="442">
         <v>139</v>
       </c>
-      <c r="I174" s="450"/>
-      <c r="J174" s="451"/>
+      <c r="I174" s="442"/>
+      <c r="J174" s="443"/>
       <c r="K174" s="353"/>
       <c r="L174" s="353"/>
     </row>
@@ -20035,40 +20109,40 @@
       <c r="L175" s="353"/>
     </row>
     <row r="176" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C176" s="441" t="s">
+      <c r="C176" s="444" t="s">
         <v>375</v>
       </c>
-      <c r="D176" s="442"/>
-      <c r="E176" s="442"/>
-      <c r="F176" s="442"/>
-      <c r="G176" s="442"/>
-      <c r="H176" s="442"/>
-      <c r="I176" s="442"/>
-      <c r="J176" s="443"/>
+      <c r="D176" s="445"/>
+      <c r="E176" s="445"/>
+      <c r="F176" s="445"/>
+      <c r="G176" s="445"/>
+      <c r="H176" s="445"/>
+      <c r="I176" s="445"/>
+      <c r="J176" s="446"/>
       <c r="K176" s="353"/>
       <c r="L176" s="353"/>
     </row>
     <row r="177" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C177" s="444"/>
-      <c r="D177" s="445"/>
-      <c r="E177" s="445"/>
-      <c r="F177" s="445"/>
-      <c r="G177" s="445"/>
-      <c r="H177" s="445"/>
-      <c r="I177" s="445"/>
-      <c r="J177" s="446"/>
+      <c r="C177" s="447"/>
+      <c r="D177" s="448"/>
+      <c r="E177" s="448"/>
+      <c r="F177" s="448"/>
+      <c r="G177" s="448"/>
+      <c r="H177" s="448"/>
+      <c r="I177" s="448"/>
+      <c r="J177" s="449"/>
       <c r="K177" s="353"/>
       <c r="L177" s="353"/>
     </row>
     <row r="178" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C178" s="447"/>
-      <c r="D178" s="448"/>
-      <c r="E178" s="448"/>
-      <c r="F178" s="448"/>
-      <c r="G178" s="448"/>
-      <c r="H178" s="448"/>
-      <c r="I178" s="448"/>
-      <c r="J178" s="449"/>
+      <c r="C178" s="450"/>
+      <c r="D178" s="451"/>
+      <c r="E178" s="451"/>
+      <c r="F178" s="451"/>
+      <c r="G178" s="451"/>
+      <c r="H178" s="451"/>
+      <c r="I178" s="451"/>
+      <c r="J178" s="452"/>
     </row>
     <row r="180" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="181" spans="3:12" x14ac:dyDescent="0.25">
@@ -20118,11 +20192,11 @@
       <c r="G183" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H183" s="450">
+      <c r="H183" s="442">
         <v>28</v>
       </c>
-      <c r="I183" s="450"/>
-      <c r="J183" s="451"/>
+      <c r="I183" s="442"/>
+      <c r="J183" s="443"/>
       <c r="K183" s="353"/>
       <c r="L183" s="353"/>
     </row>
@@ -20141,40 +20215,40 @@
       <c r="L184" s="353"/>
     </row>
     <row r="185" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C185" s="441" t="s">
+      <c r="C185" s="444" t="s">
         <v>376</v>
       </c>
-      <c r="D185" s="442"/>
-      <c r="E185" s="442"/>
-      <c r="F185" s="442"/>
-      <c r="G185" s="442"/>
-      <c r="H185" s="442"/>
-      <c r="I185" s="442"/>
-      <c r="J185" s="443"/>
+      <c r="D185" s="445"/>
+      <c r="E185" s="445"/>
+      <c r="F185" s="445"/>
+      <c r="G185" s="445"/>
+      <c r="H185" s="445"/>
+      <c r="I185" s="445"/>
+      <c r="J185" s="446"/>
       <c r="K185" s="353"/>
       <c r="L185" s="353"/>
     </row>
     <row r="186" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C186" s="444"/>
-      <c r="D186" s="445"/>
-      <c r="E186" s="445"/>
-      <c r="F186" s="445"/>
-      <c r="G186" s="445"/>
-      <c r="H186" s="445"/>
-      <c r="I186" s="445"/>
-      <c r="J186" s="446"/>
+      <c r="C186" s="447"/>
+      <c r="D186" s="448"/>
+      <c r="E186" s="448"/>
+      <c r="F186" s="448"/>
+      <c r="G186" s="448"/>
+      <c r="H186" s="448"/>
+      <c r="I186" s="448"/>
+      <c r="J186" s="449"/>
       <c r="K186" s="353"/>
       <c r="L186" s="353"/>
     </row>
     <row r="187" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C187" s="447"/>
-      <c r="D187" s="448"/>
-      <c r="E187" s="448"/>
-      <c r="F187" s="448"/>
-      <c r="G187" s="448"/>
-      <c r="H187" s="448"/>
-      <c r="I187" s="448"/>
-      <c r="J187" s="449"/>
+      <c r="C187" s="450"/>
+      <c r="D187" s="451"/>
+      <c r="E187" s="451"/>
+      <c r="F187" s="451"/>
+      <c r="G187" s="451"/>
+      <c r="H187" s="451"/>
+      <c r="I187" s="451"/>
+      <c r="J187" s="452"/>
     </row>
     <row r="189" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="190" spans="3:12" x14ac:dyDescent="0.25">
@@ -20224,11 +20298,11 @@
       <c r="G192" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H192" s="450">
+      <c r="H192" s="442">
         <v>14</v>
       </c>
-      <c r="I192" s="450"/>
-      <c r="J192" s="451"/>
+      <c r="I192" s="442"/>
+      <c r="J192" s="443"/>
       <c r="K192" s="353"/>
       <c r="L192" s="353"/>
     </row>
@@ -20247,40 +20321,40 @@
       <c r="L193" s="353"/>
     </row>
     <row r="194" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C194" s="441" t="s">
+      <c r="C194" s="444" t="s">
         <v>377</v>
       </c>
-      <c r="D194" s="442"/>
-      <c r="E194" s="442"/>
-      <c r="F194" s="442"/>
-      <c r="G194" s="442"/>
-      <c r="H194" s="442"/>
-      <c r="I194" s="442"/>
-      <c r="J194" s="443"/>
+      <c r="D194" s="445"/>
+      <c r="E194" s="445"/>
+      <c r="F194" s="445"/>
+      <c r="G194" s="445"/>
+      <c r="H194" s="445"/>
+      <c r="I194" s="445"/>
+      <c r="J194" s="446"/>
       <c r="K194" s="353"/>
       <c r="L194" s="353"/>
     </row>
     <row r="195" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C195" s="444"/>
-      <c r="D195" s="445"/>
-      <c r="E195" s="445"/>
-      <c r="F195" s="445"/>
-      <c r="G195" s="445"/>
-      <c r="H195" s="445"/>
-      <c r="I195" s="445"/>
-      <c r="J195" s="446"/>
+      <c r="C195" s="447"/>
+      <c r="D195" s="448"/>
+      <c r="E195" s="448"/>
+      <c r="F195" s="448"/>
+      <c r="G195" s="448"/>
+      <c r="H195" s="448"/>
+      <c r="I195" s="448"/>
+      <c r="J195" s="449"/>
       <c r="K195" s="353"/>
       <c r="L195" s="353"/>
     </row>
     <row r="196" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C196" s="447"/>
-      <c r="D196" s="448"/>
-      <c r="E196" s="448"/>
-      <c r="F196" s="448"/>
-      <c r="G196" s="448"/>
-      <c r="H196" s="448"/>
-      <c r="I196" s="448"/>
-      <c r="J196" s="449"/>
+      <c r="C196" s="450"/>
+      <c r="D196" s="451"/>
+      <c r="E196" s="451"/>
+      <c r="F196" s="451"/>
+      <c r="G196" s="451"/>
+      <c r="H196" s="451"/>
+      <c r="I196" s="451"/>
+      <c r="J196" s="452"/>
       <c r="K196" s="353"/>
       <c r="L196" s="353"/>
     </row>
@@ -20330,11 +20404,11 @@
       <c r="G201" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H201" s="450">
+      <c r="H201" s="442">
         <v>61</v>
       </c>
-      <c r="I201" s="450"/>
-      <c r="J201" s="451"/>
+      <c r="I201" s="442"/>
+      <c r="J201" s="443"/>
       <c r="K201" s="353"/>
       <c r="L201" s="353"/>
     </row>
@@ -20353,40 +20427,40 @@
       <c r="L202" s="353"/>
     </row>
     <row r="203" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C203" s="441" t="s">
+      <c r="C203" s="444" t="s">
         <v>379</v>
       </c>
-      <c r="D203" s="442"/>
-      <c r="E203" s="442"/>
-      <c r="F203" s="442"/>
-      <c r="G203" s="442"/>
-      <c r="H203" s="442"/>
-      <c r="I203" s="442"/>
-      <c r="J203" s="443"/>
+      <c r="D203" s="445"/>
+      <c r="E203" s="445"/>
+      <c r="F203" s="445"/>
+      <c r="G203" s="445"/>
+      <c r="H203" s="445"/>
+      <c r="I203" s="445"/>
+      <c r="J203" s="446"/>
       <c r="K203" s="353"/>
       <c r="L203" s="353"/>
     </row>
     <row r="204" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C204" s="444"/>
-      <c r="D204" s="445"/>
-      <c r="E204" s="445"/>
-      <c r="F204" s="445"/>
-      <c r="G204" s="445"/>
-      <c r="H204" s="445"/>
-      <c r="I204" s="445"/>
-      <c r="J204" s="446"/>
+      <c r="C204" s="447"/>
+      <c r="D204" s="448"/>
+      <c r="E204" s="448"/>
+      <c r="F204" s="448"/>
+      <c r="G204" s="448"/>
+      <c r="H204" s="448"/>
+      <c r="I204" s="448"/>
+      <c r="J204" s="449"/>
       <c r="K204" s="353"/>
       <c r="L204" s="353"/>
     </row>
     <row r="205" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C205" s="447"/>
-      <c r="D205" s="448"/>
-      <c r="E205" s="448"/>
-      <c r="F205" s="448"/>
-      <c r="G205" s="448"/>
-      <c r="H205" s="448"/>
-      <c r="I205" s="448"/>
-      <c r="J205" s="449"/>
+      <c r="C205" s="450"/>
+      <c r="D205" s="451"/>
+      <c r="E205" s="451"/>
+      <c r="F205" s="451"/>
+      <c r="G205" s="451"/>
+      <c r="H205" s="451"/>
+      <c r="I205" s="451"/>
+      <c r="J205" s="452"/>
       <c r="K205" s="353"/>
       <c r="L205" s="353"/>
     </row>
@@ -20438,11 +20512,11 @@
       <c r="G210" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H210" s="450">
+      <c r="H210" s="442">
         <v>109</v>
       </c>
-      <c r="I210" s="450"/>
-      <c r="J210" s="451"/>
+      <c r="I210" s="442"/>
+      <c r="J210" s="443"/>
       <c r="K210" s="353"/>
       <c r="L210" s="353"/>
     </row>
@@ -20461,40 +20535,40 @@
       <c r="L211" s="353"/>
     </row>
     <row r="212" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C212" s="441" t="s">
+      <c r="C212" s="444" t="s">
         <v>383</v>
       </c>
-      <c r="D212" s="442"/>
-      <c r="E212" s="442"/>
-      <c r="F212" s="442"/>
-      <c r="G212" s="442"/>
-      <c r="H212" s="442"/>
-      <c r="I212" s="442"/>
-      <c r="J212" s="443"/>
+      <c r="D212" s="445"/>
+      <c r="E212" s="445"/>
+      <c r="F212" s="445"/>
+      <c r="G212" s="445"/>
+      <c r="H212" s="445"/>
+      <c r="I212" s="445"/>
+      <c r="J212" s="446"/>
       <c r="K212" s="353"/>
       <c r="L212" s="353"/>
     </row>
     <row r="213" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C213" s="444"/>
-      <c r="D213" s="445"/>
-      <c r="E213" s="445"/>
-      <c r="F213" s="445"/>
-      <c r="G213" s="445"/>
-      <c r="H213" s="445"/>
-      <c r="I213" s="445"/>
-      <c r="J213" s="446"/>
+      <c r="C213" s="447"/>
+      <c r="D213" s="448"/>
+      <c r="E213" s="448"/>
+      <c r="F213" s="448"/>
+      <c r="G213" s="448"/>
+      <c r="H213" s="448"/>
+      <c r="I213" s="448"/>
+      <c r="J213" s="449"/>
       <c r="K213" s="353"/>
       <c r="L213" s="353"/>
     </row>
     <row r="214" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C214" s="447"/>
-      <c r="D214" s="448"/>
-      <c r="E214" s="448"/>
-      <c r="F214" s="448"/>
-      <c r="G214" s="448"/>
-      <c r="H214" s="448"/>
-      <c r="I214" s="448"/>
-      <c r="J214" s="449"/>
+      <c r="C214" s="450"/>
+      <c r="D214" s="451"/>
+      <c r="E214" s="451"/>
+      <c r="F214" s="451"/>
+      <c r="G214" s="451"/>
+      <c r="H214" s="451"/>
+      <c r="I214" s="451"/>
+      <c r="J214" s="452"/>
       <c r="K214" s="353"/>
       <c r="L214" s="353"/>
     </row>
@@ -20548,11 +20622,11 @@
       <c r="G219" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H219" s="450">
+      <c r="H219" s="442">
         <v>71</v>
       </c>
-      <c r="I219" s="450"/>
-      <c r="J219" s="451"/>
+      <c r="I219" s="442"/>
+      <c r="J219" s="443"/>
       <c r="K219" s="353"/>
       <c r="L219" s="353"/>
       <c r="M219" s="353"/>
@@ -20573,42 +20647,42 @@
       <c r="M220" s="353"/>
     </row>
     <row r="221" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C221" s="441" t="s">
+      <c r="C221" s="444" t="s">
         <v>385</v>
       </c>
-      <c r="D221" s="442"/>
-      <c r="E221" s="442"/>
-      <c r="F221" s="442"/>
-      <c r="G221" s="442"/>
-      <c r="H221" s="442"/>
-      <c r="I221" s="442"/>
-      <c r="J221" s="443"/>
+      <c r="D221" s="445"/>
+      <c r="E221" s="445"/>
+      <c r="F221" s="445"/>
+      <c r="G221" s="445"/>
+      <c r="H221" s="445"/>
+      <c r="I221" s="445"/>
+      <c r="J221" s="446"/>
       <c r="K221" s="353"/>
       <c r="L221" s="353"/>
       <c r="M221" s="353"/>
     </row>
     <row r="222" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C222" s="444"/>
-      <c r="D222" s="445"/>
-      <c r="E222" s="445"/>
-      <c r="F222" s="445"/>
-      <c r="G222" s="445"/>
-      <c r="H222" s="445"/>
-      <c r="I222" s="445"/>
-      <c r="J222" s="446"/>
+      <c r="C222" s="447"/>
+      <c r="D222" s="448"/>
+      <c r="E222" s="448"/>
+      <c r="F222" s="448"/>
+      <c r="G222" s="448"/>
+      <c r="H222" s="448"/>
+      <c r="I222" s="448"/>
+      <c r="J222" s="449"/>
       <c r="K222" s="353"/>
       <c r="L222" s="353"/>
       <c r="M222" s="353"/>
     </row>
     <row r="223" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C223" s="447"/>
-      <c r="D223" s="448"/>
-      <c r="E223" s="448"/>
-      <c r="F223" s="448"/>
-      <c r="G223" s="448"/>
-      <c r="H223" s="448"/>
-      <c r="I223" s="448"/>
-      <c r="J223" s="449"/>
+      <c r="C223" s="450"/>
+      <c r="D223" s="451"/>
+      <c r="E223" s="451"/>
+      <c r="F223" s="451"/>
+      <c r="G223" s="451"/>
+      <c r="H223" s="451"/>
+      <c r="I223" s="451"/>
+      <c r="J223" s="452"/>
       <c r="K223" s="353"/>
       <c r="L223" s="353"/>
       <c r="M223" s="353"/>
@@ -20661,11 +20735,11 @@
       <c r="G228" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H228" s="450">
+      <c r="H228" s="442">
         <v>59</v>
       </c>
-      <c r="I228" s="450"/>
-      <c r="J228" s="451"/>
+      <c r="I228" s="442"/>
+      <c r="J228" s="443"/>
       <c r="K228" s="353"/>
       <c r="L228" s="353"/>
     </row>
@@ -20684,40 +20758,40 @@
       <c r="L229" s="353"/>
     </row>
     <row r="230" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C230" s="441" t="s">
+      <c r="C230" s="444" t="s">
         <v>384</v>
       </c>
-      <c r="D230" s="442"/>
-      <c r="E230" s="442"/>
-      <c r="F230" s="442"/>
-      <c r="G230" s="442"/>
-      <c r="H230" s="442"/>
-      <c r="I230" s="442"/>
-      <c r="J230" s="443"/>
+      <c r="D230" s="445"/>
+      <c r="E230" s="445"/>
+      <c r="F230" s="445"/>
+      <c r="G230" s="445"/>
+      <c r="H230" s="445"/>
+      <c r="I230" s="445"/>
+      <c r="J230" s="446"/>
       <c r="K230" s="353"/>
       <c r="L230" s="353"/>
     </row>
     <row r="231" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C231" s="444"/>
-      <c r="D231" s="445"/>
-      <c r="E231" s="445"/>
-      <c r="F231" s="445"/>
-      <c r="G231" s="445"/>
-      <c r="H231" s="445"/>
-      <c r="I231" s="445"/>
-      <c r="J231" s="446"/>
+      <c r="C231" s="447"/>
+      <c r="D231" s="448"/>
+      <c r="E231" s="448"/>
+      <c r="F231" s="448"/>
+      <c r="G231" s="448"/>
+      <c r="H231" s="448"/>
+      <c r="I231" s="448"/>
+      <c r="J231" s="449"/>
       <c r="K231" s="353"/>
       <c r="L231" s="353"/>
     </row>
     <row r="232" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C232" s="447"/>
-      <c r="D232" s="448"/>
-      <c r="E232" s="448"/>
-      <c r="F232" s="448"/>
-      <c r="G232" s="448"/>
-      <c r="H232" s="448"/>
-      <c r="I232" s="448"/>
-      <c r="J232" s="449"/>
+      <c r="C232" s="450"/>
+      <c r="D232" s="451"/>
+      <c r="E232" s="451"/>
+      <c r="F232" s="451"/>
+      <c r="G232" s="451"/>
+      <c r="H232" s="451"/>
+      <c r="I232" s="451"/>
+      <c r="J232" s="452"/>
       <c r="K232" s="353"/>
       <c r="L232" s="353"/>
     </row>
@@ -20750,11 +20824,11 @@
         <v>26</v>
       </c>
       <c r="J236" s="60"/>
-      <c r="K236" s="452" t="s">
+      <c r="K236" s="453" t="s">
         <v>398</v>
       </c>
-      <c r="L236" s="453"/>
-      <c r="M236" s="453"/>
+      <c r="L236" s="454"/>
+      <c r="M236" s="454"/>
     </row>
     <row r="237" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C237" s="352" t="s">
@@ -20770,14 +20844,14 @@
       <c r="G237" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H237" s="450">
+      <c r="H237" s="442">
         <v>41</v>
       </c>
-      <c r="I237" s="450"/>
-      <c r="J237" s="451"/>
-      <c r="K237" s="452"/>
-      <c r="L237" s="453"/>
-      <c r="M237" s="453"/>
+      <c r="I237" s="442"/>
+      <c r="J237" s="443"/>
+      <c r="K237" s="453"/>
+      <c r="L237" s="454"/>
+      <c r="M237" s="454"/>
     </row>
     <row r="238" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C238" s="352" t="s">
@@ -20790,70 +20864,76 @@
       <c r="H238" s="33"/>
       <c r="I238" s="33"/>
       <c r="J238" s="61"/>
-      <c r="K238" s="452"/>
-      <c r="L238" s="453"/>
-      <c r="M238" s="453"/>
+      <c r="K238" s="453"/>
+      <c r="L238" s="454"/>
+      <c r="M238" s="454"/>
     </row>
     <row r="239" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C239" s="441" t="s">
+      <c r="C239" s="444" t="s">
         <v>397</v>
       </c>
-      <c r="D239" s="442"/>
-      <c r="E239" s="442"/>
-      <c r="F239" s="442"/>
-      <c r="G239" s="442"/>
-      <c r="H239" s="442"/>
-      <c r="I239" s="442"/>
-      <c r="J239" s="443"/>
-      <c r="K239" s="452"/>
-      <c r="L239" s="453"/>
-      <c r="M239" s="453"/>
+      <c r="D239" s="445"/>
+      <c r="E239" s="445"/>
+      <c r="F239" s="445"/>
+      <c r="G239" s="445"/>
+      <c r="H239" s="445"/>
+      <c r="I239" s="445"/>
+      <c r="J239" s="446"/>
+      <c r="K239" s="453"/>
+      <c r="L239" s="454"/>
+      <c r="M239" s="454"/>
     </row>
     <row r="240" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C240" s="444"/>
-      <c r="D240" s="445"/>
-      <c r="E240" s="445"/>
-      <c r="F240" s="445"/>
-      <c r="G240" s="445"/>
-      <c r="H240" s="445"/>
-      <c r="I240" s="445"/>
-      <c r="J240" s="446"/>
-      <c r="K240" s="452"/>
-      <c r="L240" s="453"/>
-      <c r="M240" s="453"/>
+      <c r="C240" s="447"/>
+      <c r="D240" s="448"/>
+      <c r="E240" s="448"/>
+      <c r="F240" s="448"/>
+      <c r="G240" s="448"/>
+      <c r="H240" s="448"/>
+      <c r="I240" s="448"/>
+      <c r="J240" s="449"/>
+      <c r="K240" s="453"/>
+      <c r="L240" s="454"/>
+      <c r="M240" s="454"/>
     </row>
     <row r="241" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C241" s="447"/>
-      <c r="D241" s="448"/>
-      <c r="E241" s="448"/>
-      <c r="F241" s="448"/>
-      <c r="G241" s="448"/>
-      <c r="H241" s="448"/>
-      <c r="I241" s="448"/>
-      <c r="J241" s="449"/>
-      <c r="K241" s="452"/>
-      <c r="L241" s="453"/>
-      <c r="M241" s="453"/>
+      <c r="C241" s="450"/>
+      <c r="D241" s="451"/>
+      <c r="E241" s="451"/>
+      <c r="F241" s="451"/>
+      <c r="G241" s="451"/>
+      <c r="H241" s="451"/>
+      <c r="I241" s="451"/>
+      <c r="J241" s="452"/>
+      <c r="K241" s="453"/>
+      <c r="L241" s="454"/>
+      <c r="M241" s="454"/>
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="H237:J237"/>
-    <mergeCell ref="C239:J241"/>
-    <mergeCell ref="K236:M241"/>
-    <mergeCell ref="H228:J228"/>
-    <mergeCell ref="C230:J232"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="C6:J8"/>
-    <mergeCell ref="H57:J57"/>
-    <mergeCell ref="C59:J61"/>
-    <mergeCell ref="C24:J26"/>
-    <mergeCell ref="H31:J31"/>
-    <mergeCell ref="C33:J35"/>
-    <mergeCell ref="H40:J40"/>
-    <mergeCell ref="C42:J44"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="C15:J17"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="K64:L69"/>
+    <mergeCell ref="C221:J223"/>
+    <mergeCell ref="C212:J214"/>
+    <mergeCell ref="H49:J49"/>
+    <mergeCell ref="C51:J53"/>
+    <mergeCell ref="H192:J192"/>
+    <mergeCell ref="C194:J196"/>
+    <mergeCell ref="H201:J201"/>
+    <mergeCell ref="C203:J205"/>
+    <mergeCell ref="H210:J210"/>
+    <mergeCell ref="H183:J183"/>
+    <mergeCell ref="C185:J187"/>
+    <mergeCell ref="C158:J160"/>
+    <mergeCell ref="H165:J165"/>
+    <mergeCell ref="C167:J169"/>
+    <mergeCell ref="H174:J174"/>
+    <mergeCell ref="H147:J147"/>
+    <mergeCell ref="C122:J124"/>
+    <mergeCell ref="H219:J219"/>
+    <mergeCell ref="H129:J129"/>
+    <mergeCell ref="C131:J133"/>
+    <mergeCell ref="H138:J138"/>
+    <mergeCell ref="C140:J142"/>
     <mergeCell ref="H66:J66"/>
     <mergeCell ref="C68:J70"/>
     <mergeCell ref="C176:J178"/>
@@ -20870,29 +20950,23 @@
     <mergeCell ref="H102:J102"/>
     <mergeCell ref="C149:J151"/>
     <mergeCell ref="H120:J120"/>
-    <mergeCell ref="H147:J147"/>
-    <mergeCell ref="C122:J124"/>
-    <mergeCell ref="H219:J219"/>
-    <mergeCell ref="H129:J129"/>
-    <mergeCell ref="C131:J133"/>
-    <mergeCell ref="H138:J138"/>
-    <mergeCell ref="C140:J142"/>
-    <mergeCell ref="K64:L69"/>
-    <mergeCell ref="C221:J223"/>
-    <mergeCell ref="C212:J214"/>
-    <mergeCell ref="H49:J49"/>
-    <mergeCell ref="C51:J53"/>
-    <mergeCell ref="H192:J192"/>
-    <mergeCell ref="C194:J196"/>
-    <mergeCell ref="H201:J201"/>
-    <mergeCell ref="C203:J205"/>
-    <mergeCell ref="H210:J210"/>
-    <mergeCell ref="H183:J183"/>
-    <mergeCell ref="C185:J187"/>
-    <mergeCell ref="C158:J160"/>
-    <mergeCell ref="H165:J165"/>
-    <mergeCell ref="C167:J169"/>
-    <mergeCell ref="H174:J174"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="C6:J8"/>
+    <mergeCell ref="H57:J57"/>
+    <mergeCell ref="C59:J61"/>
+    <mergeCell ref="C24:J26"/>
+    <mergeCell ref="H31:J31"/>
+    <mergeCell ref="C33:J35"/>
+    <mergeCell ref="H40:J40"/>
+    <mergeCell ref="C42:J44"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="C15:J17"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="H237:J237"/>
+    <mergeCell ref="C239:J241"/>
+    <mergeCell ref="K236:M241"/>
+    <mergeCell ref="H228:J228"/>
+    <mergeCell ref="C230:J232"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/BRISAS/EXPENSAS/2026/SEPTIEMBRE/BRISAS-SEPTIEMBRE.xlsx
+++ b/BRISAS/EXPENSAS/2026/SEPTIEMBRE/BRISAS-SEPTIEMBRE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\BRISAS\EXPENSAS\2026\SEPTIEMBRE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD379B6D-709A-4B6C-996A-C7A7216AB5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493A2C54-BAF4-4002-9795-A2B74C22D2E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -2763,6 +2763,41 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2823,54 +2858,36 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="44" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="169" fontId="22" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2929,27 +2946,10 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="5" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3410,34 +3410,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="309"/>
-      <c r="B1" s="304" t="s">
+      <c r="A1" s="322"/>
+      <c r="B1" s="317" t="s">
         <v>155</v>
       </c>
-      <c r="C1" s="305"/>
-      <c r="D1" s="305"/>
-      <c r="E1" s="306"/>
+      <c r="C1" s="318"/>
+      <c r="D1" s="318"/>
+      <c r="E1" s="319"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="310"/>
-      <c r="B2" s="304" t="s">
+      <c r="A2" s="323"/>
+      <c r="B2" s="317" t="s">
         <v>157</v>
       </c>
-      <c r="C2" s="305"/>
-      <c r="D2" s="305"/>
-      <c r="E2" s="306"/>
+      <c r="C2" s="318"/>
+      <c r="D2" s="318"/>
+      <c r="E2" s="319"/>
     </row>
     <row r="3" spans="1:5" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="310"/>
-      <c r="B3" s="321" t="s">
+      <c r="A3" s="323"/>
+      <c r="B3" s="334" t="s">
         <v>153</v>
       </c>
-      <c r="C3" s="322"/>
-      <c r="D3" s="322"/>
-      <c r="E3" s="323"/>
+      <c r="C3" s="335"/>
+      <c r="D3" s="335"/>
+      <c r="E3" s="336"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="310"/>
+      <c r="A4" s="323"/>
       <c r="B4" s="264" t="s">
         <v>154</v>
       </c>
@@ -3446,7 +3446,7 @@
       <c r="E4" s="265"/>
     </row>
     <row r="5" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="310"/>
+      <c r="A5" s="323"/>
       <c r="B5" s="266" t="s">
         <v>349</v>
       </c>
@@ -3455,7 +3455,7 @@
       <c r="E5" s="268"/>
     </row>
     <row r="6" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="310"/>
+      <c r="A6" s="323"/>
       <c r="B6" s="269" t="s">
         <v>280</v>
       </c>
@@ -3464,7 +3464,7 @@
       <c r="E6" s="268"/>
     </row>
     <row r="7" spans="1:5" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="310"/>
+      <c r="A7" s="323"/>
       <c r="B7" s="269" t="s">
         <v>279</v>
       </c>
@@ -3473,13 +3473,13 @@
       <c r="E7" s="268"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="311"/>
-      <c r="B8" s="307" t="s">
+      <c r="A8" s="324"/>
+      <c r="B8" s="320" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="307"/>
-      <c r="D8" s="307"/>
-      <c r="E8" s="308"/>
+      <c r="C8" s="320"/>
+      <c r="D8" s="320"/>
+      <c r="E8" s="321"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="27"/>
@@ -3489,27 +3489,27 @@
       <c r="E9" s="27"/>
     </row>
     <row r="10" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="312" t="s">
+      <c r="A10" s="325" t="s">
         <v>348</v>
       </c>
-      <c r="B10" s="313"/>
-      <c r="C10" s="313"/>
-      <c r="D10" s="313"/>
-      <c r="E10" s="314"/>
+      <c r="B10" s="326"/>
+      <c r="C10" s="326"/>
+      <c r="D10" s="326"/>
+      <c r="E10" s="327"/>
     </row>
     <row r="11" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="315"/>
-      <c r="B11" s="316"/>
-      <c r="C11" s="316"/>
-      <c r="D11" s="316"/>
-      <c r="E11" s="317"/>
+      <c r="A11" s="328"/>
+      <c r="B11" s="329"/>
+      <c r="C11" s="329"/>
+      <c r="D11" s="329"/>
+      <c r="E11" s="330"/>
     </row>
     <row r="12" spans="1:5" ht="14.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="318"/>
-      <c r="B12" s="319"/>
-      <c r="C12" s="319"/>
-      <c r="D12" s="319"/>
-      <c r="E12" s="320"/>
+      <c r="A12" s="331"/>
+      <c r="B12" s="332"/>
+      <c r="C12" s="332"/>
+      <c r="D12" s="332"/>
+      <c r="E12" s="333"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="27"/>
@@ -3526,34 +3526,34 @@
       <c r="E14" s="27"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="324" t="s">
+      <c r="A15" s="312" t="s">
         <v>238</v>
       </c>
-      <c r="B15" s="324"/>
-      <c r="C15" s="324"/>
-      <c r="D15" s="324"/>
-      <c r="E15" s="324"/>
+      <c r="B15" s="312"/>
+      <c r="C15" s="312"/>
+      <c r="D15" s="312"/>
+      <c r="E15" s="312"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="324"/>
-      <c r="B16" s="324"/>
-      <c r="C16" s="324"/>
-      <c r="D16" s="324"/>
-      <c r="E16" s="324"/>
+      <c r="A16" s="312"/>
+      <c r="B16" s="312"/>
+      <c r="C16" s="312"/>
+      <c r="D16" s="312"/>
+      <c r="E16" s="312"/>
     </row>
     <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="324"/>
-      <c r="B17" s="324"/>
-      <c r="C17" s="324"/>
-      <c r="D17" s="324"/>
-      <c r="E17" s="324"/>
+      <c r="A17" s="312"/>
+      <c r="B17" s="312"/>
+      <c r="C17" s="312"/>
+      <c r="D17" s="312"/>
+      <c r="E17" s="312"/>
     </row>
     <row r="18" spans="1:8" ht="243" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="324"/>
-      <c r="B18" s="324"/>
-      <c r="C18" s="324"/>
-      <c r="D18" s="324"/>
-      <c r="E18" s="324"/>
+      <c r="A18" s="312"/>
+      <c r="B18" s="312"/>
+      <c r="C18" s="312"/>
+      <c r="D18" s="312"/>
+      <c r="E18" s="312"/>
     </row>
     <row r="19" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="27"/>
@@ -3612,10 +3612,10 @@
       <c r="G24" s="213"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="325" t="s">
+      <c r="A25" s="313" t="s">
         <v>351</v>
       </c>
-      <c r="B25" s="326"/>
+      <c r="B25" s="314"/>
       <c r="C25" s="19"/>
       <c r="D25" s="225">
         <v>-501641.09</v>
@@ -3625,10 +3625,10 @@
       <c r="G25" s="214"/>
     </row>
     <row r="26" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="327" t="s">
+      <c r="A26" s="315" t="s">
         <v>352</v>
       </c>
-      <c r="B26" s="328"/>
+      <c r="B26" s="316"/>
       <c r="C26" s="19"/>
       <c r="D26" s="225">
         <v>0</v>
@@ -5181,10 +5181,10 @@
       <c r="G130" s="27"/>
     </row>
     <row r="131" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="335" t="s">
+      <c r="A131" s="304" t="s">
         <v>386</v>
       </c>
-      <c r="B131" s="336"/>
+      <c r="B131" s="305"/>
       <c r="C131" s="19"/>
       <c r="D131" s="164">
         <v>1314489</v>
@@ -5196,10 +5196,10 @@
       <c r="G131" s="27"/>
     </row>
     <row r="132" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="335" t="s">
+      <c r="A132" s="304" t="s">
         <v>388</v>
       </c>
-      <c r="B132" s="336"/>
+      <c r="B132" s="305"/>
       <c r="C132" s="19"/>
       <c r="D132" s="164">
         <v>465749</v>
@@ -5212,10 +5212,10 @@
       <c r="G132" s="27"/>
     </row>
     <row r="133" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="335" t="s">
+      <c r="A133" s="304" t="s">
         <v>387</v>
       </c>
-      <c r="B133" s="336"/>
+      <c r="B133" s="305"/>
       <c r="C133" s="19"/>
       <c r="D133" s="164">
         <v>126745</v>
@@ -5228,10 +5228,10 @@
       <c r="G133" s="27"/>
     </row>
     <row r="134" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="335" t="s">
+      <c r="A134" s="304" t="s">
         <v>410</v>
       </c>
-      <c r="B134" s="336"/>
+      <c r="B134" s="305"/>
       <c r="C134" s="19"/>
       <c r="D134" s="164">
         <v>94353</v>
@@ -5247,10 +5247,10 @@
       <c r="G134" s="27"/>
     </row>
     <row r="135" spans="1:7" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="335" t="s">
+      <c r="A135" s="304" t="s">
         <v>189</v>
       </c>
-      <c r="B135" s="336"/>
+      <c r="B135" s="305"/>
       <c r="C135" s="19"/>
       <c r="D135" s="164">
         <v>31266.93</v>
@@ -5262,10 +5262,10 @@
       <c r="G135" s="27"/>
     </row>
     <row r="136" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="335" t="s">
+      <c r="A136" s="304" t="s">
         <v>335</v>
       </c>
-      <c r="B136" s="336"/>
+      <c r="B136" s="305"/>
       <c r="C136" s="19"/>
       <c r="D136" s="164">
         <v>9137.2099999999991</v>
@@ -5313,10 +5313,10 @@
       <c r="G139" s="27"/>
     </row>
     <row r="140" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="335" t="s">
+      <c r="A140" s="304" t="s">
         <v>358</v>
       </c>
-      <c r="B140" s="336"/>
+      <c r="B140" s="305"/>
       <c r="C140" s="19"/>
       <c r="D140" s="275">
         <v>9914839.9499999993</v>
@@ -5403,10 +5403,10 @@
       <c r="G147" s="27"/>
     </row>
     <row r="148" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="330" t="s">
+      <c r="A148" s="307" t="s">
         <v>380</v>
       </c>
-      <c r="B148" s="330"/>
+      <c r="B148" s="307"/>
       <c r="C148" s="19"/>
       <c r="D148" s="164">
         <f>2974450-2450000</f>
@@ -5823,10 +5823,10 @@
       <c r="F186" s="63"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A187" s="333" t="s">
+      <c r="A187" s="310" t="s">
         <v>322</v>
       </c>
-      <c r="B187" s="334"/>
+      <c r="B187" s="311"/>
       <c r="C187" s="5"/>
       <c r="D187" s="217"/>
       <c r="E187" s="31"/>
@@ -5895,10 +5895,10 @@
       <c r="F193" s="63"/>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A194" s="331" t="s">
+      <c r="A194" s="308" t="s">
         <v>290</v>
       </c>
-      <c r="B194" s="332"/>
+      <c r="B194" s="309"/>
       <c r="C194" s="5"/>
       <c r="D194" s="12"/>
       <c r="E194" s="31"/>
@@ -6272,16 +6272,16 @@
       <c r="F221" s="32"/>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A222" s="329" t="s">
+      <c r="A222" s="306" t="s">
         <v>17</v>
       </c>
-      <c r="B222" s="329"/>
-      <c r="C222" s="329"/>
+      <c r="B222" s="306"/>
+      <c r="C222" s="306"/>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A223" s="329"/>
-      <c r="B223" s="329"/>
-      <c r="C223" s="329"/>
+      <c r="A223" s="306"/>
+      <c r="B223" s="306"/>
+      <c r="C223" s="306"/>
     </row>
     <row r="224" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="53" t="s">
@@ -6307,12 +6307,70 @@
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="A94:B94"/>
-    <mergeCell ref="A99:B99"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A100:B100"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A66:B66"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A79:B79"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="A1:A8"/>
+    <mergeCell ref="A10:E12"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A15:E18"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A222:C223"/>
+    <mergeCell ref="A148:B148"/>
+    <mergeCell ref="A194:B194"/>
+    <mergeCell ref="A151:B151"/>
+    <mergeCell ref="A187:B187"/>
+    <mergeCell ref="A103:B103"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A132:B132"/>
+    <mergeCell ref="A131:B131"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A123:B123"/>
+    <mergeCell ref="A124:B124"/>
+    <mergeCell ref="A106:B106"/>
+    <mergeCell ref="A127:B127"/>
+    <mergeCell ref="A129:B129"/>
+    <mergeCell ref="A126:B126"/>
+    <mergeCell ref="A128:B128"/>
     <mergeCell ref="A71:B71"/>
     <mergeCell ref="A70:B70"/>
     <mergeCell ref="A140:B140"/>
@@ -6329,80 +6387,22 @@
     <mergeCell ref="A135:B135"/>
     <mergeCell ref="A134:B134"/>
     <mergeCell ref="A95:B95"/>
-    <mergeCell ref="A103:B103"/>
-    <mergeCell ref="A133:B133"/>
-    <mergeCell ref="A132:B132"/>
-    <mergeCell ref="A131:B131"/>
-    <mergeCell ref="A122:B122"/>
-    <mergeCell ref="A222:C223"/>
-    <mergeCell ref="A148:B148"/>
-    <mergeCell ref="A194:B194"/>
-    <mergeCell ref="A151:B151"/>
-    <mergeCell ref="A187:B187"/>
-    <mergeCell ref="A123:B123"/>
-    <mergeCell ref="A124:B124"/>
-    <mergeCell ref="A106:B106"/>
-    <mergeCell ref="A127:B127"/>
-    <mergeCell ref="A129:B129"/>
-    <mergeCell ref="A126:B126"/>
-    <mergeCell ref="A128:B128"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="A1:A8"/>
-    <mergeCell ref="A10:E12"/>
-    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="A94:B94"/>
+    <mergeCell ref="A99:B99"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A78:B78"/>
     <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A74:C74"/>
     <mergeCell ref="A93:B93"/>
     <mergeCell ref="A97:B97"/>
-    <mergeCell ref="A89:B89"/>
     <mergeCell ref="A92:B92"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A63:B63"/>
     <mergeCell ref="A91:B91"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A79:B79"/>
     <mergeCell ref="A86:B86"/>
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A66:B66"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="115" orientation="portrait" r:id="rId1"/>
@@ -6442,27 +6442,27 @@
     <row r="1" spans="1:24" ht="251.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="348" t="s">
+      <c r="C1" s="351" t="s">
         <v>334</v>
       </c>
-      <c r="D1" s="349"/>
-      <c r="E1" s="349"/>
-      <c r="F1" s="349"/>
-      <c r="G1" s="349"/>
-      <c r="H1" s="349"/>
-      <c r="I1" s="349"/>
-      <c r="J1" s="349"/>
-      <c r="K1" s="349"/>
-      <c r="L1" s="349"/>
+      <c r="D1" s="352"/>
+      <c r="E1" s="352"/>
+      <c r="F1" s="352"/>
+      <c r="G1" s="352"/>
+      <c r="H1" s="352"/>
+      <c r="I1" s="352"/>
+      <c r="J1" s="352"/>
+      <c r="K1" s="352"/>
+      <c r="L1" s="352"/>
       <c r="M1" s="128"/>
-      <c r="N1" s="350" t="s">
+      <c r="N1" s="353" t="s">
         <v>306</v>
       </c>
-      <c r="O1" s="350"/>
-      <c r="P1" s="345">
+      <c r="O1" s="353"/>
+      <c r="P1" s="348">
         <v>30000000</v>
       </c>
-      <c r="Q1" s="345"/>
+      <c r="Q1" s="348"/>
       <c r="R1" s="148"/>
       <c r="S1" s="3"/>
       <c r="T1" s="1"/>
@@ -6476,35 +6476,35 @@
     <row r="2" spans="1:24" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="347" t="s">
+      <c r="C2" s="350" t="s">
         <v>225</v>
       </c>
-      <c r="D2" s="347"/>
-      <c r="E2" s="347"/>
+      <c r="D2" s="350"/>
+      <c r="E2" s="350"/>
       <c r="F2" s="128"/>
-      <c r="G2" s="344">
+      <c r="G2" s="345">
         <f>X2</f>
         <v>27518571.293111999</v>
       </c>
-      <c r="H2" s="344"/>
+      <c r="H2" s="345"/>
       <c r="I2" s="128" t="s">
         <v>272</v>
       </c>
       <c r="J2" s="128"/>
-      <c r="K2" s="344">
+      <c r="K2" s="345">
         <f>W1</f>
         <v>80675963.920000002</v>
       </c>
-      <c r="L2" s="344"/>
+      <c r="L2" s="345"/>
       <c r="M2" s="189"/>
       <c r="N2" s="190" t="s">
         <v>258</v>
       </c>
       <c r="O2" s="189"/>
-      <c r="P2" s="346">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="346"/>
+      <c r="P2" s="349">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="349"/>
       <c r="R2" s="149"/>
       <c r="T2" s="1"/>
       <c r="U2" t="s">
@@ -6516,112 +6516,112 @@
       </c>
     </row>
     <row r="3" spans="1:24" ht="91.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="355" t="str">
+      <c r="A3" s="358" t="str">
         <f>"ATENCIÓN: Si usted abona antes del " &amp; TEXT(RESUMEN!A10,"dd/mm/yyyy") &amp; ", deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste."</f>
         <v>ATENCIÓN: Si usted abona antes del Primer Vencimiento:  16/10, deberá abonar el importe indicado en la columna de color naranja. En caso de abonar con posterioridad a dicha fecha, deberá abonar el monto indicado en la columna de color celeste.</v>
       </c>
-      <c r="B3" s="356"/>
-      <c r="C3" s="356"/>
-      <c r="D3" s="356"/>
-      <c r="E3" s="356"/>
-      <c r="F3" s="356"/>
-      <c r="G3" s="356"/>
-      <c r="H3" s="356"/>
-      <c r="I3" s="356"/>
-      <c r="J3" s="356"/>
-      <c r="K3" s="356"/>
-      <c r="L3" s="356"/>
-      <c r="M3" s="356"/>
-      <c r="N3" s="356"/>
-      <c r="O3" s="356"/>
-      <c r="P3" s="356"/>
-      <c r="Q3" s="356"/>
-      <c r="R3" s="356"/>
-      <c r="S3" s="356"/>
-      <c r="T3" s="357"/>
+      <c r="B3" s="359"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
+      <c r="F3" s="359"/>
+      <c r="G3" s="359"/>
+      <c r="H3" s="359"/>
+      <c r="I3" s="359"/>
+      <c r="J3" s="359"/>
+      <c r="K3" s="359"/>
+      <c r="L3" s="359"/>
+      <c r="M3" s="359"/>
+      <c r="N3" s="359"/>
+      <c r="O3" s="359"/>
+      <c r="P3" s="359"/>
+      <c r="Q3" s="359"/>
+      <c r="R3" s="359"/>
+      <c r="S3" s="359"/>
+      <c r="T3" s="360"/>
       <c r="X3" s="34"/>
     </row>
     <row r="4" spans="1:24" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="358" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="360" t="s">
+      <c r="A4" s="361" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="363" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="360" t="s">
+      <c r="C4" s="363" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="360" t="s">
+      <c r="D4" s="363" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="337" t="s">
+      <c r="E4" s="346" t="s">
         <v>181</v>
       </c>
-      <c r="F4" s="360" t="s">
+      <c r="F4" s="363" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="362" t="s">
+      <c r="G4" s="365" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="337" t="s">
+      <c r="H4" s="346" t="s">
         <v>231</v>
       </c>
-      <c r="I4" s="337" t="s">
+      <c r="I4" s="346" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="337"/>
-      <c r="K4" s="337" t="s">
+      <c r="J4" s="346"/>
+      <c r="K4" s="346" t="s">
         <v>182</v>
       </c>
-      <c r="L4" s="337" t="s">
+      <c r="L4" s="346" t="s">
         <v>146</v>
       </c>
-      <c r="M4" s="337" t="s">
+      <c r="M4" s="346" t="s">
         <v>184</v>
       </c>
-      <c r="N4" s="337" t="s">
+      <c r="N4" s="346" t="s">
         <v>183</v>
       </c>
-      <c r="O4" s="337" t="s">
+      <c r="O4" s="346" t="s">
         <v>316</v>
       </c>
-      <c r="P4" s="351" t="s">
+      <c r="P4" s="354" t="s">
         <v>314</v>
       </c>
-      <c r="Q4" s="352"/>
-      <c r="R4" s="351" t="s">
+      <c r="Q4" s="355"/>
+      <c r="R4" s="354" t="s">
         <v>309</v>
       </c>
-      <c r="S4" s="352"/>
-      <c r="T4" s="337" t="s">
+      <c r="S4" s="355"/>
+      <c r="T4" s="346" t="s">
         <v>256</v>
       </c>
       <c r="U4" s="12"/>
     </row>
     <row r="5" spans="1:24" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="359"/>
-      <c r="B5" s="361"/>
-      <c r="C5" s="361"/>
-      <c r="D5" s="361"/>
-      <c r="E5" s="338"/>
-      <c r="F5" s="361"/>
-      <c r="G5" s="363"/>
-      <c r="H5" s="338"/>
-      <c r="I5" s="338"/>
-      <c r="J5" s="338"/>
-      <c r="K5" s="338"/>
-      <c r="L5" s="338"/>
-      <c r="M5" s="338"/>
-      <c r="N5" s="338"/>
-      <c r="O5" s="338"/>
-      <c r="P5" s="353" t="str">
+      <c r="A5" s="362"/>
+      <c r="B5" s="364"/>
+      <c r="C5" s="364"/>
+      <c r="D5" s="364"/>
+      <c r="E5" s="347"/>
+      <c r="F5" s="364"/>
+      <c r="G5" s="366"/>
+      <c r="H5" s="347"/>
+      <c r="I5" s="347"/>
+      <c r="J5" s="347"/>
+      <c r="K5" s="347"/>
+      <c r="L5" s="347"/>
+      <c r="M5" s="347"/>
+      <c r="N5" s="347"/>
+      <c r="O5" s="347"/>
+      <c r="P5" s="356" t="str">
         <f>RESUMEN!A10</f>
         <v>Primer Vencimiento:  16/10</v>
       </c>
-      <c r="Q5" s="354"/>
-      <c r="R5" s="353"/>
-      <c r="S5" s="354"/>
-      <c r="T5" s="338"/>
+      <c r="Q5" s="357"/>
+      <c r="R5" s="356"/>
+      <c r="S5" s="357"/>
+      <c r="T5" s="347"/>
     </row>
     <row r="6" spans="1:24" ht="26.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="152"/>
@@ -6674,11 +6674,11 @@
       <c r="O6" s="277">
         <v>0</v>
       </c>
-      <c r="P6" s="339">
+      <c r="P6" s="367">
         <f t="shared" ref="P6:P37" si="2">ROUND(SUM(G6:O6),0) + S6</f>
         <v>759748.01</v>
       </c>
-      <c r="Q6" s="340"/>
+      <c r="Q6" s="368"/>
       <c r="R6" s="191">
         <f t="shared" ref="R6:R37" si="3">ROUND(P6+P6*3.033%,0) + S6</f>
         <v>782791.01</v>
@@ -6746,11 +6746,11 @@
       <c r="O7" s="277">
         <v>0</v>
       </c>
-      <c r="P7" s="341">
+      <c r="P7" s="369">
         <f t="shared" si="2"/>
         <v>5430599.0199999996</v>
       </c>
-      <c r="Q7" s="342"/>
+      <c r="Q7" s="370"/>
       <c r="R7" s="191">
         <f t="shared" si="3"/>
         <v>5595309.0199999996</v>
@@ -6815,11 +6815,11 @@
       <c r="O8" s="277">
         <v>0</v>
       </c>
-      <c r="P8" s="343">
+      <c r="P8" s="337">
         <f t="shared" si="2"/>
         <v>737384.03</v>
       </c>
-      <c r="Q8" s="343"/>
+      <c r="Q8" s="337"/>
       <c r="R8" s="191">
         <f t="shared" si="3"/>
         <v>759749.03</v>
@@ -6885,11 +6885,11 @@
       <c r="O9" s="277">
         <v>0</v>
       </c>
-      <c r="P9" s="343">
+      <c r="P9" s="337">
         <f t="shared" si="2"/>
         <v>1078638.04</v>
       </c>
-      <c r="Q9" s="343"/>
+      <c r="Q9" s="337"/>
       <c r="R9" s="191">
         <f t="shared" si="3"/>
         <v>1111353.04</v>
@@ -6959,11 +6959,11 @@
       <c r="O10" s="277">
         <v>0</v>
       </c>
-      <c r="P10" s="343">
+      <c r="P10" s="337">
         <f t="shared" si="2"/>
         <v>767816.05</v>
       </c>
-      <c r="Q10" s="343"/>
+      <c r="Q10" s="337"/>
       <c r="R10" s="191">
         <f t="shared" si="3"/>
         <v>791104.05</v>
@@ -7030,11 +7030,11 @@
       <c r="O11" s="277">
         <v>0</v>
       </c>
-      <c r="P11" s="343">
+      <c r="P11" s="337">
         <f t="shared" si="2"/>
         <v>751681.06</v>
       </c>
-      <c r="Q11" s="343"/>
+      <c r="Q11" s="337"/>
       <c r="R11" s="191">
         <f t="shared" si="3"/>
         <v>774480.06</v>
@@ -7103,11 +7103,11 @@
       <c r="O12" s="277">
         <v>0</v>
       </c>
-      <c r="P12" s="343">
+      <c r="P12" s="337">
         <f t="shared" si="2"/>
         <v>735546.07</v>
       </c>
-      <c r="Q12" s="343"/>
+      <c r="Q12" s="337"/>
       <c r="R12" s="191">
         <f t="shared" si="3"/>
         <v>757855.07</v>
@@ -7176,11 +7176,11 @@
       <c r="O13" s="277">
         <v>0</v>
       </c>
-      <c r="P13" s="343">
+      <c r="P13" s="337">
         <f t="shared" si="2"/>
         <v>767816.08</v>
       </c>
-      <c r="Q13" s="343"/>
+      <c r="Q13" s="337"/>
       <c r="R13" s="191">
         <f t="shared" si="3"/>
         <v>791104.08</v>
@@ -7248,11 +7248,11 @@
       <c r="O14" s="277">
         <v>0</v>
       </c>
-      <c r="P14" s="343">
+      <c r="P14" s="337">
         <f t="shared" si="2"/>
         <v>768441.09</v>
       </c>
-      <c r="Q14" s="343"/>
+      <c r="Q14" s="337"/>
       <c r="R14" s="191">
         <f t="shared" si="3"/>
         <v>791748.09</v>
@@ -7318,11 +7318,11 @@
       <c r="O15" s="277">
         <v>0</v>
       </c>
-      <c r="P15" s="343">
+      <c r="P15" s="337">
         <f t="shared" si="2"/>
         <v>767816.1</v>
       </c>
-      <c r="Q15" s="343"/>
+      <c r="Q15" s="337"/>
       <c r="R15" s="191">
         <f t="shared" si="3"/>
         <v>791104.1</v>
@@ -7391,11 +7391,11 @@
         <f>I16/2</f>
         <v>189588.515212</v>
       </c>
-      <c r="P16" s="343">
+      <c r="P16" s="337">
         <f t="shared" si="2"/>
         <v>934803.11</v>
       </c>
-      <c r="Q16" s="343"/>
+      <c r="Q16" s="337"/>
       <c r="R16" s="191">
         <f t="shared" si="3"/>
         <v>963156.11</v>
@@ -7461,11 +7461,11 @@
       <c r="O17" s="277">
         <v>0</v>
       </c>
-      <c r="P17" s="343">
+      <c r="P17" s="337">
         <f t="shared" si="2"/>
         <v>6344888.1200000001</v>
       </c>
-      <c r="Q17" s="343"/>
+      <c r="Q17" s="337"/>
       <c r="R17" s="191">
         <f t="shared" si="3"/>
         <v>6537329.1200000001</v>
@@ -7534,11 +7534,11 @@
       <c r="O18" s="277">
         <v>0</v>
       </c>
-      <c r="P18" s="343">
+      <c r="P18" s="337">
         <f t="shared" si="2"/>
         <v>759748.13</v>
       </c>
-      <c r="Q18" s="343"/>
+      <c r="Q18" s="337"/>
       <c r="R18" s="191">
         <f t="shared" si="3"/>
         <v>782791.13</v>
@@ -7604,11 +7604,11 @@
       <c r="O19" s="277">
         <v>0</v>
       </c>
-      <c r="P19" s="343">
+      <c r="P19" s="337">
         <f t="shared" si="2"/>
         <v>767816.14</v>
       </c>
-      <c r="Q19" s="343"/>
+      <c r="Q19" s="337"/>
       <c r="R19" s="191">
         <f t="shared" si="3"/>
         <v>791104.14</v>
@@ -7676,11 +7676,11 @@
       <c r="O20" s="277">
         <v>0</v>
       </c>
-      <c r="P20" s="343">
+      <c r="P20" s="337">
         <f t="shared" si="2"/>
         <v>766863.15</v>
       </c>
-      <c r="Q20" s="343"/>
+      <c r="Q20" s="337"/>
       <c r="R20" s="191">
         <f t="shared" si="3"/>
         <v>790122.15</v>
@@ -7749,11 +7749,11 @@
       <c r="O21" s="277">
         <v>0</v>
       </c>
-      <c r="P21" s="343">
+      <c r="P21" s="337">
         <f t="shared" si="2"/>
         <v>759748.16</v>
       </c>
-      <c r="Q21" s="343"/>
+      <c r="Q21" s="337"/>
       <c r="R21" s="191">
         <f t="shared" si="3"/>
         <v>782791.16</v>
@@ -7819,11 +7819,11 @@
       <c r="O22" s="277">
         <v>0</v>
       </c>
-      <c r="P22" s="343">
+      <c r="P22" s="337">
         <f t="shared" si="2"/>
         <v>649195.17000000004</v>
       </c>
-      <c r="Q22" s="343"/>
+      <c r="Q22" s="337"/>
       <c r="R22" s="191">
         <f t="shared" si="3"/>
         <v>668885.17000000004</v>
@@ -7892,11 +7892,11 @@
       <c r="O23" s="277">
         <v>0</v>
       </c>
-      <c r="P23" s="343">
+      <c r="P23" s="337">
         <f t="shared" si="2"/>
         <v>759748.18</v>
       </c>
-      <c r="Q23" s="343"/>
+      <c r="Q23" s="337"/>
       <c r="R23" s="191">
         <f t="shared" si="3"/>
         <v>782791.18</v>
@@ -7964,11 +7964,11 @@
       <c r="O24" s="277">
         <v>0</v>
       </c>
-      <c r="P24" s="343">
+      <c r="P24" s="337">
         <f t="shared" si="2"/>
         <v>745234.19</v>
       </c>
-      <c r="Q24" s="343"/>
+      <c r="Q24" s="337"/>
       <c r="R24" s="191">
         <f t="shared" si="3"/>
         <v>767837.19</v>
@@ -8034,11 +8034,11 @@
       <c r="O25" s="277">
         <v>0</v>
       </c>
-      <c r="P25" s="343">
+      <c r="P25" s="337">
         <f t="shared" si="2"/>
         <v>767816.2</v>
       </c>
-      <c r="Q25" s="343"/>
+      <c r="Q25" s="337"/>
       <c r="R25" s="191">
         <f t="shared" si="3"/>
         <v>791104.2</v>
@@ -8104,11 +8104,11 @@
       <c r="O26" s="277">
         <v>0</v>
       </c>
-      <c r="P26" s="343">
+      <c r="P26" s="337">
         <f t="shared" si="2"/>
         <v>767816.21</v>
       </c>
-      <c r="Q26" s="343"/>
+      <c r="Q26" s="337"/>
       <c r="R26" s="191">
         <f t="shared" si="3"/>
         <v>791104.21</v>
@@ -8180,11 +8180,11 @@
       <c r="O27" s="277">
         <v>0</v>
       </c>
-      <c r="P27" s="343">
+      <c r="P27" s="337">
         <f t="shared" si="2"/>
         <v>767816.22</v>
       </c>
-      <c r="Q27" s="343"/>
+      <c r="Q27" s="337"/>
       <c r="R27" s="191">
         <f t="shared" si="3"/>
         <v>791104.22</v>
@@ -8252,11 +8252,11 @@
       <c r="O28" s="277">
         <v>0</v>
       </c>
-      <c r="P28" s="343">
+      <c r="P28" s="337">
         <f t="shared" si="2"/>
         <v>745213.23</v>
       </c>
-      <c r="Q28" s="343"/>
+      <c r="Q28" s="337"/>
       <c r="R28" s="191">
         <f t="shared" si="3"/>
         <v>767816.23</v>
@@ -8324,11 +8324,11 @@
       <c r="O29" s="277">
         <v>0</v>
       </c>
-      <c r="P29" s="343">
+      <c r="P29" s="337">
         <f t="shared" si="2"/>
         <v>721228.24</v>
       </c>
-      <c r="Q29" s="343"/>
+      <c r="Q29" s="337"/>
       <c r="R29" s="191">
         <f t="shared" si="3"/>
         <v>743103.24</v>
@@ -8397,11 +8397,11 @@
       <c r="O30" s="277">
         <v>0</v>
       </c>
-      <c r="P30" s="343">
+      <c r="P30" s="337">
         <f t="shared" si="2"/>
         <v>775884.25</v>
       </c>
-      <c r="Q30" s="343"/>
+      <c r="Q30" s="337"/>
       <c r="R30" s="191">
         <f t="shared" si="3"/>
         <v>799417.25</v>
@@ -8469,11 +8469,11 @@
       <c r="O31" s="277">
         <v>0</v>
       </c>
-      <c r="P31" s="343">
+      <c r="P31" s="337">
         <f t="shared" si="2"/>
         <v>775884.26</v>
       </c>
-      <c r="Q31" s="343"/>
+      <c r="Q31" s="337"/>
       <c r="R31" s="191">
         <f t="shared" si="3"/>
         <v>799417.26</v>
@@ -8542,11 +8542,11 @@
       <c r="O32" s="277">
         <v>0</v>
       </c>
-      <c r="P32" s="343">
+      <c r="P32" s="337">
         <f t="shared" si="2"/>
         <v>775884.27</v>
       </c>
-      <c r="Q32" s="343"/>
+      <c r="Q32" s="337"/>
       <c r="R32" s="191">
         <f t="shared" si="3"/>
         <v>799417.27</v>
@@ -8611,11 +8611,11 @@
       <c r="O33" s="277">
         <v>0</v>
       </c>
-      <c r="P33" s="343">
+      <c r="P33" s="337">
         <f t="shared" si="2"/>
         <v>573644.28</v>
       </c>
-      <c r="Q33" s="343"/>
+      <c r="Q33" s="337"/>
       <c r="R33" s="191">
         <f t="shared" si="3"/>
         <v>591043.28</v>
@@ -8684,11 +8684,11 @@
       <c r="O34" s="277">
         <v>0</v>
       </c>
-      <c r="P34" s="343">
+      <c r="P34" s="337">
         <f t="shared" si="2"/>
         <v>775884.29</v>
       </c>
-      <c r="Q34" s="343"/>
+      <c r="Q34" s="337"/>
       <c r="R34" s="191">
         <f t="shared" si="3"/>
         <v>799417.29</v>
@@ -8757,11 +8757,11 @@
       <c r="O35" s="277">
         <v>0</v>
       </c>
-      <c r="P35" s="343">
+      <c r="P35" s="337">
         <f t="shared" si="2"/>
         <v>751681.3</v>
       </c>
-      <c r="Q35" s="343"/>
+      <c r="Q35" s="337"/>
       <c r="R35" s="191">
         <f t="shared" si="3"/>
         <v>774480.3</v>
@@ -8827,11 +8827,11 @@
       <c r="O36" s="277">
         <v>0</v>
       </c>
-      <c r="P36" s="343">
+      <c r="P36" s="337">
         <f t="shared" si="2"/>
         <v>4080719.31</v>
       </c>
-      <c r="Q36" s="343"/>
+      <c r="Q36" s="337"/>
       <c r="R36" s="191">
         <f t="shared" si="3"/>
         <v>4204488.3099999996</v>
@@ -8900,11 +8900,11 @@
       <c r="O37" s="277">
         <v>0</v>
       </c>
-      <c r="P37" s="343">
+      <c r="P37" s="337">
         <f t="shared" si="2"/>
         <v>618436.31999999995</v>
       </c>
-      <c r="Q37" s="343"/>
+      <c r="Q37" s="337"/>
       <c r="R37" s="191">
         <f t="shared" si="3"/>
         <v>637193.31999999995</v>
@@ -8969,11 +8969,11 @@
       <c r="O38" s="277">
         <v>0</v>
       </c>
-      <c r="P38" s="343">
+      <c r="P38" s="337">
         <f t="shared" ref="P38:P69" si="13">ROUND(SUM(G38:O38),0) + S38</f>
         <v>751681.33</v>
       </c>
-      <c r="Q38" s="343"/>
+      <c r="Q38" s="337"/>
       <c r="R38" s="191">
         <f t="shared" ref="R38:R69" si="14">ROUND(P38+P38*3.033%,0) + S38</f>
         <v>774480.33</v>
@@ -9037,11 +9037,11 @@
       <c r="O39" s="277">
         <v>0</v>
       </c>
-      <c r="P39" s="343">
+      <c r="P39" s="337">
         <f t="shared" si="13"/>
         <v>4128501.34</v>
       </c>
-      <c r="Q39" s="343"/>
+      <c r="Q39" s="337"/>
       <c r="R39" s="191">
         <f t="shared" si="14"/>
         <v>4253719.34</v>
@@ -9111,11 +9111,11 @@
       <c r="O40" s="277">
         <v>0</v>
       </c>
-      <c r="P40" s="343">
+      <c r="P40" s="337">
         <f t="shared" si="13"/>
         <v>759748.35</v>
       </c>
-      <c r="Q40" s="343"/>
+      <c r="Q40" s="337"/>
       <c r="R40" s="191">
         <f t="shared" si="14"/>
         <v>782792.35</v>
@@ -9184,11 +9184,11 @@
       <c r="O41" s="277">
         <v>0</v>
       </c>
-      <c r="P41" s="343">
+      <c r="P41" s="337">
         <f t="shared" si="13"/>
         <v>732078.36</v>
       </c>
-      <c r="Q41" s="343"/>
+      <c r="Q41" s="337"/>
       <c r="R41" s="191">
         <f t="shared" si="14"/>
         <v>754282.36</v>
@@ -9255,11 +9255,11 @@
       <c r="O42" s="277">
         <v>0</v>
       </c>
-      <c r="P42" s="343">
+      <c r="P42" s="337">
         <f t="shared" si="13"/>
         <v>775184.37</v>
       </c>
-      <c r="Q42" s="343"/>
+      <c r="Q42" s="337"/>
       <c r="R42" s="191">
         <f t="shared" si="14"/>
         <v>798696.37</v>
@@ -9324,11 +9324,11 @@
       <c r="O43" s="277">
         <v>0</v>
       </c>
-      <c r="P43" s="343">
+      <c r="P43" s="337">
         <f t="shared" si="13"/>
         <v>1503064.38</v>
       </c>
-      <c r="Q43" s="343"/>
+      <c r="Q43" s="337"/>
       <c r="R43" s="191">
         <f t="shared" si="14"/>
         <v>1548652.38</v>
@@ -9397,11 +9397,11 @@
       <c r="O44" s="277">
         <v>0</v>
       </c>
-      <c r="P44" s="343">
+      <c r="P44" s="337">
         <f t="shared" si="13"/>
         <v>751605.39</v>
       </c>
-      <c r="Q44" s="343"/>
+      <c r="Q44" s="337"/>
       <c r="R44" s="191">
         <f t="shared" si="14"/>
         <v>774402.39</v>
@@ -9471,11 +9471,11 @@
       <c r="O45" s="277">
         <v>0</v>
       </c>
-      <c r="P45" s="343">
+      <c r="P45" s="337">
         <f t="shared" si="13"/>
         <v>751681.4</v>
       </c>
-      <c r="Q45" s="343"/>
+      <c r="Q45" s="337"/>
       <c r="R45" s="191">
         <f t="shared" si="14"/>
         <v>774480.4</v>
@@ -9541,11 +9541,11 @@
       <c r="O46" s="277">
         <v>0</v>
       </c>
-      <c r="P46" s="343">
+      <c r="P46" s="337">
         <f t="shared" si="13"/>
         <v>751362.41</v>
       </c>
-      <c r="Q46" s="343"/>
+      <c r="Q46" s="337"/>
       <c r="R46" s="191">
         <f t="shared" si="14"/>
         <v>774151.41</v>
@@ -9615,11 +9615,11 @@
       <c r="O47" s="277">
         <v>0</v>
       </c>
-      <c r="P47" s="343">
+      <c r="P47" s="337">
         <f t="shared" si="13"/>
         <v>751681.42</v>
       </c>
-      <c r="Q47" s="343"/>
+      <c r="Q47" s="337"/>
       <c r="R47" s="191">
         <f t="shared" si="14"/>
         <v>774480.42</v>
@@ -9689,11 +9689,11 @@
       <c r="O48" s="277">
         <v>0</v>
       </c>
-      <c r="P48" s="343">
+      <c r="P48" s="337">
         <f t="shared" si="13"/>
         <v>679072.43</v>
       </c>
-      <c r="Q48" s="343"/>
+      <c r="Q48" s="337"/>
       <c r="R48" s="191">
         <f t="shared" si="14"/>
         <v>699669.43</v>
@@ -9757,11 +9757,11 @@
       <c r="O49" s="277">
         <v>0</v>
       </c>
-      <c r="P49" s="343">
+      <c r="P49" s="337">
         <f t="shared" si="13"/>
         <v>531782.43999999994</v>
       </c>
-      <c r="Q49" s="343"/>
+      <c r="Q49" s="337"/>
       <c r="R49" s="191">
         <f t="shared" si="14"/>
         <v>547911.43999999994</v>
@@ -9831,11 +9831,11 @@
         <f>O82</f>
         <v>225800</v>
       </c>
-      <c r="P50" s="343">
+      <c r="P50" s="337">
         <f t="shared" si="13"/>
         <v>1695003.45</v>
       </c>
-      <c r="Q50" s="343"/>
+      <c r="Q50" s="337"/>
       <c r="R50" s="191">
         <f t="shared" si="14"/>
         <v>1746413.45</v>
@@ -9901,11 +9901,11 @@
       <c r="O51" s="277">
         <v>0</v>
       </c>
-      <c r="P51" s="343">
+      <c r="P51" s="337">
         <f t="shared" si="13"/>
         <v>1451354.46</v>
       </c>
-      <c r="Q51" s="343"/>
+      <c r="Q51" s="337"/>
       <c r="R51" s="191">
         <f t="shared" si="14"/>
         <v>1495374.46</v>
@@ -9972,11 +9972,11 @@
       <c r="O52" s="277">
         <v>0</v>
       </c>
-      <c r="P52" s="343">
+      <c r="P52" s="337">
         <f t="shared" si="13"/>
         <v>1526567.47</v>
       </c>
-      <c r="Q52" s="343"/>
+      <c r="Q52" s="337"/>
       <c r="R52" s="191">
         <f t="shared" si="14"/>
         <v>1572868.47</v>
@@ -10047,11 +10047,11 @@
       <c r="O53" s="277">
         <v>0</v>
       </c>
-      <c r="P53" s="343">
+      <c r="P53" s="337">
         <f t="shared" si="13"/>
         <v>1187332.48</v>
       </c>
-      <c r="Q53" s="343"/>
+      <c r="Q53" s="337"/>
       <c r="R53" s="191">
         <f t="shared" si="14"/>
         <v>1223344.48</v>
@@ -10091,7 +10091,6 @@
         <v>0</v>
       </c>
       <c r="H54" s="46">
-        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="I54" s="279">
@@ -10119,11 +10118,11 @@
       <c r="O54" s="277">
         <v>0</v>
       </c>
-      <c r="P54" s="343">
+      <c r="P54" s="337">
         <f t="shared" si="13"/>
         <v>751681.49</v>
       </c>
-      <c r="Q54" s="343"/>
+      <c r="Q54" s="337"/>
       <c r="R54" s="191">
         <f t="shared" si="14"/>
         <v>774480.49</v>
@@ -10192,11 +10191,11 @@
       <c r="O55" s="277">
         <v>0</v>
       </c>
-      <c r="P55" s="343">
+      <c r="P55" s="337">
         <f t="shared" si="13"/>
         <v>751681.5</v>
       </c>
-      <c r="Q55" s="343"/>
+      <c r="Q55" s="337"/>
       <c r="R55" s="191">
         <f t="shared" si="14"/>
         <v>774480.5</v>
@@ -10265,11 +10264,11 @@
       <c r="O56" s="277">
         <v>0</v>
       </c>
-      <c r="P56" s="343">
+      <c r="P56" s="337">
         <f t="shared" si="13"/>
         <v>1526985.51</v>
       </c>
-      <c r="Q56" s="343"/>
+      <c r="Q56" s="337"/>
       <c r="R56" s="191">
         <f t="shared" si="14"/>
         <v>1573299.51</v>
@@ -10339,11 +10338,11 @@
       <c r="O57" s="277">
         <v>0</v>
       </c>
-      <c r="P57" s="343">
+      <c r="P57" s="337">
         <f t="shared" si="13"/>
         <v>759748.52</v>
       </c>
-      <c r="Q57" s="343"/>
+      <c r="Q57" s="337"/>
       <c r="R57" s="191">
         <f t="shared" si="14"/>
         <v>782792.52</v>
@@ -10410,11 +10409,11 @@
       <c r="O58" s="277">
         <v>0</v>
       </c>
-      <c r="P58" s="343">
+      <c r="P58" s="337">
         <f t="shared" si="13"/>
         <v>4249221.53</v>
       </c>
-      <c r="Q58" s="343"/>
+      <c r="Q58" s="337"/>
       <c r="R58" s="191">
         <f t="shared" si="14"/>
         <v>4378100.53</v>
@@ -10480,11 +10479,11 @@
       <c r="O59" s="277">
         <v>0</v>
       </c>
-      <c r="P59" s="343">
+      <c r="P59" s="337">
         <f t="shared" si="13"/>
         <v>781584.54</v>
       </c>
-      <c r="Q59" s="343"/>
+      <c r="Q59" s="337"/>
       <c r="R59" s="191">
         <f t="shared" si="14"/>
         <v>805290.54</v>
@@ -10553,11 +10552,11 @@
       <c r="O60" s="277">
         <v>0</v>
       </c>
-      <c r="P60" s="343">
+      <c r="P60" s="337">
         <f t="shared" si="13"/>
         <v>730463.55</v>
       </c>
-      <c r="Q60" s="343"/>
+      <c r="Q60" s="337"/>
       <c r="R60" s="191">
         <f t="shared" si="14"/>
         <v>752619.55</v>
@@ -10627,11 +10626,11 @@
       <c r="O61" s="277">
         <v>0</v>
       </c>
-      <c r="P61" s="343">
+      <c r="P61" s="337">
         <f t="shared" si="13"/>
         <v>751681.56</v>
       </c>
-      <c r="Q61" s="343"/>
+      <c r="Q61" s="337"/>
       <c r="R61" s="191">
         <f t="shared" si="14"/>
         <v>774480.56</v>
@@ -10701,11 +10700,11 @@
       <c r="O62" s="277">
         <v>0</v>
       </c>
-      <c r="P62" s="343">
+      <c r="P62" s="337">
         <f t="shared" si="13"/>
         <v>751681.57</v>
       </c>
-      <c r="Q62" s="343"/>
+      <c r="Q62" s="337"/>
       <c r="R62" s="191">
         <f t="shared" si="14"/>
         <v>774480.57</v>
@@ -10772,11 +10771,11 @@
       <c r="O63" s="277">
         <v>0</v>
       </c>
-      <c r="P63" s="343">
+      <c r="P63" s="337">
         <f t="shared" si="13"/>
         <v>706071.58</v>
       </c>
-      <c r="Q63" s="343"/>
+      <c r="Q63" s="337"/>
       <c r="R63" s="191">
         <f t="shared" si="14"/>
         <v>727487.58</v>
@@ -10843,11 +10842,11 @@
       <c r="O64" s="277">
         <v>0</v>
       </c>
-      <c r="P64" s="343">
+      <c r="P64" s="337">
         <f t="shared" si="13"/>
         <v>698821.59</v>
       </c>
-      <c r="Q64" s="343"/>
+      <c r="Q64" s="337"/>
       <c r="R64" s="191">
         <f t="shared" si="14"/>
         <v>720017.59</v>
@@ -10915,11 +10914,11 @@
         <f>I65/2</f>
         <v>181520.91881999999</v>
       </c>
-      <c r="P65" s="343">
+      <c r="P65" s="337">
         <f t="shared" si="13"/>
         <v>1684101.6</v>
       </c>
-      <c r="Q65" s="343"/>
+      <c r="Q65" s="337"/>
       <c r="R65" s="191">
         <f t="shared" si="14"/>
         <v>1735180.6</v>
@@ -10988,11 +10987,11 @@
       <c r="O66" s="277">
         <v>0</v>
       </c>
-      <c r="P66" s="343">
+      <c r="P66" s="337">
         <f t="shared" si="13"/>
         <v>751387.61</v>
       </c>
-      <c r="Q66" s="343"/>
+      <c r="Q66" s="337"/>
       <c r="R66" s="191">
         <f t="shared" si="14"/>
         <v>774177.61</v>
@@ -11062,11 +11061,11 @@
       <c r="O67" s="277">
         <v>0</v>
       </c>
-      <c r="P67" s="343">
+      <c r="P67" s="337">
         <f t="shared" si="13"/>
         <v>719410.62</v>
       </c>
-      <c r="Q67" s="343"/>
+      <c r="Q67" s="337"/>
       <c r="R67" s="191">
         <f t="shared" si="14"/>
         <v>741230.62</v>
@@ -11133,11 +11132,11 @@
       <c r="O68" s="277">
         <v>0</v>
       </c>
-      <c r="P68" s="343">
+      <c r="P68" s="337">
         <f t="shared" si="13"/>
         <v>751681.63</v>
       </c>
-      <c r="Q68" s="343"/>
+      <c r="Q68" s="337"/>
       <c r="R68" s="191">
         <f t="shared" si="14"/>
         <v>774480.63</v>
@@ -11207,11 +11206,11 @@
       <c r="O69" s="277">
         <v>0</v>
       </c>
-      <c r="P69" s="343">
+      <c r="P69" s="337">
         <f t="shared" si="13"/>
         <v>751681.64</v>
       </c>
-      <c r="Q69" s="343"/>
+      <c r="Q69" s="337"/>
       <c r="R69" s="191">
         <f t="shared" si="14"/>
         <v>774480.64</v>
@@ -11281,11 +11280,11 @@
       <c r="O70" s="277">
         <v>0</v>
       </c>
-      <c r="P70" s="343">
+      <c r="P70" s="337">
         <f t="shared" ref="P70:P101" si="21">ROUND(SUM(G70:O70),0) + S70</f>
         <v>751681.65</v>
       </c>
-      <c r="Q70" s="343"/>
+      <c r="Q70" s="337"/>
       <c r="R70" s="191">
         <f t="shared" ref="R70:R101" si="22">ROUND(P70+P70*3.033%,0) + S70</f>
         <v>774480.65</v>
@@ -11352,11 +11351,11 @@
       <c r="O71" s="277">
         <v>0</v>
       </c>
-      <c r="P71" s="343">
+      <c r="P71" s="337">
         <f t="shared" si="21"/>
         <v>751681.66</v>
       </c>
-      <c r="Q71" s="343"/>
+      <c r="Q71" s="337"/>
       <c r="R71" s="191">
         <f t="shared" si="22"/>
         <v>774480.66</v>
@@ -11423,11 +11422,11 @@
       <c r="O72" s="277">
         <v>0</v>
       </c>
-      <c r="P72" s="343">
+      <c r="P72" s="337">
         <f t="shared" si="21"/>
         <v>2405492.67</v>
       </c>
-      <c r="Q72" s="343"/>
+      <c r="Q72" s="337"/>
       <c r="R72" s="191">
         <f t="shared" si="22"/>
         <v>2478451.67</v>
@@ -11494,11 +11493,11 @@
       <c r="O73" s="277">
         <v>0</v>
       </c>
-      <c r="P73" s="343">
+      <c r="P73" s="337">
         <f t="shared" si="21"/>
         <v>7696932.6799999997</v>
       </c>
-      <c r="Q73" s="343"/>
+      <c r="Q73" s="337"/>
       <c r="R73" s="191">
         <f t="shared" si="22"/>
         <v>7930381.6799999997</v>
@@ -11564,11 +11563,11 @@
       <c r="O74" s="277">
         <v>0</v>
       </c>
-      <c r="P74" s="343">
+      <c r="P74" s="337">
         <f t="shared" si="21"/>
         <v>679072.69</v>
       </c>
-      <c r="Q74" s="343"/>
+      <c r="Q74" s="337"/>
       <c r="R74" s="191">
         <f t="shared" si="22"/>
         <v>699669.69</v>
@@ -11636,11 +11635,11 @@
       <c r="O75" s="277">
         <v>0</v>
       </c>
-      <c r="P75" s="343">
+      <c r="P75" s="337">
         <f t="shared" si="21"/>
         <v>1782528.7</v>
       </c>
-      <c r="Q75" s="343"/>
+      <c r="Q75" s="337"/>
       <c r="R75" s="191">
         <f t="shared" si="22"/>
         <v>1836593.7</v>
@@ -11708,11 +11707,11 @@
       <c r="O76" s="277">
         <v>0</v>
       </c>
-      <c r="P76" s="343">
+      <c r="P76" s="337">
         <f t="shared" si="21"/>
         <v>1975071.71</v>
       </c>
-      <c r="Q76" s="343"/>
+      <c r="Q76" s="337"/>
       <c r="R76" s="191">
         <f t="shared" si="22"/>
         <v>2034976.71</v>
@@ -11781,11 +11780,11 @@
       <c r="O77" s="277">
         <v>0</v>
       </c>
-      <c r="P77" s="343">
+      <c r="P77" s="337">
         <f t="shared" si="21"/>
         <v>711343.72</v>
       </c>
-      <c r="Q77" s="343"/>
+      <c r="Q77" s="337"/>
       <c r="R77" s="191">
         <f t="shared" si="22"/>
         <v>732919.72</v>
@@ -11854,11 +11853,11 @@
       <c r="O78" s="277">
         <v>0</v>
       </c>
-      <c r="P78" s="343">
+      <c r="P78" s="337">
         <f t="shared" si="21"/>
         <v>711343.73</v>
       </c>
-      <c r="Q78" s="343"/>
+      <c r="Q78" s="337"/>
       <c r="R78" s="191">
         <f t="shared" si="22"/>
         <v>732919.73</v>
@@ -11924,11 +11923,11 @@
       <c r="O79" s="277">
         <v>0</v>
       </c>
-      <c r="P79" s="343">
+      <c r="P79" s="337">
         <f t="shared" si="21"/>
         <v>743613.74</v>
       </c>
-      <c r="Q79" s="343"/>
+      <c r="Q79" s="337"/>
       <c r="R79" s="191">
         <f t="shared" si="22"/>
         <v>766168.74</v>
@@ -11994,11 +11993,11 @@
       <c r="O80" s="280">
         <v>91915.68</v>
       </c>
-      <c r="P80" s="343">
+      <c r="P80" s="337">
         <f t="shared" si="21"/>
         <v>811326.75</v>
       </c>
-      <c r="Q80" s="343"/>
+      <c r="Q80" s="337"/>
       <c r="R80" s="191">
         <f t="shared" si="22"/>
         <v>835934.75</v>
@@ -12067,11 +12066,11 @@
       <c r="O81" s="277">
         <v>0</v>
       </c>
-      <c r="P81" s="343">
+      <c r="P81" s="337">
         <f t="shared" si="21"/>
         <v>751681.76</v>
       </c>
-      <c r="Q81" s="343"/>
+      <c r="Q81" s="337"/>
       <c r="R81" s="191">
         <f t="shared" si="22"/>
         <v>774480.76</v>
@@ -12137,11 +12136,11 @@
         <f>2258*100</f>
         <v>225800</v>
       </c>
-      <c r="P82" s="343">
+      <c r="P82" s="337">
         <f t="shared" si="21"/>
         <v>1105325.77</v>
       </c>
-      <c r="Q82" s="343"/>
+      <c r="Q82" s="337"/>
       <c r="R82" s="191">
         <f t="shared" si="22"/>
         <v>1138850.77</v>
@@ -12211,11 +12210,11 @@
         <f>2258*100</f>
         <v>225800</v>
       </c>
-      <c r="P83" s="343">
+      <c r="P83" s="337">
         <f t="shared" si="21"/>
         <v>978501.78</v>
       </c>
-      <c r="Q83" s="343"/>
+      <c r="Q83" s="337"/>
       <c r="R83" s="191">
         <f t="shared" si="22"/>
         <v>1008180.78</v>
@@ -12283,11 +12282,11 @@
       <c r="O84" s="277">
         <v>0</v>
       </c>
-      <c r="P84" s="343">
+      <c r="P84" s="337">
         <f t="shared" si="21"/>
         <v>1525697.79</v>
       </c>
-      <c r="Q84" s="343"/>
+      <c r="Q84" s="337"/>
       <c r="R84" s="191">
         <f t="shared" si="22"/>
         <v>1571972.79</v>
@@ -12358,11 +12357,11 @@
       <c r="O85" s="277">
         <v>0</v>
       </c>
-      <c r="P85" s="343">
+      <c r="P85" s="337">
         <f t="shared" si="21"/>
         <v>728882.8</v>
       </c>
-      <c r="Q85" s="343"/>
+      <c r="Q85" s="337"/>
       <c r="R85" s="191">
         <f t="shared" si="22"/>
         <v>750990.8</v>
@@ -12431,11 +12430,11 @@
       <c r="O86" s="277">
         <v>0</v>
       </c>
-      <c r="P86" s="343">
+      <c r="P86" s="337">
         <f t="shared" si="21"/>
         <v>751681.81</v>
       </c>
-      <c r="Q86" s="343"/>
+      <c r="Q86" s="337"/>
       <c r="R86" s="191">
         <f t="shared" si="22"/>
         <v>774480.81</v>
@@ -12504,11 +12503,11 @@
       <c r="O87" s="277">
         <v>0</v>
       </c>
-      <c r="P87" s="343">
+      <c r="P87" s="337">
         <f t="shared" si="21"/>
         <v>706909.82</v>
       </c>
-      <c r="Q87" s="343"/>
+      <c r="Q87" s="337"/>
       <c r="R87" s="191">
         <f t="shared" si="22"/>
         <v>728350.82</v>
@@ -12577,11 +12576,11 @@
       <c r="O88" s="277">
         <v>0</v>
       </c>
-      <c r="P88" s="343">
+      <c r="P88" s="337">
         <f t="shared" si="21"/>
         <v>752351.83</v>
       </c>
-      <c r="Q88" s="343"/>
+      <c r="Q88" s="337"/>
       <c r="R88" s="191">
         <f t="shared" si="22"/>
         <v>775171.83</v>
@@ -12646,11 +12645,11 @@
       <c r="O89" s="277">
         <v>0</v>
       </c>
-      <c r="P89" s="343">
+      <c r="P89" s="337">
         <f t="shared" si="21"/>
         <v>752351.84</v>
       </c>
-      <c r="Q89" s="343"/>
+      <c r="Q89" s="337"/>
       <c r="R89" s="191">
         <f t="shared" si="22"/>
         <v>775171.84</v>
@@ -12716,11 +12715,11 @@
       <c r="O90" s="277">
         <v>0</v>
       </c>
-      <c r="P90" s="343">
+      <c r="P90" s="337">
         <f t="shared" si="21"/>
         <v>775884.85</v>
       </c>
-      <c r="Q90" s="343"/>
+      <c r="Q90" s="337"/>
       <c r="R90" s="191">
         <f t="shared" si="22"/>
         <v>799417.85</v>
@@ -12790,11 +12789,11 @@
       <c r="O91" s="277">
         <v>0</v>
       </c>
-      <c r="P91" s="343">
+      <c r="P91" s="337">
         <f t="shared" si="21"/>
         <v>1240578.8600000001</v>
       </c>
-      <c r="Q91" s="343"/>
+      <c r="Q91" s="337"/>
       <c r="R91" s="191">
         <f t="shared" si="22"/>
         <v>1278206.8600000001</v>
@@ -12863,11 +12862,11 @@
       <c r="O92" s="277">
         <v>0</v>
       </c>
-      <c r="P92" s="343">
+      <c r="P92" s="337">
         <f t="shared" si="21"/>
         <v>775884.87</v>
       </c>
-      <c r="Q92" s="343"/>
+      <c r="Q92" s="337"/>
       <c r="R92" s="191">
         <f t="shared" si="22"/>
         <v>799417.87</v>
@@ -12932,11 +12931,11 @@
       <c r="O93" s="277">
         <v>0</v>
       </c>
-      <c r="P93" s="343">
+      <c r="P93" s="337">
         <f t="shared" si="21"/>
         <v>775424.88</v>
       </c>
-      <c r="Q93" s="343"/>
+      <c r="Q93" s="337"/>
       <c r="R93" s="191">
         <f t="shared" si="22"/>
         <v>798944.88</v>
@@ -12999,11 +12998,11 @@
       <c r="O94" s="277">
         <v>0</v>
       </c>
-      <c r="P94" s="343">
+      <c r="P94" s="337">
         <f t="shared" si="21"/>
         <v>1786739.89</v>
       </c>
-      <c r="Q94" s="343"/>
+      <c r="Q94" s="337"/>
       <c r="R94" s="191">
         <f t="shared" si="22"/>
         <v>1840932.89</v>
@@ -13071,11 +13070,11 @@
       <c r="O95" s="277">
         <v>0</v>
       </c>
-      <c r="P95" s="343">
+      <c r="P95" s="337">
         <f t="shared" si="21"/>
         <v>1407107.9</v>
       </c>
-      <c r="Q95" s="343"/>
+      <c r="Q95" s="337"/>
       <c r="R95" s="191">
         <f t="shared" si="22"/>
         <v>1449785.9</v>
@@ -13144,11 +13143,11 @@
       <c r="O96" s="277">
         <v>0</v>
       </c>
-      <c r="P96" s="343">
+      <c r="P96" s="337">
         <f t="shared" si="21"/>
         <v>775884.91</v>
       </c>
-      <c r="Q96" s="343"/>
+      <c r="Q96" s="337"/>
       <c r="R96" s="191">
         <f t="shared" si="22"/>
         <v>799417.91</v>
@@ -13217,11 +13216,11 @@
       <c r="O97" s="277">
         <v>0</v>
       </c>
-      <c r="P97" s="343">
+      <c r="P97" s="337">
         <f t="shared" si="21"/>
         <v>775884.92</v>
       </c>
-      <c r="Q97" s="343"/>
+      <c r="Q97" s="337"/>
       <c r="R97" s="191">
         <f t="shared" si="22"/>
         <v>799418.92</v>
@@ -13289,11 +13288,11 @@
       <c r="O98" s="277">
         <v>0</v>
       </c>
-      <c r="P98" s="343">
+      <c r="P98" s="337">
         <f t="shared" si="21"/>
         <v>1524078.93</v>
       </c>
-      <c r="Q98" s="343"/>
+      <c r="Q98" s="337"/>
       <c r="R98" s="191">
         <f t="shared" si="22"/>
         <v>1570304.93</v>
@@ -13362,11 +13361,11 @@
       <c r="O99" s="277">
         <v>0</v>
       </c>
-      <c r="P99" s="343">
+      <c r="P99" s="337">
         <f t="shared" si="21"/>
         <v>775884.94</v>
       </c>
-      <c r="Q99" s="343"/>
+      <c r="Q99" s="337"/>
       <c r="R99" s="191">
         <f t="shared" si="22"/>
         <v>799418.94</v>
@@ -13432,11 +13431,11 @@
       <c r="O100" s="277">
         <v>0</v>
       </c>
-      <c r="P100" s="343">
+      <c r="P100" s="337">
         <f t="shared" si="21"/>
         <v>7379940.9500000002</v>
       </c>
-      <c r="Q100" s="343"/>
+      <c r="Q100" s="337"/>
       <c r="R100" s="191">
         <f t="shared" si="22"/>
         <v>7603775.9500000002</v>
@@ -13501,11 +13500,11 @@
       <c r="O101" s="277">
         <v>0</v>
       </c>
-      <c r="P101" s="343">
+      <c r="P101" s="337">
         <f t="shared" si="21"/>
         <v>703583.96</v>
       </c>
-      <c r="Q101" s="343"/>
+      <c r="Q101" s="337"/>
       <c r="R101" s="191">
         <f t="shared" si="22"/>
         <v>724924.96</v>
@@ -13574,11 +13573,11 @@
       <c r="O102" s="277">
         <v>0</v>
       </c>
-      <c r="P102" s="343">
+      <c r="P102" s="337">
         <f t="shared" ref="P102:P133" si="30">ROUND(SUM(G102:O102),0) + S102</f>
         <v>727186.97</v>
       </c>
-      <c r="Q102" s="343"/>
+      <c r="Q102" s="337"/>
       <c r="R102" s="191">
         <f t="shared" ref="R102:R133" si="31">ROUND(P102+P102*3.033%,0) + S102</f>
         <v>749243.97</v>
@@ -13647,11 +13646,11 @@
       <c r="O103" s="277">
         <v>0</v>
       </c>
-      <c r="P103" s="343">
+      <c r="P103" s="337">
         <f t="shared" si="30"/>
         <v>775884.98</v>
       </c>
-      <c r="Q103" s="343"/>
+      <c r="Q103" s="337"/>
       <c r="R103" s="191">
         <f t="shared" si="31"/>
         <v>799418.98</v>
@@ -13717,11 +13716,11 @@
       <c r="O104" s="277">
         <v>0</v>
       </c>
-      <c r="P104" s="343">
+      <c r="P104" s="337">
         <f t="shared" si="30"/>
         <v>775884.99</v>
       </c>
-      <c r="Q104" s="343"/>
+      <c r="Q104" s="337"/>
       <c r="R104" s="191">
         <f t="shared" si="31"/>
         <v>799418.99</v>
@@ -13790,11 +13789,11 @@
       <c r="O105" s="277">
         <v>0</v>
       </c>
-      <c r="P105" s="343">
+      <c r="P105" s="337">
         <f t="shared" si="30"/>
         <v>775885</v>
       </c>
-      <c r="Q105" s="343"/>
+      <c r="Q105" s="337"/>
       <c r="R105" s="191">
         <f t="shared" si="31"/>
         <v>799419</v>
@@ -13860,11 +13859,11 @@
       <c r="O106" s="280">
         <v>122554.24000000001</v>
       </c>
-      <c r="P106" s="343">
+      <c r="P106" s="337">
         <f t="shared" si="30"/>
         <v>898439.01</v>
       </c>
-      <c r="Q106" s="343"/>
+      <c r="Q106" s="337"/>
       <c r="R106" s="191">
         <f t="shared" si="31"/>
         <v>925690.01</v>
@@ -13929,11 +13928,11 @@
       <c r="O107" s="277">
         <v>0</v>
       </c>
-      <c r="P107" s="343">
+      <c r="P107" s="337">
         <f t="shared" si="30"/>
         <v>776326.02</v>
       </c>
-      <c r="Q107" s="343"/>
+      <c r="Q107" s="337"/>
       <c r="R107" s="191">
         <f t="shared" si="31"/>
         <v>799873.02</v>
@@ -14002,11 +14001,11 @@
       <c r="O108" s="277">
         <v>0</v>
       </c>
-      <c r="P108" s="343">
+      <c r="P108" s="337">
         <f t="shared" si="30"/>
         <v>775885.03</v>
       </c>
-      <c r="Q108" s="343"/>
+      <c r="Q108" s="337"/>
       <c r="R108" s="191">
         <f t="shared" si="31"/>
         <v>799419.03</v>
@@ -14072,11 +14071,11 @@
       <c r="O109" s="277">
         <v>0</v>
       </c>
-      <c r="P109" s="343">
+      <c r="P109" s="337">
         <f t="shared" si="30"/>
         <v>767817.04</v>
       </c>
-      <c r="Q109" s="343"/>
+      <c r="Q109" s="337"/>
       <c r="R109" s="191">
         <f t="shared" si="31"/>
         <v>791106.04</v>
@@ -14145,11 +14144,11 @@
       <c r="O110" s="277">
         <v>0</v>
       </c>
-      <c r="P110" s="343">
+      <c r="P110" s="337">
         <f t="shared" si="30"/>
         <v>1201854.05</v>
       </c>
-      <c r="Q110" s="343"/>
+      <c r="Q110" s="337"/>
       <c r="R110" s="191">
         <f t="shared" si="31"/>
         <v>1238307.05</v>
@@ -14217,11 +14216,11 @@
       <c r="O111" s="277">
         <v>0</v>
       </c>
-      <c r="P111" s="343">
+      <c r="P111" s="337">
         <f t="shared" si="30"/>
         <v>6220287.0599999996</v>
       </c>
-      <c r="Q111" s="343"/>
+      <c r="Q111" s="337"/>
       <c r="R111" s="191">
         <f t="shared" si="31"/>
         <v>6408949.0599999996</v>
@@ -14290,11 +14289,11 @@
       <c r="O112" s="277">
         <v>0</v>
       </c>
-      <c r="P112" s="343">
+      <c r="P112" s="337">
         <f t="shared" si="30"/>
         <v>743614.07</v>
       </c>
-      <c r="Q112" s="343"/>
+      <c r="Q112" s="337"/>
       <c r="R112" s="191">
         <f t="shared" si="31"/>
         <v>766169.07</v>
@@ -14363,11 +14362,11 @@
       <c r="O113" s="277">
         <v>0</v>
       </c>
-      <c r="P113" s="343">
+      <c r="P113" s="337">
         <f t="shared" si="30"/>
         <v>743614.08</v>
       </c>
-      <c r="Q113" s="343"/>
+      <c r="Q113" s="337"/>
       <c r="R113" s="191">
         <f t="shared" si="31"/>
         <v>766169.08</v>
@@ -14432,11 +14431,11 @@
       <c r="O114" s="277">
         <v>0</v>
       </c>
-      <c r="P114" s="343">
+      <c r="P114" s="337">
         <f t="shared" si="30"/>
         <v>1614062.09</v>
       </c>
-      <c r="Q114" s="343"/>
+      <c r="Q114" s="337"/>
       <c r="R114" s="191">
         <f t="shared" si="31"/>
         <v>1663018.09</v>
@@ -14505,11 +14504,11 @@
       <c r="O115" s="277">
         <v>0</v>
       </c>
-      <c r="P115" s="343">
+      <c r="P115" s="337">
         <f t="shared" si="30"/>
         <v>759749.1</v>
       </c>
-      <c r="Q115" s="343"/>
+      <c r="Q115" s="337"/>
       <c r="R115" s="191">
         <f t="shared" si="31"/>
         <v>782793.1</v>
@@ -14579,11 +14578,11 @@
       <c r="O116" s="277">
         <v>0</v>
       </c>
-      <c r="P116" s="343">
+      <c r="P116" s="337">
         <f t="shared" si="30"/>
         <v>751682.11</v>
       </c>
-      <c r="Q116" s="343"/>
+      <c r="Q116" s="337"/>
       <c r="R116" s="191">
         <f t="shared" si="31"/>
         <v>774482.11</v>
@@ -14648,11 +14647,11 @@
       <c r="O117" s="277">
         <v>0</v>
       </c>
-      <c r="P117" s="343">
+      <c r="P117" s="337">
         <f t="shared" si="30"/>
         <v>1473295.12</v>
       </c>
-      <c r="Q117" s="343"/>
+      <c r="Q117" s="337"/>
       <c r="R117" s="191">
         <f t="shared" si="31"/>
         <v>1517981.12</v>
@@ -14720,11 +14719,11 @@
       <c r="O118" s="277">
         <v>0</v>
       </c>
-      <c r="P118" s="343">
+      <c r="P118" s="337">
         <f t="shared" si="30"/>
         <v>745215.13</v>
       </c>
-      <c r="Q118" s="343"/>
+      <c r="Q118" s="337"/>
       <c r="R118" s="191">
         <f t="shared" si="31"/>
         <v>767819.13</v>
@@ -14790,11 +14789,11 @@
       <c r="O119" s="277">
         <v>0</v>
       </c>
-      <c r="P119" s="343">
+      <c r="P119" s="337">
         <f t="shared" si="30"/>
         <v>751682.14</v>
       </c>
-      <c r="Q119" s="343"/>
+      <c r="Q119" s="337"/>
       <c r="R119" s="191">
         <f t="shared" si="31"/>
         <v>774482.14</v>
@@ -14860,11 +14859,11 @@
       <c r="O120" s="277">
         <v>0</v>
       </c>
-      <c r="P120" s="343">
+      <c r="P120" s="337">
         <f t="shared" si="30"/>
         <v>904966.15</v>
       </c>
-      <c r="Q120" s="343"/>
+      <c r="Q120" s="337"/>
       <c r="R120" s="191">
         <f t="shared" si="31"/>
         <v>932415.15</v>
@@ -14932,11 +14931,11 @@
       <c r="O121" s="280">
         <v>107234.96</v>
       </c>
-      <c r="P121" s="343">
+      <c r="P121" s="337">
         <f t="shared" si="30"/>
         <v>931484.16000000003</v>
       </c>
-      <c r="Q121" s="343"/>
+      <c r="Q121" s="337"/>
       <c r="R121" s="191">
         <f t="shared" si="31"/>
         <v>959737.16</v>
@@ -15002,11 +15001,11 @@
       <c r="O122" s="277">
         <v>0</v>
       </c>
-      <c r="P122" s="343">
+      <c r="P122" s="337">
         <f t="shared" si="30"/>
         <v>880763.17</v>
       </c>
-      <c r="Q122" s="343"/>
+      <c r="Q122" s="337"/>
       <c r="R122" s="191">
         <f t="shared" si="31"/>
         <v>907478.17</v>
@@ -15075,11 +15074,11 @@
       <c r="O123" s="277">
         <v>0</v>
       </c>
-      <c r="P123" s="343">
+      <c r="P123" s="337">
         <f t="shared" si="30"/>
         <v>856559.18</v>
       </c>
-      <c r="Q123" s="343"/>
+      <c r="Q123" s="337"/>
       <c r="R123" s="191">
         <f t="shared" si="31"/>
         <v>882540.18</v>
@@ -15147,11 +15146,11 @@
       <c r="O124" s="277">
         <v>0</v>
       </c>
-      <c r="P124" s="343">
+      <c r="P124" s="337">
         <f t="shared" si="30"/>
         <v>824588.19</v>
       </c>
-      <c r="Q124" s="343"/>
+      <c r="Q124" s="337"/>
       <c r="R124" s="191">
         <f t="shared" si="31"/>
         <v>849599.19</v>
@@ -15220,11 +15219,11 @@
       <c r="O125" s="277">
         <v>0</v>
       </c>
-      <c r="P125" s="343">
+      <c r="P125" s="337">
         <f t="shared" si="30"/>
         <v>759749.2</v>
       </c>
-      <c r="Q125" s="343"/>
+      <c r="Q125" s="337"/>
       <c r="R125" s="191">
         <f t="shared" si="31"/>
         <v>782793.2</v>
@@ -15293,11 +15292,11 @@
       <c r="O126" s="277">
         <v>0</v>
       </c>
-      <c r="P126" s="343">
+      <c r="P126" s="337">
         <f t="shared" si="30"/>
         <v>759749.21</v>
       </c>
-      <c r="Q126" s="343"/>
+      <c r="Q126" s="337"/>
       <c r="R126" s="191">
         <f t="shared" si="31"/>
         <v>782793.21</v>
@@ -15366,11 +15365,11 @@
       <c r="O127" s="277">
         <v>0</v>
       </c>
-      <c r="P127" s="343">
+      <c r="P127" s="337">
         <f t="shared" si="30"/>
         <v>759749.22</v>
       </c>
-      <c r="Q127" s="343"/>
+      <c r="Q127" s="337"/>
       <c r="R127" s="191">
         <f t="shared" si="31"/>
         <v>782793.22</v>
@@ -15436,11 +15435,11 @@
       <c r="O128" s="277">
         <v>0</v>
       </c>
-      <c r="P128" s="343">
+      <c r="P128" s="337">
         <f t="shared" si="30"/>
         <v>759749.23</v>
       </c>
-      <c r="Q128" s="343"/>
+      <c r="Q128" s="337"/>
       <c r="R128" s="191">
         <f t="shared" si="31"/>
         <v>782793.23</v>
@@ -15508,11 +15507,11 @@
       <c r="O129" s="277">
         <v>0</v>
       </c>
-      <c r="P129" s="343">
+      <c r="P129" s="337">
         <f t="shared" si="30"/>
         <v>737383.24</v>
       </c>
-      <c r="Q129" s="343"/>
+      <c r="Q129" s="337"/>
       <c r="R129" s="191">
         <f t="shared" si="31"/>
         <v>759749.24</v>
@@ -15578,11 +15577,11 @@
       <c r="O130" s="277">
         <v>0</v>
       </c>
-      <c r="P130" s="343">
+      <c r="P130" s="337">
         <f t="shared" si="30"/>
         <v>759749.25</v>
       </c>
-      <c r="Q130" s="343"/>
+      <c r="Q130" s="337"/>
       <c r="R130" s="191">
         <f t="shared" si="31"/>
         <v>782793.25</v>
@@ -15651,11 +15650,11 @@
       <c r="O131" s="277">
         <v>0</v>
       </c>
-      <c r="P131" s="343">
+      <c r="P131" s="337">
         <f t="shared" si="30"/>
         <v>759749.26</v>
       </c>
-      <c r="Q131" s="343"/>
+      <c r="Q131" s="337"/>
       <c r="R131" s="191">
         <f t="shared" si="31"/>
         <v>782793.26</v>
@@ -15721,11 +15720,11 @@
       <c r="O132" s="277">
         <v>0</v>
       </c>
-      <c r="P132" s="343">
+      <c r="P132" s="337">
         <f t="shared" si="30"/>
         <v>840425.27</v>
       </c>
-      <c r="Q132" s="343"/>
+      <c r="Q132" s="337"/>
       <c r="R132" s="191">
         <f t="shared" si="31"/>
         <v>865916.27</v>
@@ -15794,11 +15793,11 @@
       <c r="O133" s="277">
         <v>0</v>
       </c>
-      <c r="P133" s="343">
+      <c r="P133" s="337">
         <f t="shared" si="30"/>
         <v>880763.28</v>
       </c>
-      <c r="Q133" s="343"/>
+      <c r="Q133" s="337"/>
       <c r="R133" s="191">
         <f t="shared" si="31"/>
         <v>907478.28</v>
@@ -15864,11 +15863,11 @@
       <c r="O134" s="277">
         <v>0</v>
       </c>
-      <c r="P134" s="343">
+      <c r="P134" s="337">
         <f t="shared" ref="P134:P144" si="36">ROUND(SUM(G134:O134),0) + S134</f>
         <v>880763.29</v>
       </c>
-      <c r="Q134" s="343"/>
+      <c r="Q134" s="337"/>
       <c r="R134" s="191">
         <f t="shared" ref="R134:R144" si="37">ROUND(P134+P134*3.033%,0) + S134</f>
         <v>907478.29</v>
@@ -15936,11 +15935,11 @@
       <c r="O135" s="277">
         <v>0</v>
       </c>
-      <c r="P135" s="343">
+      <c r="P135" s="337">
         <f t="shared" si="36"/>
         <v>848316.3</v>
       </c>
-      <c r="Q135" s="343"/>
+      <c r="Q135" s="337"/>
       <c r="R135" s="191">
         <f t="shared" si="37"/>
         <v>874047.3</v>
@@ -16009,11 +16008,11 @@
       <c r="O136" s="277">
         <v>0</v>
       </c>
-      <c r="P136" s="343">
+      <c r="P136" s="337">
         <f t="shared" si="36"/>
         <v>880763.31</v>
       </c>
-      <c r="Q136" s="343"/>
+      <c r="Q136" s="337"/>
       <c r="R136" s="191">
         <f t="shared" si="37"/>
         <v>907478.31</v>
@@ -16082,11 +16081,11 @@
       <c r="O137" s="277">
         <v>0</v>
       </c>
-      <c r="P137" s="343">
+      <c r="P137" s="337">
         <f t="shared" si="36"/>
         <v>872696.31999999995</v>
       </c>
-      <c r="Q137" s="343"/>
+      <c r="Q137" s="337"/>
       <c r="R137" s="191">
         <f t="shared" si="37"/>
         <v>899166.32</v>
@@ -16155,11 +16154,11 @@
       <c r="O138" s="277">
         <v>0</v>
       </c>
-      <c r="P138" s="343">
+      <c r="P138" s="337">
         <f t="shared" si="36"/>
         <v>904966.33</v>
       </c>
-      <c r="Q138" s="343"/>
+      <c r="Q138" s="337"/>
       <c r="R138" s="191">
         <f t="shared" si="37"/>
         <v>932415.33</v>
@@ -16227,11 +16226,11 @@
       <c r="O139" s="277">
         <v>0</v>
       </c>
-      <c r="P139" s="343">
+      <c r="P139" s="337">
         <f t="shared" si="36"/>
         <v>792194.34</v>
       </c>
-      <c r="Q139" s="343"/>
+      <c r="Q139" s="337"/>
       <c r="R139" s="191">
         <f t="shared" si="37"/>
         <v>816223.34</v>
@@ -16299,11 +16298,11 @@
       <c r="O140" s="277">
         <v>0</v>
       </c>
-      <c r="P140" s="343">
+      <c r="P140" s="337">
         <f t="shared" si="36"/>
         <v>854834.35</v>
       </c>
-      <c r="Q140" s="343"/>
+      <c r="Q140" s="337"/>
       <c r="R140" s="191">
         <f t="shared" si="37"/>
         <v>880762.35</v>
@@ -16372,11 +16371,11 @@
       <c r="O141" s="277">
         <v>0</v>
       </c>
-      <c r="P141" s="343">
+      <c r="P141" s="337">
         <f t="shared" si="36"/>
         <v>888831.36</v>
       </c>
-      <c r="Q141" s="343"/>
+      <c r="Q141" s="337"/>
       <c r="R141" s="191">
         <f t="shared" si="37"/>
         <v>915791.35999999999</v>
@@ -16445,11 +16444,11 @@
       <c r="O142" s="277">
         <v>0</v>
       </c>
-      <c r="P142" s="343">
+      <c r="P142" s="337">
         <f t="shared" si="36"/>
         <v>824290.37</v>
       </c>
-      <c r="Q142" s="343"/>
+      <c r="Q142" s="337"/>
       <c r="R142" s="191">
         <f t="shared" si="37"/>
         <v>849292.37</v>
@@ -16515,11 +16514,11 @@
       <c r="O143" s="277">
         <v>0</v>
       </c>
-      <c r="P143" s="343">
+      <c r="P143" s="337">
         <f t="shared" si="36"/>
         <v>877401.38</v>
       </c>
-      <c r="Q143" s="343"/>
+      <c r="Q143" s="337"/>
       <c r="R143" s="191">
         <f t="shared" si="37"/>
         <v>904014.38</v>
@@ -16587,11 +16586,11 @@
       <c r="O144" s="277">
         <v>0</v>
       </c>
-      <c r="P144" s="343">
+      <c r="P144" s="337">
         <f t="shared" si="36"/>
         <v>785399.39</v>
       </c>
-      <c r="Q144" s="343"/>
+      <c r="Q144" s="337"/>
       <c r="R144" s="191">
         <f t="shared" si="37"/>
         <v>809222.39</v>
@@ -16637,8 +16636,8 @@
       <c r="O145" s="277">
         <v>0</v>
       </c>
-      <c r="P145" s="343"/>
-      <c r="Q145" s="343"/>
+      <c r="P145" s="337"/>
+      <c r="Q145" s="337"/>
       <c r="R145" s="192"/>
       <c r="S145" s="217">
         <f t="shared" si="38"/>
@@ -16678,8 +16677,8 @@
       <c r="O146" s="277">
         <v>0</v>
       </c>
-      <c r="P146" s="343"/>
-      <c r="Q146" s="343"/>
+      <c r="P146" s="337"/>
+      <c r="Q146" s="337"/>
       <c r="R146" s="192"/>
       <c r="S146" s="217">
         <f t="shared" si="38"/>
@@ -16712,8 +16711,8 @@
       <c r="O147" s="277">
         <v>0</v>
       </c>
-      <c r="P147" s="343"/>
-      <c r="Q147" s="343"/>
+      <c r="P147" s="337"/>
+      <c r="Q147" s="337"/>
       <c r="R147" s="192"/>
       <c r="S147" s="217">
         <f t="shared" si="38"/>
@@ -16746,8 +16745,8 @@
       <c r="O148" s="277">
         <v>0</v>
       </c>
-      <c r="P148" s="343"/>
-      <c r="Q148" s="343"/>
+      <c r="P148" s="337"/>
+      <c r="Q148" s="337"/>
       <c r="R148" s="192"/>
       <c r="S148" s="217">
         <f t="shared" si="38"/>
@@ -16809,11 +16808,11 @@
       <c r="O149" s="277">
         <v>0</v>
       </c>
-      <c r="P149" s="343">
+      <c r="P149" s="337">
         <f t="shared" ref="P149:P158" si="46">ROUND(SUM(G149:O149),0) + S149</f>
         <v>695209.46</v>
       </c>
-      <c r="Q149" s="343"/>
+      <c r="Q149" s="337"/>
       <c r="R149" s="191">
         <f t="shared" ref="R149:R158" si="47">ROUND(P149+P149*3.033%,0) + S149</f>
         <v>716296.46</v>
@@ -16876,11 +16875,11 @@
       <c r="O150" s="277">
         <v>0</v>
       </c>
-      <c r="P150" s="343">
+      <c r="P150" s="337">
         <f t="shared" si="46"/>
         <v>1139411.55</v>
       </c>
-      <c r="Q150" s="343"/>
+      <c r="Q150" s="337"/>
       <c r="R150" s="191">
         <f t="shared" si="47"/>
         <v>1173971.55</v>
@@ -16948,11 +16947,11 @@
       <c r="O151" s="277">
         <v>0</v>
       </c>
-      <c r="P151" s="343">
+      <c r="P151" s="337">
         <f t="shared" si="46"/>
         <v>759749.58</v>
       </c>
-      <c r="Q151" s="343"/>
+      <c r="Q151" s="337"/>
       <c r="R151" s="191">
         <f t="shared" si="47"/>
         <v>782794.58</v>
@@ -17017,11 +17016,11 @@
       <c r="O152" s="277">
         <v>0</v>
       </c>
-      <c r="P152" s="343">
+      <c r="P152" s="337">
         <f t="shared" si="46"/>
         <v>759749.59</v>
       </c>
-      <c r="Q152" s="343"/>
+      <c r="Q152" s="337"/>
       <c r="R152" s="191">
         <f t="shared" si="47"/>
         <v>782794.59</v>
@@ -17086,11 +17085,11 @@
       <c r="O153" s="277">
         <v>0</v>
       </c>
-      <c r="P153" s="343">
+      <c r="P153" s="337">
         <f t="shared" si="46"/>
         <v>759749.63</v>
       </c>
-      <c r="Q153" s="343"/>
+      <c r="Q153" s="337"/>
       <c r="R153" s="191">
         <f t="shared" si="47"/>
         <v>782794.63</v>
@@ -17155,11 +17154,11 @@
       <c r="O154" s="277">
         <v>0</v>
       </c>
-      <c r="P154" s="343">
+      <c r="P154" s="337">
         <f t="shared" si="46"/>
         <v>743614.68</v>
       </c>
-      <c r="Q154" s="343"/>
+      <c r="Q154" s="337"/>
       <c r="R154" s="191">
         <f t="shared" si="47"/>
         <v>766170.68</v>
@@ -17223,11 +17222,11 @@
       <c r="O155" s="277">
         <v>0</v>
       </c>
-      <c r="P155" s="343">
+      <c r="P155" s="337">
         <f t="shared" si="46"/>
         <v>759750.73</v>
       </c>
-      <c r="Q155" s="343"/>
+      <c r="Q155" s="337"/>
       <c r="R155" s="191">
         <f t="shared" si="47"/>
         <v>782795.73</v>
@@ -17294,11 +17293,11 @@
       <c r="O156" s="277">
         <v>0</v>
       </c>
-      <c r="P156" s="343">
+      <c r="P156" s="337">
         <f t="shared" si="46"/>
         <v>759750.75</v>
       </c>
-      <c r="Q156" s="343"/>
+      <c r="Q156" s="337"/>
       <c r="R156" s="191">
         <f t="shared" si="47"/>
         <v>782795.75</v>
@@ -17366,11 +17365,11 @@
       <c r="O157" s="277">
         <v>0</v>
       </c>
-      <c r="P157" s="343">
+      <c r="P157" s="337">
         <f t="shared" si="46"/>
         <v>759749.76</v>
       </c>
-      <c r="Q157" s="343"/>
+      <c r="Q157" s="337"/>
       <c r="R157" s="191">
         <f t="shared" si="47"/>
         <v>782794.76</v>
@@ -17434,11 +17433,11 @@
       <c r="O158" s="277">
         <v>0</v>
       </c>
-      <c r="P158" s="343">
+      <c r="P158" s="337">
         <f t="shared" si="46"/>
         <v>760873.04</v>
       </c>
-      <c r="Q158" s="343"/>
+      <c r="Q158" s="337"/>
       <c r="R158" s="191">
         <f t="shared" si="47"/>
         <v>783952.04</v>
@@ -17473,8 +17472,8 @@
         <v>0</v>
       </c>
       <c r="O159" s="279"/>
-      <c r="P159" s="369"/>
-      <c r="Q159" s="369"/>
+      <c r="P159" s="343"/>
+      <c r="Q159" s="343"/>
       <c r="R159" s="259"/>
       <c r="S159" s="217"/>
       <c r="T159" s="19"/>
@@ -17495,8 +17494,8 @@
       <c r="M160" s="287"/>
       <c r="N160" s="287"/>
       <c r="O160" s="288"/>
-      <c r="P160" s="370"/>
-      <c r="Q160" s="370"/>
+      <c r="P160" s="344"/>
+      <c r="Q160" s="344"/>
       <c r="R160" s="260"/>
       <c r="S160" s="217"/>
       <c r="T160" s="151"/>
@@ -17550,264 +17549,198 @@
         <f t="shared" si="50"/>
         <v>1370214.314032</v>
       </c>
-      <c r="P161" s="367">
+      <c r="P161" s="341">
         <f>SUM(P6:P160)</f>
         <v>169569238.07000002</v>
       </c>
-      <c r="Q161" s="368"/>
+      <c r="Q161" s="342"/>
       <c r="R161" s="298">
         <f>SUM(R6:R160)</f>
         <v>174712392.07000002</v>
       </c>
-      <c r="S161" s="367"/>
-      <c r="T161" s="368"/>
+      <c r="S161" s="341"/>
+      <c r="T161" s="342"/>
     </row>
     <row r="162" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="364" t="s">
+      <c r="B162" s="338" t="s">
         <v>310</v>
       </c>
-      <c r="C162" s="364"/>
-      <c r="D162" s="364"/>
-      <c r="E162" s="364"/>
-      <c r="F162" s="364"/>
-      <c r="G162" s="364"/>
-      <c r="H162" s="364"/>
-      <c r="I162" s="364"/>
-      <c r="J162" s="364"/>
-      <c r="K162" s="364"/>
-      <c r="L162" s="364"/>
-      <c r="M162" s="364"/>
-      <c r="N162" s="364"/>
-      <c r="O162" s="364"/>
-      <c r="P162" s="364"/>
-      <c r="Q162" s="364"/>
-      <c r="R162" s="364"/>
-      <c r="S162" s="364"/>
-      <c r="T162" s="364"/>
+      <c r="C162" s="338"/>
+      <c r="D162" s="338"/>
+      <c r="E162" s="338"/>
+      <c r="F162" s="338"/>
+      <c r="G162" s="338"/>
+      <c r="H162" s="338"/>
+      <c r="I162" s="338"/>
+      <c r="J162" s="338"/>
+      <c r="K162" s="338"/>
+      <c r="L162" s="338"/>
+      <c r="M162" s="338"/>
+      <c r="N162" s="338"/>
+      <c r="O162" s="338"/>
+      <c r="P162" s="338"/>
+      <c r="Q162" s="338"/>
+      <c r="R162" s="338"/>
+      <c r="S162" s="338"/>
+      <c r="T162" s="338"/>
     </row>
     <row r="163" spans="1:20" ht="49.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="365"/>
-      <c r="C163" s="365"/>
-      <c r="D163" s="365"/>
-      <c r="E163" s="365"/>
-      <c r="F163" s="365"/>
-      <c r="G163" s="365"/>
-      <c r="H163" s="365"/>
-      <c r="I163" s="365"/>
-      <c r="J163" s="365"/>
-      <c r="K163" s="365"/>
-      <c r="L163" s="365"/>
-      <c r="M163" s="365"/>
-      <c r="N163" s="365"/>
-      <c r="O163" s="365"/>
-      <c r="P163" s="365"/>
-      <c r="Q163" s="365"/>
-      <c r="R163" s="365"/>
-      <c r="S163" s="365"/>
-      <c r="T163" s="365"/>
+      <c r="B163" s="339"/>
+      <c r="C163" s="339"/>
+      <c r="D163" s="339"/>
+      <c r="E163" s="339"/>
+      <c r="F163" s="339"/>
+      <c r="G163" s="339"/>
+      <c r="H163" s="339"/>
+      <c r="I163" s="339"/>
+      <c r="J163" s="339"/>
+      <c r="K163" s="339"/>
+      <c r="L163" s="339"/>
+      <c r="M163" s="339"/>
+      <c r="N163" s="339"/>
+      <c r="O163" s="339"/>
+      <c r="P163" s="339"/>
+      <c r="Q163" s="339"/>
+      <c r="R163" s="339"/>
+      <c r="S163" s="339"/>
+      <c r="T163" s="339"/>
     </row>
     <row r="164" spans="1:20" ht="13.7" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="366" t="s">
+      <c r="B164" s="340" t="s">
         <v>257</v>
       </c>
-      <c r="C164" s="366"/>
-      <c r="D164" s="366"/>
-      <c r="E164" s="366"/>
-      <c r="F164" s="366"/>
-      <c r="G164" s="366"/>
-      <c r="H164" s="366"/>
-      <c r="I164" s="366"/>
-      <c r="J164" s="366"/>
-      <c r="K164" s="366"/>
-      <c r="L164" s="366"/>
-      <c r="M164" s="366"/>
-      <c r="N164" s="366"/>
-      <c r="O164" s="366"/>
-      <c r="P164" s="366"/>
-      <c r="Q164" s="366"/>
-      <c r="R164" s="366"/>
-      <c r="S164" s="366"/>
-      <c r="T164" s="366"/>
+      <c r="C164" s="340"/>
+      <c r="D164" s="340"/>
+      <c r="E164" s="340"/>
+      <c r="F164" s="340"/>
+      <c r="G164" s="340"/>
+      <c r="H164" s="340"/>
+      <c r="I164" s="340"/>
+      <c r="J164" s="340"/>
+      <c r="K164" s="340"/>
+      <c r="L164" s="340"/>
+      <c r="M164" s="340"/>
+      <c r="N164" s="340"/>
+      <c r="O164" s="340"/>
+      <c r="P164" s="340"/>
+      <c r="Q164" s="340"/>
+      <c r="R164" s="340"/>
+      <c r="S164" s="340"/>
+      <c r="T164" s="340"/>
     </row>
     <row r="165" spans="1:20" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="366"/>
-      <c r="C165" s="366"/>
-      <c r="D165" s="366"/>
-      <c r="E165" s="366"/>
-      <c r="F165" s="366"/>
-      <c r="G165" s="366"/>
-      <c r="H165" s="366"/>
-      <c r="I165" s="366"/>
-      <c r="J165" s="366"/>
-      <c r="K165" s="366"/>
-      <c r="L165" s="366"/>
-      <c r="M165" s="366"/>
-      <c r="N165" s="366"/>
-      <c r="O165" s="366"/>
-      <c r="P165" s="366"/>
-      <c r="Q165" s="366"/>
-      <c r="R165" s="366"/>
-      <c r="S165" s="366"/>
-      <c r="T165" s="366"/>
+      <c r="B165" s="340"/>
+      <c r="C165" s="340"/>
+      <c r="D165" s="340"/>
+      <c r="E165" s="340"/>
+      <c r="F165" s="340"/>
+      <c r="G165" s="340"/>
+      <c r="H165" s="340"/>
+      <c r="I165" s="340"/>
+      <c r="J165" s="340"/>
+      <c r="K165" s="340"/>
+      <c r="L165" s="340"/>
+      <c r="M165" s="340"/>
+      <c r="N165" s="340"/>
+      <c r="O165" s="340"/>
+      <c r="P165" s="340"/>
+      <c r="Q165" s="340"/>
+      <c r="R165" s="340"/>
+      <c r="S165" s="340"/>
+      <c r="T165" s="340"/>
     </row>
     <row r="166" spans="1:20" ht="3.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="366"/>
-      <c r="C166" s="366"/>
-      <c r="D166" s="366"/>
-      <c r="E166" s="366"/>
-      <c r="F166" s="366"/>
-      <c r="G166" s="366"/>
-      <c r="H166" s="366"/>
-      <c r="I166" s="366"/>
-      <c r="J166" s="366"/>
-      <c r="K166" s="366"/>
-      <c r="L166" s="366"/>
-      <c r="M166" s="366"/>
-      <c r="N166" s="366"/>
-      <c r="O166" s="366"/>
-      <c r="P166" s="366"/>
-      <c r="Q166" s="366"/>
-      <c r="R166" s="366"/>
-      <c r="S166" s="366"/>
-      <c r="T166" s="366"/>
+      <c r="B166" s="340"/>
+      <c r="C166" s="340"/>
+      <c r="D166" s="340"/>
+      <c r="E166" s="340"/>
+      <c r="F166" s="340"/>
+      <c r="G166" s="340"/>
+      <c r="H166" s="340"/>
+      <c r="I166" s="340"/>
+      <c r="J166" s="340"/>
+      <c r="K166" s="340"/>
+      <c r="L166" s="340"/>
+      <c r="M166" s="340"/>
+      <c r="N166" s="340"/>
+      <c r="O166" s="340"/>
+      <c r="P166" s="340"/>
+      <c r="Q166" s="340"/>
+      <c r="R166" s="340"/>
+      <c r="S166" s="340"/>
+      <c r="T166" s="340"/>
     </row>
     <row r="167" spans="1:20" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="366"/>
-      <c r="C167" s="366"/>
-      <c r="D167" s="366"/>
-      <c r="E167" s="366"/>
-      <c r="F167" s="366"/>
-      <c r="G167" s="366"/>
-      <c r="H167" s="366"/>
-      <c r="I167" s="366"/>
-      <c r="J167" s="366"/>
-      <c r="K167" s="366"/>
-      <c r="L167" s="366"/>
-      <c r="M167" s="366"/>
-      <c r="N167" s="366"/>
-      <c r="O167" s="366"/>
-      <c r="P167" s="366"/>
-      <c r="Q167" s="366"/>
-      <c r="R167" s="366"/>
-      <c r="S167" s="366"/>
-      <c r="T167" s="366"/>
+      <c r="B167" s="340"/>
+      <c r="C167" s="340"/>
+      <c r="D167" s="340"/>
+      <c r="E167" s="340"/>
+      <c r="F167" s="340"/>
+      <c r="G167" s="340"/>
+      <c r="H167" s="340"/>
+      <c r="I167" s="340"/>
+      <c r="J167" s="340"/>
+      <c r="K167" s="340"/>
+      <c r="L167" s="340"/>
+      <c r="M167" s="340"/>
+      <c r="N167" s="340"/>
+      <c r="O167" s="340"/>
+      <c r="P167" s="340"/>
+      <c r="Q167" s="340"/>
+      <c r="R167" s="340"/>
+      <c r="S167" s="340"/>
+      <c r="T167" s="340"/>
     </row>
   </sheetData>
   <mergeCells count="186">
-    <mergeCell ref="P146:Q146"/>
-    <mergeCell ref="P147:Q147"/>
-    <mergeCell ref="P148:Q148"/>
-    <mergeCell ref="P149:Q149"/>
-    <mergeCell ref="P151:Q151"/>
-    <mergeCell ref="P141:Q141"/>
-    <mergeCell ref="P142:Q142"/>
-    <mergeCell ref="P143:Q143"/>
-    <mergeCell ref="P144:Q144"/>
-    <mergeCell ref="P145:Q145"/>
-    <mergeCell ref="P150:Q150"/>
-    <mergeCell ref="B162:T163"/>
-    <mergeCell ref="B164:T167"/>
-    <mergeCell ref="P157:Q157"/>
-    <mergeCell ref="P158:Q158"/>
-    <mergeCell ref="P161:Q161"/>
-    <mergeCell ref="P159:Q159"/>
-    <mergeCell ref="P160:Q160"/>
-    <mergeCell ref="P152:Q152"/>
-    <mergeCell ref="P153:Q153"/>
-    <mergeCell ref="P154:Q154"/>
-    <mergeCell ref="P155:Q155"/>
-    <mergeCell ref="P156:Q156"/>
-    <mergeCell ref="S161:T161"/>
-    <mergeCell ref="P136:Q136"/>
-    <mergeCell ref="P137:Q137"/>
-    <mergeCell ref="P138:Q138"/>
-    <mergeCell ref="P139:Q139"/>
-    <mergeCell ref="P140:Q140"/>
-    <mergeCell ref="P131:Q131"/>
-    <mergeCell ref="P132:Q132"/>
-    <mergeCell ref="P133:Q133"/>
-    <mergeCell ref="P134:Q134"/>
-    <mergeCell ref="P135:Q135"/>
-    <mergeCell ref="P126:Q126"/>
-    <mergeCell ref="P127:Q127"/>
-    <mergeCell ref="P128:Q128"/>
-    <mergeCell ref="P129:Q129"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="P121:Q121"/>
-    <mergeCell ref="P122:Q122"/>
-    <mergeCell ref="P123:Q123"/>
-    <mergeCell ref="P124:Q124"/>
-    <mergeCell ref="P125:Q125"/>
-    <mergeCell ref="P116:Q116"/>
-    <mergeCell ref="P117:Q117"/>
-    <mergeCell ref="P118:Q118"/>
-    <mergeCell ref="P119:Q119"/>
-    <mergeCell ref="P120:Q120"/>
-    <mergeCell ref="P111:Q111"/>
-    <mergeCell ref="P112:Q112"/>
-    <mergeCell ref="P113:Q113"/>
-    <mergeCell ref="P114:Q114"/>
-    <mergeCell ref="P115:Q115"/>
-    <mergeCell ref="P106:Q106"/>
-    <mergeCell ref="P107:Q107"/>
-    <mergeCell ref="P108:Q108"/>
-    <mergeCell ref="P109:Q109"/>
-    <mergeCell ref="P110:Q110"/>
-    <mergeCell ref="P101:Q101"/>
-    <mergeCell ref="P102:Q102"/>
-    <mergeCell ref="P103:Q103"/>
-    <mergeCell ref="P104:Q104"/>
-    <mergeCell ref="P105:Q105"/>
-    <mergeCell ref="P96:Q96"/>
-    <mergeCell ref="P97:Q97"/>
-    <mergeCell ref="P98:Q98"/>
-    <mergeCell ref="P99:Q99"/>
-    <mergeCell ref="P100:Q100"/>
-    <mergeCell ref="P91:Q91"/>
-    <mergeCell ref="P92:Q92"/>
-    <mergeCell ref="P93:Q93"/>
-    <mergeCell ref="P94:Q94"/>
-    <mergeCell ref="P95:Q95"/>
-    <mergeCell ref="P86:Q86"/>
-    <mergeCell ref="P87:Q87"/>
-    <mergeCell ref="P88:Q88"/>
-    <mergeCell ref="P89:Q89"/>
-    <mergeCell ref="P90:Q90"/>
-    <mergeCell ref="P81:Q81"/>
-    <mergeCell ref="P82:Q82"/>
-    <mergeCell ref="P83:Q83"/>
-    <mergeCell ref="P84:Q84"/>
-    <mergeCell ref="P85:Q85"/>
-    <mergeCell ref="P76:Q76"/>
-    <mergeCell ref="P77:Q77"/>
-    <mergeCell ref="P78:Q78"/>
-    <mergeCell ref="P79:Q79"/>
-    <mergeCell ref="P80:Q80"/>
-    <mergeCell ref="P71:Q71"/>
-    <mergeCell ref="P72:Q72"/>
-    <mergeCell ref="P73:Q73"/>
-    <mergeCell ref="P74:Q74"/>
-    <mergeCell ref="P75:Q75"/>
-    <mergeCell ref="P66:Q66"/>
-    <mergeCell ref="P67:Q67"/>
-    <mergeCell ref="P68:Q68"/>
-    <mergeCell ref="P69:Q69"/>
-    <mergeCell ref="P70:Q70"/>
-    <mergeCell ref="P61:Q61"/>
-    <mergeCell ref="P62:Q62"/>
-    <mergeCell ref="P63:Q63"/>
-    <mergeCell ref="P64:Q64"/>
-    <mergeCell ref="P65:Q65"/>
-    <mergeCell ref="P56:Q56"/>
-    <mergeCell ref="P57:Q57"/>
-    <mergeCell ref="P58:Q58"/>
-    <mergeCell ref="P59:Q59"/>
-    <mergeCell ref="P60:Q60"/>
-    <mergeCell ref="P51:Q51"/>
-    <mergeCell ref="P52:Q52"/>
-    <mergeCell ref="P53:Q53"/>
-    <mergeCell ref="P54:Q54"/>
-    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="P8:Q8"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="P10:Q10"/>
+    <mergeCell ref="P26:Q26"/>
+    <mergeCell ref="P21:Q21"/>
+    <mergeCell ref="P16:Q16"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
+    <mergeCell ref="P19:Q19"/>
+    <mergeCell ref="P20:Q20"/>
+    <mergeCell ref="P11:Q11"/>
+    <mergeCell ref="P12:Q12"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="P14:Q14"/>
+    <mergeCell ref="P15:Q15"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="P22:Q22"/>
+    <mergeCell ref="P23:Q23"/>
+    <mergeCell ref="P24:Q24"/>
+    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="O4:O5"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:T5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="P28:Q28"/>
     <mergeCell ref="P29:Q29"/>
@@ -17832,54 +17765,120 @@
     <mergeCell ref="P33:Q33"/>
     <mergeCell ref="P34:Q34"/>
     <mergeCell ref="P35:Q35"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="N4:N5"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C1:L1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="P5:Q5"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:T5"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="P8:Q8"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="P10:Q10"/>
-    <mergeCell ref="P26:Q26"/>
-    <mergeCell ref="P21:Q21"/>
-    <mergeCell ref="P16:Q16"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
-    <mergeCell ref="P19:Q19"/>
-    <mergeCell ref="P20:Q20"/>
-    <mergeCell ref="P11:Q11"/>
-    <mergeCell ref="P12:Q12"/>
-    <mergeCell ref="P13:Q13"/>
-    <mergeCell ref="P14:Q14"/>
-    <mergeCell ref="P15:Q15"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="P23:Q23"/>
-    <mergeCell ref="P24:Q24"/>
-    <mergeCell ref="P25:Q25"/>
+    <mergeCell ref="P56:Q56"/>
+    <mergeCell ref="P57:Q57"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="P59:Q59"/>
+    <mergeCell ref="P60:Q60"/>
+    <mergeCell ref="P51:Q51"/>
+    <mergeCell ref="P52:Q52"/>
+    <mergeCell ref="P53:Q53"/>
+    <mergeCell ref="P54:Q54"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="P66:Q66"/>
+    <mergeCell ref="P67:Q67"/>
+    <mergeCell ref="P68:Q68"/>
+    <mergeCell ref="P69:Q69"/>
+    <mergeCell ref="P70:Q70"/>
+    <mergeCell ref="P61:Q61"/>
+    <mergeCell ref="P62:Q62"/>
+    <mergeCell ref="P63:Q63"/>
+    <mergeCell ref="P64:Q64"/>
+    <mergeCell ref="P65:Q65"/>
+    <mergeCell ref="P76:Q76"/>
+    <mergeCell ref="P77:Q77"/>
+    <mergeCell ref="P78:Q78"/>
+    <mergeCell ref="P79:Q79"/>
+    <mergeCell ref="P80:Q80"/>
+    <mergeCell ref="P71:Q71"/>
+    <mergeCell ref="P72:Q72"/>
+    <mergeCell ref="P73:Q73"/>
+    <mergeCell ref="P74:Q74"/>
+    <mergeCell ref="P75:Q75"/>
+    <mergeCell ref="P86:Q86"/>
+    <mergeCell ref="P87:Q87"/>
+    <mergeCell ref="P88:Q88"/>
+    <mergeCell ref="P89:Q89"/>
+    <mergeCell ref="P90:Q90"/>
+    <mergeCell ref="P81:Q81"/>
+    <mergeCell ref="P82:Q82"/>
+    <mergeCell ref="P83:Q83"/>
+    <mergeCell ref="P84:Q84"/>
+    <mergeCell ref="P85:Q85"/>
+    <mergeCell ref="P96:Q96"/>
+    <mergeCell ref="P97:Q97"/>
+    <mergeCell ref="P98:Q98"/>
+    <mergeCell ref="P99:Q99"/>
+    <mergeCell ref="P100:Q100"/>
+    <mergeCell ref="P91:Q91"/>
+    <mergeCell ref="P92:Q92"/>
+    <mergeCell ref="P93:Q93"/>
+    <mergeCell ref="P94:Q94"/>
+    <mergeCell ref="P95:Q95"/>
+    <mergeCell ref="P106:Q106"/>
+    <mergeCell ref="P107:Q107"/>
+    <mergeCell ref="P108:Q108"/>
+    <mergeCell ref="P109:Q109"/>
+    <mergeCell ref="P110:Q110"/>
+    <mergeCell ref="P101:Q101"/>
+    <mergeCell ref="P102:Q102"/>
+    <mergeCell ref="P103:Q103"/>
+    <mergeCell ref="P104:Q104"/>
+    <mergeCell ref="P105:Q105"/>
+    <mergeCell ref="P116:Q116"/>
+    <mergeCell ref="P117:Q117"/>
+    <mergeCell ref="P118:Q118"/>
+    <mergeCell ref="P119:Q119"/>
+    <mergeCell ref="P120:Q120"/>
+    <mergeCell ref="P111:Q111"/>
+    <mergeCell ref="P112:Q112"/>
+    <mergeCell ref="P113:Q113"/>
+    <mergeCell ref="P114:Q114"/>
+    <mergeCell ref="P115:Q115"/>
+    <mergeCell ref="P126:Q126"/>
+    <mergeCell ref="P127:Q127"/>
+    <mergeCell ref="P128:Q128"/>
+    <mergeCell ref="P129:Q129"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="P121:Q121"/>
+    <mergeCell ref="P122:Q122"/>
+    <mergeCell ref="P123:Q123"/>
+    <mergeCell ref="P124:Q124"/>
+    <mergeCell ref="P125:Q125"/>
+    <mergeCell ref="P136:Q136"/>
+    <mergeCell ref="P137:Q137"/>
+    <mergeCell ref="P138:Q138"/>
+    <mergeCell ref="P139:Q139"/>
+    <mergeCell ref="P140:Q140"/>
+    <mergeCell ref="P131:Q131"/>
+    <mergeCell ref="P132:Q132"/>
+    <mergeCell ref="P133:Q133"/>
+    <mergeCell ref="P134:Q134"/>
+    <mergeCell ref="P135:Q135"/>
+    <mergeCell ref="B162:T163"/>
+    <mergeCell ref="B164:T167"/>
+    <mergeCell ref="P157:Q157"/>
+    <mergeCell ref="P158:Q158"/>
+    <mergeCell ref="P161:Q161"/>
+    <mergeCell ref="P159:Q159"/>
+    <mergeCell ref="P160:Q160"/>
+    <mergeCell ref="P152:Q152"/>
+    <mergeCell ref="P153:Q153"/>
+    <mergeCell ref="P154:Q154"/>
+    <mergeCell ref="P155:Q155"/>
+    <mergeCell ref="P156:Q156"/>
+    <mergeCell ref="S161:T161"/>
+    <mergeCell ref="P146:Q146"/>
+    <mergeCell ref="P147:Q147"/>
+    <mergeCell ref="P148:Q148"/>
+    <mergeCell ref="P149:Q149"/>
+    <mergeCell ref="P151:Q151"/>
+    <mergeCell ref="P141:Q141"/>
+    <mergeCell ref="P142:Q142"/>
+    <mergeCell ref="P143:Q143"/>
+    <mergeCell ref="P144:Q144"/>
+    <mergeCell ref="P145:Q145"/>
+    <mergeCell ref="P150:Q150"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="U66" r:id="rId1" xr:uid="{60CCA824-04D7-4098-BB5B-CC4EC0E5DE92}"/>
